--- a/main/eteacher/database_manager/python_script/excel/stage_1.xlsx
+++ b/main/eteacher/database_manager/python_script/excel/stage_1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23152" windowHeight="12195"/>
+    <workbookView windowWidth="23152" windowHeight="11745"/>
   </bookViews>
   <sheets>
     <sheet name="小学词汇1166" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3498" uniqueCount="3158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3495" uniqueCount="3156">
   <si>
     <t>word</t>
   </si>
@@ -5027,10 +5027,7 @@
     <t>n. (缩写词)数学</t>
   </si>
   <si>
-    <t>Physical</t>
-  </si>
-  <si>
-    <t>Educ...</t>
+    <t>physical education</t>
   </si>
   <si>
     <t>n. 体育课</t>
@@ -6380,7 +6377,7 @@
     <t>n. 网球; 网球运动</t>
   </si>
   <si>
-    <t>court</t>
+    <t>tennis court</t>
   </si>
   <si>
     <t>网球场</t>
@@ -7127,10 +7124,7 @@
     <t>n. 混合体; 混合; 混合物</t>
   </si>
   <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>Zealand</t>
+    <t>New Zealand</t>
   </si>
   <si>
     <t>新西兰(地名) n. 新西兰(大洋洲)</t>
@@ -10485,7 +10479,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.03539823008849" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="2" max="2" width="39.2035398230088" customWidth="1"/>
     <col min="3" max="3" width="38.9734513274336" customWidth="1"/>
     <col min="4" max="4" width="42.4955752212389" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.9911504424779" customWidth="1"/>
@@ -20730,11 +20724,9 @@
       <c r="B603" s="6" t="s">
         <v>1665</v>
       </c>
-      <c r="C603" s="6" t="s">
+      <c r="C603" s="6"/>
+      <c r="D603" s="6" t="s">
         <v>1666</v>
-      </c>
-      <c r="D603" s="6" t="s">
-        <v>1667</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -20745,13 +20737,13 @@
         <v>603</v>
       </c>
       <c r="B604" s="6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C604" s="6" t="s">
         <v>1668</v>
       </c>
-      <c r="C604" s="6" t="s">
+      <c r="D604" s="6" t="s">
         <v>1669</v>
-      </c>
-      <c r="D604" s="6" t="s">
-        <v>1670</v>
       </c>
       <c r="E604" s="3">
         <v>1</v>
@@ -20762,13 +20754,13 @@
         <v>604</v>
       </c>
       <c r="B605" s="6" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C605" s="6" t="s">
         <v>1671</v>
       </c>
-      <c r="C605" s="6" t="s">
+      <c r="D605" s="6" t="s">
         <v>1672</v>
-      </c>
-      <c r="D605" s="6" t="s">
-        <v>1673</v>
       </c>
       <c r="E605" s="3">
         <v>1</v>
@@ -20779,13 +20771,13 @@
         <v>605</v>
       </c>
       <c r="B606" s="6" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C606" s="6" t="s">
         <v>1674</v>
       </c>
-      <c r="C606" s="6" t="s">
+      <c r="D606" s="6" t="s">
         <v>1675</v>
-      </c>
-      <c r="D606" s="6" t="s">
-        <v>1676</v>
       </c>
       <c r="E606" s="3">
         <v>1</v>
@@ -20796,13 +20788,13 @@
         <v>606</v>
       </c>
       <c r="B607" s="6" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C607" s="6" t="s">
         <v>1677</v>
       </c>
-      <c r="C607" s="6" t="s">
+      <c r="D607" s="6" t="s">
         <v>1678</v>
-      </c>
-      <c r="D607" s="6" t="s">
-        <v>1679</v>
       </c>
       <c r="E607" s="3">
         <v>1</v>
@@ -20813,13 +20805,13 @@
         <v>607</v>
       </c>
       <c r="B608" s="6" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C608" s="6" t="s">
         <v>1680</v>
       </c>
-      <c r="C608" s="6" t="s">
+      <c r="D608" s="6" t="s">
         <v>1681</v>
-      </c>
-      <c r="D608" s="6" t="s">
-        <v>1682</v>
       </c>
       <c r="E608" s="3">
         <v>1</v>
@@ -20830,13 +20822,13 @@
         <v>608</v>
       </c>
       <c r="B609" s="6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C609" s="6" t="s">
         <v>1683</v>
       </c>
-      <c r="C609" s="6" t="s">
+      <c r="D609" s="6" t="s">
         <v>1684</v>
-      </c>
-      <c r="D609" s="6" t="s">
-        <v>1685</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -20847,13 +20839,13 @@
         <v>609</v>
       </c>
       <c r="B610" s="6" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C610" s="6" t="s">
         <v>1686</v>
       </c>
-      <c r="C610" s="6" t="s">
+      <c r="D610" s="6" t="s">
         <v>1687</v>
-      </c>
-      <c r="D610" s="6" t="s">
-        <v>1688</v>
       </c>
       <c r="E610" s="3">
         <v>1</v>
@@ -20864,13 +20856,13 @@
         <v>610</v>
       </c>
       <c r="B611" s="6" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C611" s="6" t="s">
         <v>1689</v>
       </c>
-      <c r="C611" s="6" t="s">
+      <c r="D611" s="6" t="s">
         <v>1690</v>
-      </c>
-      <c r="D611" s="6" t="s">
-        <v>1691</v>
       </c>
       <c r="E611" s="3">
         <v>1</v>
@@ -20881,13 +20873,13 @@
         <v>611</v>
       </c>
       <c r="B612" s="6" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C612" s="6" t="s">
         <v>1692</v>
       </c>
-      <c r="C612" s="6" t="s">
+      <c r="D612" s="6" t="s">
         <v>1693</v>
-      </c>
-      <c r="D612" s="6" t="s">
-        <v>1694</v>
       </c>
       <c r="E612" s="3">
         <v>1</v>
@@ -20898,13 +20890,13 @@
         <v>612</v>
       </c>
       <c r="B613" s="6" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C613" s="6" t="s">
         <v>1695</v>
       </c>
-      <c r="C613" s="6" t="s">
+      <c r="D613" s="6" t="s">
         <v>1696</v>
-      </c>
-      <c r="D613" s="6" t="s">
-        <v>1697</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -20932,13 +20924,13 @@
         <v>614</v>
       </c>
       <c r="B615" s="6" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C615" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="C615" s="6" t="s">
+      <c r="D615" s="6" t="s">
         <v>1699</v>
-      </c>
-      <c r="D615" s="6" t="s">
-        <v>1700</v>
       </c>
       <c r="E615" s="3">
         <v>1</v>
@@ -20949,13 +20941,13 @@
         <v>615</v>
       </c>
       <c r="B616" s="6" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C616" s="6" t="s">
         <v>1701</v>
       </c>
-      <c r="C616" s="6" t="s">
+      <c r="D616" s="6" t="s">
         <v>1702</v>
-      </c>
-      <c r="D616" s="6" t="s">
-        <v>1703</v>
       </c>
       <c r="E616" s="3">
         <v>1</v>
@@ -20966,13 +20958,13 @@
         <v>616</v>
       </c>
       <c r="B617" s="6" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C617" s="6" t="s">
         <v>1704</v>
       </c>
-      <c r="C617" s="6" t="s">
+      <c r="D617" s="6" t="s">
         <v>1705</v>
-      </c>
-      <c r="D617" s="6" t="s">
-        <v>1706</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -20983,13 +20975,13 @@
         <v>617</v>
       </c>
       <c r="B618" s="6" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C618" s="6" t="s">
         <v>1707</v>
       </c>
-      <c r="C618" s="6" t="s">
+      <c r="D618" s="6" t="s">
         <v>1708</v>
-      </c>
-      <c r="D618" s="6" t="s">
-        <v>1709</v>
       </c>
       <c r="E618" s="3">
         <v>1</v>
@@ -21017,13 +21009,13 @@
         <v>619</v>
       </c>
       <c r="B620" s="6" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C620" s="6" t="s">
         <v>1710</v>
       </c>
-      <c r="C620" s="6" t="s">
+      <c r="D620" s="6" t="s">
         <v>1711</v>
-      </c>
-      <c r="D620" s="6" t="s">
-        <v>1712</v>
       </c>
       <c r="E620" s="3">
         <v>1</v>
@@ -21034,13 +21026,13 @@
         <v>620</v>
       </c>
       <c r="B621" s="6" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C621" s="6" t="s">
         <v>1713</v>
       </c>
-      <c r="C621" s="6" t="s">
+      <c r="D621" s="6" t="s">
         <v>1714</v>
-      </c>
-      <c r="D621" s="6" t="s">
-        <v>1715</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -21051,13 +21043,13 @@
         <v>621</v>
       </c>
       <c r="B622" s="6" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C622" s="6" t="s">
         <v>1716</v>
       </c>
-      <c r="C622" s="6" t="s">
+      <c r="D622" s="6" t="s">
         <v>1717</v>
-      </c>
-      <c r="D622" s="6" t="s">
-        <v>1718</v>
       </c>
       <c r="E622" s="3">
         <v>1</v>
@@ -21068,13 +21060,13 @@
         <v>622</v>
       </c>
       <c r="B623" s="6" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C623" s="6" t="s">
         <v>1719</v>
       </c>
-      <c r="C623" s="6" t="s">
+      <c r="D623" s="6" t="s">
         <v>1720</v>
-      </c>
-      <c r="D623" s="6" t="s">
-        <v>1721</v>
       </c>
       <c r="E623" s="3">
         <v>1</v>
@@ -21085,13 +21077,13 @@
         <v>623</v>
       </c>
       <c r="B624" s="6" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C624" s="6" t="s">
         <v>1722</v>
       </c>
-      <c r="C624" s="6" t="s">
+      <c r="D624" s="6" t="s">
         <v>1723</v>
-      </c>
-      <c r="D624" s="6" t="s">
-        <v>1724</v>
       </c>
       <c r="E624" s="3">
         <v>1</v>
@@ -21102,13 +21094,13 @@
         <v>624</v>
       </c>
       <c r="B625" s="6" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C625" s="6" t="s">
         <v>1725</v>
       </c>
-      <c r="C625" s="6" t="s">
+      <c r="D625" s="6" t="s">
         <v>1726</v>
-      </c>
-      <c r="D625" s="6" t="s">
-        <v>1727</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -21119,13 +21111,13 @@
         <v>625</v>
       </c>
       <c r="B626" s="6" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C626" s="6" t="s">
         <v>1728</v>
       </c>
-      <c r="C626" s="6" t="s">
+      <c r="D626" s="6" t="s">
         <v>1729</v>
-      </c>
-      <c r="D626" s="6" t="s">
-        <v>1730</v>
       </c>
       <c r="E626" s="3">
         <v>1</v>
@@ -21136,13 +21128,13 @@
         <v>626</v>
       </c>
       <c r="B627" s="6" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C627" s="6" t="s">
         <v>1731</v>
       </c>
-      <c r="C627" s="6" t="s">
+      <c r="D627" s="6" t="s">
         <v>1732</v>
-      </c>
-      <c r="D627" s="6" t="s">
-        <v>1733</v>
       </c>
       <c r="E627" s="3">
         <v>1</v>
@@ -21153,13 +21145,13 @@
         <v>627</v>
       </c>
       <c r="B628" s="6" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C628" s="6" t="s">
         <v>1734</v>
       </c>
-      <c r="C628" s="6" t="s">
+      <c r="D628" s="6" t="s">
         <v>1735</v>
-      </c>
-      <c r="D628" s="6" t="s">
-        <v>1736</v>
       </c>
       <c r="E628" s="3">
         <v>1</v>
@@ -21170,13 +21162,13 @@
         <v>628</v>
       </c>
       <c r="B629" s="6" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C629" s="6" t="s">
         <v>1737</v>
       </c>
-      <c r="C629" s="6" t="s">
+      <c r="D629" s="6" t="s">
         <v>1738</v>
-      </c>
-      <c r="D629" s="6" t="s">
-        <v>1739</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -21187,13 +21179,13 @@
         <v>629</v>
       </c>
       <c r="B630" s="6" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C630" s="6" t="s">
         <v>1740</v>
       </c>
-      <c r="C630" s="6" t="s">
+      <c r="D630" s="6" t="s">
         <v>1741</v>
-      </c>
-      <c r="D630" s="6" t="s">
-        <v>1742</v>
       </c>
       <c r="E630" s="3">
         <v>1</v>
@@ -21204,13 +21196,13 @@
         <v>630</v>
       </c>
       <c r="B631" s="6" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C631" s="6" t="s">
         <v>1743</v>
       </c>
-      <c r="C631" s="6" t="s">
+      <c r="D631" s="6" t="s">
         <v>1744</v>
-      </c>
-      <c r="D631" s="6" t="s">
-        <v>1745</v>
       </c>
       <c r="E631" s="3">
         <v>1</v>
@@ -21221,13 +21213,13 @@
         <v>631</v>
       </c>
       <c r="B632" s="6" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C632" s="6" t="s">
         <v>1746</v>
       </c>
-      <c r="C632" s="6" t="s">
+      <c r="D632" s="6" t="s">
         <v>1747</v>
-      </c>
-      <c r="D632" s="6" t="s">
-        <v>1748</v>
       </c>
       <c r="E632" s="3">
         <v>1</v>
@@ -21238,13 +21230,13 @@
         <v>632</v>
       </c>
       <c r="B633" s="6" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C633" s="6" t="s">
         <v>1749</v>
       </c>
-      <c r="C633" s="6" t="s">
+      <c r="D633" s="6" t="s">
         <v>1750</v>
-      </c>
-      <c r="D633" s="6" t="s">
-        <v>1751</v>
       </c>
       <c r="E633" s="3">
         <v>1</v>
@@ -21255,13 +21247,13 @@
         <v>633</v>
       </c>
       <c r="B634" s="6" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C634" s="6" t="s">
         <v>1752</v>
       </c>
-      <c r="C634" s="6" t="s">
+      <c r="D634" s="6" t="s">
         <v>1753</v>
-      </c>
-      <c r="D634" s="6" t="s">
-        <v>1754</v>
       </c>
       <c r="E634" s="3">
         <v>1</v>
@@ -21272,13 +21264,13 @@
         <v>634</v>
       </c>
       <c r="B635" s="6" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C635" s="6" t="s">
         <v>1755</v>
       </c>
-      <c r="C635" s="6" t="s">
+      <c r="D635" s="6" t="s">
         <v>1756</v>
-      </c>
-      <c r="D635" s="6" t="s">
-        <v>1757</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -21289,13 +21281,13 @@
         <v>635</v>
       </c>
       <c r="B636" s="6" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C636" s="6" t="s">
         <v>1758</v>
       </c>
-      <c r="C636" s="6" t="s">
+      <c r="D636" s="6" t="s">
         <v>1759</v>
-      </c>
-      <c r="D636" s="6" t="s">
-        <v>1760</v>
       </c>
       <c r="E636" s="3">
         <v>1</v>
@@ -21306,13 +21298,13 @@
         <v>636</v>
       </c>
       <c r="B637" s="6" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C637" s="6" t="s">
         <v>1761</v>
       </c>
-      <c r="C637" s="6" t="s">
+      <c r="D637" s="6" t="s">
         <v>1762</v>
-      </c>
-      <c r="D637" s="6" t="s">
-        <v>1763</v>
       </c>
       <c r="E637" s="3">
         <v>1</v>
@@ -21329,7 +21321,7 @@
         <v>1604</v>
       </c>
       <c r="D638" s="6" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="E638" s="3">
         <v>1</v>
@@ -21340,13 +21332,13 @@
         <v>638</v>
       </c>
       <c r="B639" s="6" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C639" s="6" t="s">
         <v>1765</v>
       </c>
-      <c r="C639" s="6" t="s">
+      <c r="D639" s="6" t="s">
         <v>1766</v>
-      </c>
-      <c r="D639" s="6" t="s">
-        <v>1767</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -21357,13 +21349,13 @@
         <v>639</v>
       </c>
       <c r="B640" s="6" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C640" s="6" t="s">
         <v>1768</v>
       </c>
-      <c r="C640" s="6" t="s">
+      <c r="D640" s="6" t="s">
         <v>1769</v>
-      </c>
-      <c r="D640" s="6" t="s">
-        <v>1770</v>
       </c>
       <c r="E640" s="3">
         <v>1</v>
@@ -21374,13 +21366,13 @@
         <v>640</v>
       </c>
       <c r="B641" s="6" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C641" s="6" t="s">
         <v>1771</v>
       </c>
-      <c r="C641" s="6" t="s">
+      <c r="D641" s="6" t="s">
         <v>1772</v>
-      </c>
-      <c r="D641" s="6" t="s">
-        <v>1773</v>
       </c>
       <c r="E641" s="3">
         <v>1</v>
@@ -21391,13 +21383,13 @@
         <v>641</v>
       </c>
       <c r="B642" s="6" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C642" s="6" t="s">
         <v>1774</v>
       </c>
-      <c r="C642" s="6" t="s">
+      <c r="D642" s="6" t="s">
         <v>1775</v>
-      </c>
-      <c r="D642" s="6" t="s">
-        <v>1776</v>
       </c>
       <c r="E642" s="3">
         <v>1</v>
@@ -21408,13 +21400,13 @@
         <v>642</v>
       </c>
       <c r="B643" s="6" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C643" s="6" t="s">
         <v>1777</v>
       </c>
-      <c r="C643" s="6" t="s">
+      <c r="D643" s="6" t="s">
         <v>1778</v>
-      </c>
-      <c r="D643" s="6" t="s">
-        <v>1779</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -21425,13 +21417,13 @@
         <v>643</v>
       </c>
       <c r="B644" s="6" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C644" s="6" t="s">
         <v>1780</v>
       </c>
-      <c r="C644" s="6" t="s">
+      <c r="D644" s="6" t="s">
         <v>1781</v>
-      </c>
-      <c r="D644" s="6" t="s">
-        <v>1782</v>
       </c>
       <c r="E644" s="3">
         <v>1</v>
@@ -21442,13 +21434,13 @@
         <v>644</v>
       </c>
       <c r="B645" s="6" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C645" s="6" t="s">
         <v>1783</v>
       </c>
-      <c r="C645" s="6" t="s">
+      <c r="D645" s="6" t="s">
         <v>1784</v>
-      </c>
-      <c r="D645" s="6" t="s">
-        <v>1785</v>
       </c>
       <c r="E645" s="3">
         <v>1</v>
@@ -21459,13 +21451,13 @@
         <v>645</v>
       </c>
       <c r="B646" s="6" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C646" s="6" t="s">
         <v>1786</v>
       </c>
-      <c r="C646" s="6" t="s">
+      <c r="D646" s="6" t="s">
         <v>1787</v>
-      </c>
-      <c r="D646" s="6" t="s">
-        <v>1788</v>
       </c>
       <c r="E646" s="3">
         <v>1</v>
@@ -21476,13 +21468,13 @@
         <v>646</v>
       </c>
       <c r="B647" s="6" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C647" s="6" t="s">
         <v>1789</v>
       </c>
-      <c r="C647" s="6" t="s">
+      <c r="D647" s="6" t="s">
         <v>1790</v>
-      </c>
-      <c r="D647" s="6" t="s">
-        <v>1791</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -21493,13 +21485,13 @@
         <v>647</v>
       </c>
       <c r="B648" s="6" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C648" s="6" t="s">
         <v>1792</v>
       </c>
-      <c r="C648" s="6" t="s">
+      <c r="D648" s="6" t="s">
         <v>1793</v>
-      </c>
-      <c r="D648" s="6" t="s">
-        <v>1794</v>
       </c>
       <c r="E648" s="3">
         <v>1</v>
@@ -21510,13 +21502,13 @@
         <v>648</v>
       </c>
       <c r="B649" s="6" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C649" s="6" t="s">
         <v>1795</v>
       </c>
-      <c r="C649" s="6" t="s">
+      <c r="D649" s="6" t="s">
         <v>1796</v>
-      </c>
-      <c r="D649" s="6" t="s">
-        <v>1797</v>
       </c>
       <c r="E649" s="3">
         <v>1</v>
@@ -21527,13 +21519,13 @@
         <v>649</v>
       </c>
       <c r="B650" s="6" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C650" s="6" t="s">
         <v>1798</v>
       </c>
-      <c r="C650" s="6" t="s">
+      <c r="D650" s="6" t="s">
         <v>1799</v>
-      </c>
-      <c r="D650" s="6" t="s">
-        <v>1800</v>
       </c>
       <c r="E650" s="3">
         <v>1</v>
@@ -21544,13 +21536,13 @@
         <v>650</v>
       </c>
       <c r="B651" s="6" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C651" s="6" t="s">
         <v>1801</v>
       </c>
-      <c r="C651" s="6" t="s">
+      <c r="D651" s="6" t="s">
         <v>1802</v>
-      </c>
-      <c r="D651" s="6" t="s">
-        <v>1803</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -21561,13 +21553,13 @@
         <v>651</v>
       </c>
       <c r="B652" s="6" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C652" s="6" t="s">
         <v>1804</v>
       </c>
-      <c r="C652" s="6" t="s">
+      <c r="D652" s="6" t="s">
         <v>1805</v>
-      </c>
-      <c r="D652" s="6" t="s">
-        <v>1806</v>
       </c>
       <c r="E652" s="3">
         <v>1</v>
@@ -21578,13 +21570,13 @@
         <v>652</v>
       </c>
       <c r="B653" s="6" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C653" s="6" t="s">
         <v>1807</v>
       </c>
-      <c r="C653" s="6" t="s">
+      <c r="D653" s="6" t="s">
         <v>1808</v>
-      </c>
-      <c r="D653" s="6" t="s">
-        <v>1809</v>
       </c>
       <c r="E653" s="3">
         <v>1</v>
@@ -21595,13 +21587,13 @@
         <v>653</v>
       </c>
       <c r="B654" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C654" s="6" t="s">
         <v>1810</v>
       </c>
-      <c r="C654" s="6" t="s">
+      <c r="D654" s="6" t="s">
         <v>1811</v>
-      </c>
-      <c r="D654" s="6" t="s">
-        <v>1812</v>
       </c>
       <c r="E654" s="3">
         <v>1</v>
@@ -21612,13 +21604,13 @@
         <v>654</v>
       </c>
       <c r="B655" s="6" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C655" s="6" t="s">
         <v>1813</v>
       </c>
-      <c r="C655" s="6" t="s">
+      <c r="D655" s="6" t="s">
         <v>1814</v>
-      </c>
-      <c r="D655" s="6" t="s">
-        <v>1815</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -21629,13 +21621,13 @@
         <v>655</v>
       </c>
       <c r="B656" s="6" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C656" s="6" t="s">
         <v>1816</v>
       </c>
-      <c r="C656" s="6" t="s">
+      <c r="D656" s="6" t="s">
         <v>1817</v>
-      </c>
-      <c r="D656" s="6" t="s">
-        <v>1818</v>
       </c>
       <c r="E656" s="3">
         <v>1</v>
@@ -21646,13 +21638,13 @@
         <v>656</v>
       </c>
       <c r="B657" s="6" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C657" s="6" t="s">
         <v>1819</v>
       </c>
-      <c r="C657" s="6" t="s">
+      <c r="D657" s="6" t="s">
         <v>1820</v>
-      </c>
-      <c r="D657" s="6" t="s">
-        <v>1821</v>
       </c>
       <c r="E657" s="3">
         <v>1</v>
@@ -21663,13 +21655,13 @@
         <v>657</v>
       </c>
       <c r="B658" s="6" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C658" s="6" t="s">
         <v>1822</v>
       </c>
-      <c r="C658" s="6" t="s">
+      <c r="D658" s="6" t="s">
         <v>1823</v>
-      </c>
-      <c r="D658" s="6" t="s">
-        <v>1824</v>
       </c>
       <c r="E658" s="3">
         <v>1</v>
@@ -21680,13 +21672,13 @@
         <v>658</v>
       </c>
       <c r="B659" s="6" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C659" s="6" t="s">
         <v>1825</v>
       </c>
-      <c r="C659" s="6" t="s">
+      <c r="D659" s="6" t="s">
         <v>1826</v>
-      </c>
-      <c r="D659" s="6" t="s">
-        <v>1827</v>
       </c>
       <c r="E659" s="3">
         <v>1</v>
@@ -21697,13 +21689,13 @@
         <v>659</v>
       </c>
       <c r="B660" s="6" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C660" s="6" t="s">
         <v>1828</v>
       </c>
-      <c r="C660" s="6" t="s">
+      <c r="D660" s="6" t="s">
         <v>1829</v>
-      </c>
-      <c r="D660" s="6" t="s">
-        <v>1830</v>
       </c>
       <c r="E660" s="3">
         <v>1</v>
@@ -21714,13 +21706,13 @@
         <v>660</v>
       </c>
       <c r="B661" s="6" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C661" s="6" t="s">
         <v>1831</v>
       </c>
-      <c r="C661" s="6" t="s">
+      <c r="D661" s="6" t="s">
         <v>1832</v>
-      </c>
-      <c r="D661" s="6" t="s">
-        <v>1833</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -21731,13 +21723,13 @@
         <v>661</v>
       </c>
       <c r="B662" s="6" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C662" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="C662" s="6" t="s">
+      <c r="D662" s="6" t="s">
         <v>1835</v>
-      </c>
-      <c r="D662" s="6" t="s">
-        <v>1836</v>
       </c>
       <c r="E662" s="3">
         <v>1</v>
@@ -21748,13 +21740,13 @@
         <v>662</v>
       </c>
       <c r="B663" s="6" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C663" s="6" t="s">
         <v>1837</v>
       </c>
-      <c r="C663" s="6" t="s">
+      <c r="D663" s="6" t="s">
         <v>1838</v>
-      </c>
-      <c r="D663" s="6" t="s">
-        <v>1839</v>
       </c>
       <c r="E663" s="3">
         <v>1</v>
@@ -21765,13 +21757,13 @@
         <v>663</v>
       </c>
       <c r="B664" s="6" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C664" s="6" t="s">
         <v>1840</v>
       </c>
-      <c r="C664" s="6" t="s">
+      <c r="D664" s="6" t="s">
         <v>1841</v>
-      </c>
-      <c r="D664" s="6" t="s">
-        <v>1842</v>
       </c>
       <c r="E664" s="3">
         <v>1</v>
@@ -21782,13 +21774,13 @@
         <v>664</v>
       </c>
       <c r="B665" s="6" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C665" s="6" t="s">
         <v>1843</v>
       </c>
-      <c r="C665" s="6" t="s">
+      <c r="D665" s="6" t="s">
         <v>1844</v>
-      </c>
-      <c r="D665" s="6" t="s">
-        <v>1845</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -21799,13 +21791,13 @@
         <v>665</v>
       </c>
       <c r="B666" s="6" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C666" s="6" t="s">
         <v>1846</v>
       </c>
-      <c r="C666" s="6" t="s">
+      <c r="D666" s="6" t="s">
         <v>1847</v>
-      </c>
-      <c r="D666" s="6" t="s">
-        <v>1848</v>
       </c>
       <c r="E666" s="3">
         <v>1</v>
@@ -21833,13 +21825,13 @@
         <v>667</v>
       </c>
       <c r="B668" s="6" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C668" s="6" t="s">
         <v>1849</v>
       </c>
-      <c r="C668" s="6" t="s">
+      <c r="D668" s="6" t="s">
         <v>1850</v>
-      </c>
-      <c r="D668" s="6" t="s">
-        <v>1851</v>
       </c>
       <c r="E668" s="3">
         <v>1</v>
@@ -21850,13 +21842,13 @@
         <v>668</v>
       </c>
       <c r="B669" s="6" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C669" s="6" t="s">
         <v>1852</v>
       </c>
-      <c r="C669" s="6" t="s">
+      <c r="D669" s="6" t="s">
         <v>1853</v>
-      </c>
-      <c r="D669" s="6" t="s">
-        <v>1854</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -21867,13 +21859,13 @@
         <v>669</v>
       </c>
       <c r="B670" s="6" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C670" s="6" t="s">
         <v>1855</v>
       </c>
-      <c r="C670" s="6" t="s">
+      <c r="D670" s="6" t="s">
         <v>1856</v>
-      </c>
-      <c r="D670" s="6" t="s">
-        <v>1857</v>
       </c>
       <c r="E670" s="3">
         <v>1</v>
@@ -21884,13 +21876,13 @@
         <v>670</v>
       </c>
       <c r="B671" s="6" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C671" s="6" t="s">
         <v>1858</v>
       </c>
-      <c r="C671" s="6" t="s">
+      <c r="D671" s="6" t="s">
         <v>1859</v>
-      </c>
-      <c r="D671" s="6" t="s">
-        <v>1860</v>
       </c>
       <c r="E671" s="3">
         <v>1</v>
@@ -21901,13 +21893,13 @@
         <v>671</v>
       </c>
       <c r="B672" s="6" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C672" s="6" t="s">
         <v>1861</v>
       </c>
-      <c r="C672" s="6" t="s">
+      <c r="D672" s="6" t="s">
         <v>1862</v>
-      </c>
-      <c r="D672" s="6" t="s">
-        <v>1863</v>
       </c>
       <c r="E672" s="3">
         <v>1</v>
@@ -21918,13 +21910,13 @@
         <v>672</v>
       </c>
       <c r="B673" s="6" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C673" s="6" t="s">
         <v>1864</v>
       </c>
-      <c r="C673" s="6" t="s">
+      <c r="D673" s="6" t="s">
         <v>1865</v>
-      </c>
-      <c r="D673" s="6" t="s">
-        <v>1866</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -21935,13 +21927,13 @@
         <v>673</v>
       </c>
       <c r="B674" s="6" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C674" s="6" t="s">
         <v>1867</v>
       </c>
-      <c r="C674" s="6" t="s">
+      <c r="D674" s="6" t="s">
         <v>1868</v>
-      </c>
-      <c r="D674" s="6" t="s">
-        <v>1869</v>
       </c>
       <c r="E674" s="3">
         <v>1</v>
@@ -21952,13 +21944,13 @@
         <v>674</v>
       </c>
       <c r="B675" s="6" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C675" s="6" t="s">
         <v>1870</v>
       </c>
-      <c r="C675" s="6" t="s">
+      <c r="D675" s="6" t="s">
         <v>1871</v>
-      </c>
-      <c r="D675" s="6" t="s">
-        <v>1872</v>
       </c>
       <c r="E675" s="3">
         <v>1</v>
@@ -21969,13 +21961,13 @@
         <v>675</v>
       </c>
       <c r="B676" s="6" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C676" s="6" t="s">
         <v>1873</v>
       </c>
-      <c r="C676" s="6" t="s">
+      <c r="D676" s="6" t="s">
         <v>1874</v>
-      </c>
-      <c r="D676" s="6" t="s">
-        <v>1875</v>
       </c>
       <c r="E676" s="3">
         <v>1</v>
@@ -21986,13 +21978,13 @@
         <v>676</v>
       </c>
       <c r="B677" s="6" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C677" s="6" t="s">
         <v>1876</v>
       </c>
-      <c r="C677" s="6" t="s">
+      <c r="D677" s="6" t="s">
         <v>1877</v>
-      </c>
-      <c r="D677" s="6" t="s">
-        <v>1878</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -22003,13 +21995,13 @@
         <v>677</v>
       </c>
       <c r="B678" s="6" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C678" s="6" t="s">
         <v>1879</v>
       </c>
-      <c r="C678" s="6" t="s">
+      <c r="D678" s="6" t="s">
         <v>1880</v>
-      </c>
-      <c r="D678" s="6" t="s">
-        <v>1881</v>
       </c>
       <c r="E678" s="3">
         <v>1</v>
@@ -22020,13 +22012,13 @@
         <v>678</v>
       </c>
       <c r="B679" s="6" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C679" s="6" t="s">
         <v>1882</v>
       </c>
-      <c r="C679" s="6" t="s">
+      <c r="D679" s="6" t="s">
         <v>1883</v>
-      </c>
-      <c r="D679" s="6" t="s">
-        <v>1884</v>
       </c>
       <c r="E679" s="3">
         <v>1</v>
@@ -22054,13 +22046,13 @@
         <v>680</v>
       </c>
       <c r="B681" s="6" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C681" s="6" t="s">
         <v>1885</v>
       </c>
-      <c r="C681" s="6" t="s">
+      <c r="D681" s="6" t="s">
         <v>1886</v>
-      </c>
-      <c r="D681" s="6" t="s">
-        <v>1887</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -22105,13 +22097,13 @@
         <v>683</v>
       </c>
       <c r="B684" s="6" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C684" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C684" s="6" t="s">
+      <c r="D684" s="6" t="s">
         <v>1889</v>
-      </c>
-      <c r="D684" s="6" t="s">
-        <v>1890</v>
       </c>
       <c r="E684" s="3">
         <v>1</v>
@@ -22122,13 +22114,13 @@
         <v>684</v>
       </c>
       <c r="B685" s="6" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C685" s="6" t="s">
         <v>1891</v>
       </c>
-      <c r="C685" s="6" t="s">
+      <c r="D685" s="6" t="s">
         <v>1892</v>
-      </c>
-      <c r="D685" s="6" t="s">
-        <v>1893</v>
       </c>
       <c r="E685" s="3">
         <v>1</v>
@@ -22139,13 +22131,13 @@
         <v>685</v>
       </c>
       <c r="B686" s="6" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C686" s="6" t="s">
         <v>1894</v>
       </c>
-      <c r="C686" s="6" t="s">
+      <c r="D686" s="6" t="s">
         <v>1895</v>
-      </c>
-      <c r="D686" s="6" t="s">
-        <v>1896</v>
       </c>
       <c r="E686" s="3">
         <v>1</v>
@@ -22156,13 +22148,13 @@
         <v>686</v>
       </c>
       <c r="B687" s="6" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C687" s="6" t="s">
         <v>1897</v>
       </c>
-      <c r="C687" s="6" t="s">
+      <c r="D687" s="6" t="s">
         <v>1898</v>
-      </c>
-      <c r="D687" s="6" t="s">
-        <v>1899</v>
       </c>
       <c r="E687" s="3">
         <v>1</v>
@@ -22173,13 +22165,13 @@
         <v>687</v>
       </c>
       <c r="B688" s="6" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C688" s="6" t="s">
         <v>1900</v>
       </c>
-      <c r="C688" s="6" t="s">
+      <c r="D688" s="6" t="s">
         <v>1901</v>
-      </c>
-      <c r="D688" s="6" t="s">
-        <v>1902</v>
       </c>
       <c r="E688" s="3">
         <v>1</v>
@@ -22190,13 +22182,13 @@
         <v>688</v>
       </c>
       <c r="B689" s="6" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C689" s="6" t="s">
         <v>1903</v>
       </c>
-      <c r="C689" s="6" t="s">
+      <c r="D689" s="6" t="s">
         <v>1904</v>
-      </c>
-      <c r="D689" s="6" t="s">
-        <v>1905</v>
       </c>
       <c r="E689" s="3">
         <v>1</v>
@@ -22207,13 +22199,13 @@
         <v>689</v>
       </c>
       <c r="B690" s="6" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C690" s="6" t="s">
         <v>1906</v>
       </c>
-      <c r="C690" s="6" t="s">
+      <c r="D690" s="6" t="s">
         <v>1907</v>
-      </c>
-      <c r="D690" s="6" t="s">
-        <v>1908</v>
       </c>
       <c r="E690" s="3">
         <v>1</v>
@@ -22224,13 +22216,13 @@
         <v>690</v>
       </c>
       <c r="B691" s="6" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C691" s="6" t="s">
         <v>1909</v>
       </c>
-      <c r="C691" s="6" t="s">
+      <c r="D691" s="6" t="s">
         <v>1910</v>
-      </c>
-      <c r="D691" s="6" t="s">
-        <v>1911</v>
       </c>
       <c r="E691" s="3">
         <v>1</v>
@@ -22241,13 +22233,13 @@
         <v>691</v>
       </c>
       <c r="B692" s="6" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C692" s="6" t="s">
         <v>1912</v>
       </c>
-      <c r="C692" s="6" t="s">
+      <c r="D692" s="6" t="s">
         <v>1913</v>
-      </c>
-      <c r="D692" s="6" t="s">
-        <v>1914</v>
       </c>
       <c r="E692" s="3">
         <v>1</v>
@@ -22258,13 +22250,13 @@
         <v>692</v>
       </c>
       <c r="B693" s="6" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C693" s="6" t="s">
         <v>1915</v>
       </c>
-      <c r="C693" s="6" t="s">
+      <c r="D693" s="6" t="s">
         <v>1916</v>
-      </c>
-      <c r="D693" s="6" t="s">
-        <v>1917</v>
       </c>
       <c r="E693" s="3">
         <v>1</v>
@@ -22292,13 +22284,13 @@
         <v>694</v>
       </c>
       <c r="B695" s="6" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C695" s="6" t="s">
         <v>1918</v>
       </c>
-      <c r="C695" s="6" t="s">
+      <c r="D695" s="6" t="s">
         <v>1919</v>
-      </c>
-      <c r="D695" s="6" t="s">
-        <v>1920</v>
       </c>
       <c r="E695" s="3">
         <v>1</v>
@@ -22309,13 +22301,13 @@
         <v>695</v>
       </c>
       <c r="B696" s="6" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C696" s="6" t="s">
         <v>1921</v>
       </c>
-      <c r="C696" s="6" t="s">
+      <c r="D696" s="6" t="s">
         <v>1922</v>
-      </c>
-      <c r="D696" s="6" t="s">
-        <v>1923</v>
       </c>
       <c r="E696" s="3">
         <v>1</v>
@@ -22343,13 +22335,13 @@
         <v>697</v>
       </c>
       <c r="B698" s="6" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C698" s="6" t="s">
         <v>1924</v>
       </c>
-      <c r="C698" s="6" t="s">
+      <c r="D698" s="6" t="s">
         <v>1925</v>
-      </c>
-      <c r="D698" s="6" t="s">
-        <v>1926</v>
       </c>
       <c r="E698" s="3">
         <v>1</v>
@@ -22360,13 +22352,13 @@
         <v>698</v>
       </c>
       <c r="B699" s="6" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C699" s="6" t="s">
         <v>1927</v>
       </c>
-      <c r="C699" s="6" t="s">
+      <c r="D699" s="6" t="s">
         <v>1928</v>
-      </c>
-      <c r="D699" s="6" t="s">
-        <v>1929</v>
       </c>
       <c r="E699" s="3">
         <v>1</v>
@@ -22377,13 +22369,13 @@
         <v>699</v>
       </c>
       <c r="B700" s="6" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C700" s="6" t="s">
         <v>1930</v>
       </c>
-      <c r="C700" s="6" t="s">
+      <c r="D700" s="6" t="s">
         <v>1931</v>
-      </c>
-      <c r="D700" s="6" t="s">
-        <v>1932</v>
       </c>
       <c r="E700" s="3">
         <v>1</v>
@@ -22394,13 +22386,13 @@
         <v>700</v>
       </c>
       <c r="B701" s="6" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C701" s="6" t="s">
         <v>1933</v>
       </c>
-      <c r="C701" s="6" t="s">
+      <c r="D701" s="6" t="s">
         <v>1934</v>
-      </c>
-      <c r="D701" s="6" t="s">
-        <v>1935</v>
       </c>
       <c r="E701" s="3">
         <v>1</v>
@@ -22411,13 +22403,13 @@
         <v>701</v>
       </c>
       <c r="B702" s="6" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C702" s="6" t="s">
         <v>1936</v>
       </c>
-      <c r="C702" s="6" t="s">
+      <c r="D702" s="6" t="s">
         <v>1937</v>
-      </c>
-      <c r="D702" s="6" t="s">
-        <v>1938</v>
       </c>
       <c r="E702" s="3">
         <v>1</v>
@@ -22428,13 +22420,13 @@
         <v>702</v>
       </c>
       <c r="B703" s="6" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C703" s="6" t="s">
         <v>1939</v>
       </c>
-      <c r="C703" s="6" t="s">
+      <c r="D703" s="6" t="s">
         <v>1940</v>
-      </c>
-      <c r="D703" s="6" t="s">
-        <v>1941</v>
       </c>
       <c r="E703" s="3">
         <v>1</v>
@@ -22445,13 +22437,13 @@
         <v>703</v>
       </c>
       <c r="B704" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C704" s="6" t="s">
         <v>1942</v>
       </c>
-      <c r="C704" s="6" t="s">
+      <c r="D704" s="6" t="s">
         <v>1943</v>
-      </c>
-      <c r="D704" s="6" t="s">
-        <v>1944</v>
       </c>
       <c r="E704" s="3">
         <v>1</v>
@@ -22462,13 +22454,13 @@
         <v>704</v>
       </c>
       <c r="B705" s="6" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C705" s="6" t="s">
         <v>1945</v>
       </c>
-      <c r="C705" s="6" t="s">
+      <c r="D705" s="6" t="s">
         <v>1946</v>
-      </c>
-      <c r="D705" s="6" t="s">
-        <v>1947</v>
       </c>
       <c r="E705" s="3">
         <v>1</v>
@@ -22479,13 +22471,13 @@
         <v>705</v>
       </c>
       <c r="B706" s="6" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C706" s="6" t="s">
         <v>1948</v>
       </c>
-      <c r="C706" s="6" t="s">
+      <c r="D706" s="6" t="s">
         <v>1949</v>
-      </c>
-      <c r="D706" s="6" t="s">
-        <v>1950</v>
       </c>
       <c r="E706" s="3">
         <v>1</v>
@@ -22496,13 +22488,13 @@
         <v>706</v>
       </c>
       <c r="B707" s="6" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C707" s="6" t="s">
         <v>1951</v>
       </c>
-      <c r="C707" s="6" t="s">
+      <c r="D707" s="6" t="s">
         <v>1952</v>
-      </c>
-      <c r="D707" s="6" t="s">
-        <v>1953</v>
       </c>
       <c r="E707" s="3">
         <v>1</v>
@@ -22513,13 +22505,13 @@
         <v>707</v>
       </c>
       <c r="B708" s="6" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C708" s="6" t="s">
         <v>1695</v>
       </c>
-      <c r="C708" s="6" t="s">
+      <c r="D708" s="6" t="s">
         <v>1696</v>
-      </c>
-      <c r="D708" s="6" t="s">
-        <v>1697</v>
       </c>
       <c r="E708" s="3">
         <v>1</v>
@@ -22530,13 +22522,13 @@
         <v>708</v>
       </c>
       <c r="B709" s="6" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C709" s="6" t="s">
         <v>1954</v>
       </c>
-      <c r="C709" s="6" t="s">
+      <c r="D709" s="6" t="s">
         <v>1955</v>
-      </c>
-      <c r="D709" s="6" t="s">
-        <v>1956</v>
       </c>
       <c r="E709" s="3">
         <v>1</v>
@@ -22553,7 +22545,7 @@
         <v>859</v>
       </c>
       <c r="D710" s="6" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="E710" s="3">
         <v>1</v>
@@ -22564,13 +22556,13 @@
         <v>710</v>
       </c>
       <c r="B711" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C711" s="5" t="s">
         <v>1945</v>
       </c>
-      <c r="C711" s="5" t="s">
+      <c r="D711" s="5" t="s">
         <v>1946</v>
-      </c>
-      <c r="D711" s="5" t="s">
-        <v>1947</v>
       </c>
       <c r="E711" s="3">
         <v>1</v>
@@ -22581,13 +22573,13 @@
         <v>711</v>
       </c>
       <c r="B712" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C712" s="5" t="s">
         <v>1958</v>
       </c>
-      <c r="C712" s="5" t="s">
+      <c r="D712" s="5" t="s">
         <v>1959</v>
-      </c>
-      <c r="D712" s="5" t="s">
-        <v>1960</v>
       </c>
       <c r="E712" s="3">
         <v>1</v>
@@ -22598,13 +22590,13 @@
         <v>712</v>
       </c>
       <c r="B713" s="5" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C713" s="5" t="s">
         <v>1961</v>
       </c>
-      <c r="C713" s="5" t="s">
+      <c r="D713" s="5" t="s">
         <v>1962</v>
-      </c>
-      <c r="D713" s="5" t="s">
-        <v>1963</v>
       </c>
       <c r="E713" s="3">
         <v>1</v>
@@ -22621,7 +22613,7 @@
         <v>219</v>
       </c>
       <c r="D714" s="5" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E714" s="3">
         <v>1</v>
@@ -22632,13 +22624,13 @@
         <v>714</v>
       </c>
       <c r="B715" s="5" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C715" s="5" t="s">
         <v>396</v>
       </c>
       <c r="D715" s="5" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E715" s="3">
         <v>1</v>
@@ -22649,13 +22641,13 @@
         <v>715</v>
       </c>
       <c r="B716" s="5" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C716" s="5" t="s">
         <v>1967</v>
       </c>
-      <c r="C716" s="5" t="s">
+      <c r="D716" s="5" t="s">
         <v>1968</v>
-      </c>
-      <c r="D716" s="5" t="s">
-        <v>1969</v>
       </c>
       <c r="E716" s="3">
         <v>1</v>
@@ -22666,13 +22658,13 @@
         <v>716</v>
       </c>
       <c r="B717" s="5" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C717" s="5" t="s">
         <v>1970</v>
       </c>
-      <c r="C717" s="5" t="s">
+      <c r="D717" s="5" t="s">
         <v>1971</v>
-      </c>
-      <c r="D717" s="5" t="s">
-        <v>1972</v>
       </c>
       <c r="E717" s="3">
         <v>1</v>
@@ -22683,13 +22675,13 @@
         <v>717</v>
       </c>
       <c r="B718" s="5" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C718" s="5" t="s">
         <v>1973</v>
       </c>
-      <c r="C718" s="5" t="s">
+      <c r="D718" s="5" t="s">
         <v>1974</v>
-      </c>
-      <c r="D718" s="5" t="s">
-        <v>1975</v>
       </c>
       <c r="E718" s="3">
         <v>1</v>
@@ -22700,13 +22692,13 @@
         <v>718</v>
       </c>
       <c r="B719" s="5" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C719" s="5" t="s">
         <v>126</v>
       </c>
       <c r="D719" s="5" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="E719" s="3">
         <v>1</v>
@@ -22717,13 +22709,13 @@
         <v>719</v>
       </c>
       <c r="B720" s="5" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C720" s="5" t="s">
         <v>1978</v>
       </c>
-      <c r="C720" s="5" t="s">
+      <c r="D720" s="5" t="s">
         <v>1979</v>
-      </c>
-      <c r="D720" s="5" t="s">
-        <v>1980</v>
       </c>
       <c r="E720" s="3">
         <v>1</v>
@@ -22734,13 +22726,13 @@
         <v>720</v>
       </c>
       <c r="B721" s="5" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C721" s="5" t="s">
         <v>1981</v>
       </c>
-      <c r="C721" s="5" t="s">
+      <c r="D721" s="5" t="s">
         <v>1982</v>
-      </c>
-      <c r="D721" s="5" t="s">
-        <v>1983</v>
       </c>
       <c r="E721" s="3">
         <v>1</v>
@@ -22751,13 +22743,13 @@
         <v>721</v>
       </c>
       <c r="B722" s="5" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C722" s="5" t="s">
         <v>1984</v>
       </c>
-      <c r="C722" s="5" t="s">
+      <c r="D722" s="5" t="s">
         <v>1985</v>
-      </c>
-      <c r="D722" s="5" t="s">
-        <v>1986</v>
       </c>
       <c r="E722" s="3">
         <v>1</v>
@@ -22768,13 +22760,13 @@
         <v>722</v>
       </c>
       <c r="B723" s="5" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C723" s="5" t="s">
         <v>1987</v>
       </c>
-      <c r="C723" s="5" t="s">
+      <c r="D723" s="5" t="s">
         <v>1988</v>
-      </c>
-      <c r="D723" s="5" t="s">
-        <v>1989</v>
       </c>
       <c r="E723" s="3">
         <v>1</v>
@@ -22785,13 +22777,13 @@
         <v>723</v>
       </c>
       <c r="B724" s="5" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C724" s="5" t="s">
         <v>1990</v>
       </c>
-      <c r="C724" s="5" t="s">
+      <c r="D724" s="5" t="s">
         <v>1991</v>
-      </c>
-      <c r="D724" s="5" t="s">
-        <v>1992</v>
       </c>
       <c r="E724" s="3">
         <v>1</v>
@@ -22802,13 +22794,13 @@
         <v>724</v>
       </c>
       <c r="B725" s="5" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C725" s="5" t="s">
         <v>1993</v>
       </c>
-      <c r="C725" s="5" t="s">
+      <c r="D725" s="5" t="s">
         <v>1994</v>
-      </c>
-      <c r="D725" s="5" t="s">
-        <v>1995</v>
       </c>
       <c r="E725" s="3">
         <v>1</v>
@@ -22819,13 +22811,13 @@
         <v>725</v>
       </c>
       <c r="B726" s="5" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C726" s="5" t="s">
         <v>1996</v>
       </c>
-      <c r="C726" s="5" t="s">
+      <c r="D726" s="5" t="s">
         <v>1997</v>
-      </c>
-      <c r="D726" s="5" t="s">
-        <v>1998</v>
       </c>
       <c r="E726" s="3">
         <v>1</v>
@@ -22836,13 +22828,13 @@
         <v>726</v>
       </c>
       <c r="B727" s="5" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C727" s="5" t="s">
         <v>1999</v>
       </c>
-      <c r="C727" s="5" t="s">
+      <c r="D727" s="5" t="s">
         <v>2000</v>
-      </c>
-      <c r="D727" s="5" t="s">
-        <v>2001</v>
       </c>
       <c r="E727" s="3">
         <v>1</v>
@@ -22853,13 +22845,13 @@
         <v>727</v>
       </c>
       <c r="B728" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C728" s="5" t="s">
         <v>2002</v>
       </c>
-      <c r="C728" s="5" t="s">
+      <c r="D728" s="5" t="s">
         <v>2003</v>
-      </c>
-      <c r="D728" s="5" t="s">
-        <v>2004</v>
       </c>
       <c r="E728" s="3">
         <v>1</v>
@@ -22870,13 +22862,13 @@
         <v>728</v>
       </c>
       <c r="B729" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C729" s="5" t="s">
         <v>2005</v>
       </c>
-      <c r="C729" s="5" t="s">
+      <c r="D729" s="5" t="s">
         <v>2006</v>
-      </c>
-      <c r="D729" s="5" t="s">
-        <v>2007</v>
       </c>
       <c r="E729" s="3">
         <v>1</v>
@@ -22887,13 +22879,13 @@
         <v>729</v>
       </c>
       <c r="B730" s="5" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C730" s="5" t="s">
         <v>2008</v>
       </c>
-      <c r="C730" s="5" t="s">
+      <c r="D730" s="5" t="s">
         <v>2009</v>
-      </c>
-      <c r="D730" s="5" t="s">
-        <v>2010</v>
       </c>
       <c r="E730" s="3">
         <v>1</v>
@@ -22904,13 +22896,13 @@
         <v>730</v>
       </c>
       <c r="B731" s="5" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C731" s="5" t="s">
         <v>2011</v>
       </c>
-      <c r="C731" s="5" t="s">
+      <c r="D731" s="5" t="s">
         <v>2012</v>
-      </c>
-      <c r="D731" s="5" t="s">
-        <v>2013</v>
       </c>
       <c r="E731" s="3">
         <v>1</v>
@@ -22921,13 +22913,13 @@
         <v>731</v>
       </c>
       <c r="B732" s="5" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C732" s="5" t="s">
         <v>2014</v>
       </c>
-      <c r="C732" s="5" t="s">
+      <c r="D732" s="5" t="s">
         <v>2015</v>
-      </c>
-      <c r="D732" s="5" t="s">
-        <v>2016</v>
       </c>
       <c r="E732" s="3">
         <v>1</v>
@@ -22938,13 +22930,13 @@
         <v>732</v>
       </c>
       <c r="B733" s="5" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C733" s="5" t="s">
         <v>2017</v>
       </c>
-      <c r="C733" s="5" t="s">
+      <c r="D733" s="5" t="s">
         <v>2018</v>
-      </c>
-      <c r="D733" s="5" t="s">
-        <v>2019</v>
       </c>
       <c r="E733" s="3">
         <v>1</v>
@@ -22955,13 +22947,13 @@
         <v>733</v>
       </c>
       <c r="B734" s="5" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C734" s="5" t="s">
         <v>2020</v>
       </c>
-      <c r="C734" s="5" t="s">
+      <c r="D734" s="5" t="s">
         <v>2021</v>
-      </c>
-      <c r="D734" s="5" t="s">
-        <v>2022</v>
       </c>
       <c r="E734" s="3">
         <v>1</v>
@@ -22989,13 +22981,13 @@
         <v>735</v>
       </c>
       <c r="B736" s="5" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C736" s="5" t="s">
         <v>2023</v>
       </c>
-      <c r="C736" s="5" t="s">
+      <c r="D736" s="5" t="s">
         <v>2024</v>
-      </c>
-      <c r="D736" s="5" t="s">
-        <v>2025</v>
       </c>
       <c r="E736" s="3">
         <v>1</v>
@@ -23006,13 +22998,13 @@
         <v>736</v>
       </c>
       <c r="B737" s="5" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C737" s="5" t="s">
         <v>2026</v>
       </c>
-      <c r="C737" s="5" t="s">
+      <c r="D737" s="5" t="s">
         <v>2027</v>
-      </c>
-      <c r="D737" s="5" t="s">
-        <v>2028</v>
       </c>
       <c r="E737" s="3">
         <v>1</v>
@@ -23023,13 +23015,13 @@
         <v>737</v>
       </c>
       <c r="B738" s="5" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C738" s="5" t="s">
         <v>2029</v>
       </c>
-      <c r="C738" s="5" t="s">
+      <c r="D738" s="5" t="s">
         <v>2030</v>
-      </c>
-      <c r="D738" s="5" t="s">
-        <v>2031</v>
       </c>
       <c r="E738" s="3">
         <v>1</v>
@@ -23040,13 +23032,13 @@
         <v>738</v>
       </c>
       <c r="B739" s="5" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C739" s="5" t="s">
         <v>2032</v>
       </c>
-      <c r="C739" s="5" t="s">
+      <c r="D739" s="5" t="s">
         <v>2033</v>
-      </c>
-      <c r="D739" s="5" t="s">
-        <v>2034</v>
       </c>
       <c r="E739" s="3">
         <v>1</v>
@@ -23057,13 +23049,13 @@
         <v>739</v>
       </c>
       <c r="B740" s="5" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C740" s="5" t="s">
         <v>2035</v>
       </c>
-      <c r="C740" s="5" t="s">
+      <c r="D740" s="5" t="s">
         <v>2036</v>
-      </c>
-      <c r="D740" s="5" t="s">
-        <v>2037</v>
       </c>
       <c r="E740" s="3">
         <v>1</v>
@@ -23074,13 +23066,13 @@
         <v>740</v>
       </c>
       <c r="B741" s="5" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C741" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C741" s="5" t="s">
+      <c r="D741" s="5" t="s">
         <v>2039</v>
-      </c>
-      <c r="D741" s="5" t="s">
-        <v>2040</v>
       </c>
       <c r="E741" s="3">
         <v>1</v>
@@ -23091,13 +23083,13 @@
         <v>741</v>
       </c>
       <c r="B742" s="5" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C742" s="5" t="s">
         <v>2041</v>
       </c>
-      <c r="C742" s="5" t="s">
+      <c r="D742" s="5" t="s">
         <v>2042</v>
-      </c>
-      <c r="D742" s="5" t="s">
-        <v>2043</v>
       </c>
       <c r="E742" s="3">
         <v>1</v>
@@ -23125,13 +23117,13 @@
         <v>743</v>
       </c>
       <c r="B744" s="5" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C744" s="5" t="s">
         <v>2044</v>
       </c>
-      <c r="C744" s="5" t="s">
+      <c r="D744" s="5" t="s">
         <v>2045</v>
-      </c>
-      <c r="D744" s="5" t="s">
-        <v>2046</v>
       </c>
       <c r="E744" s="3">
         <v>1</v>
@@ -23142,13 +23134,13 @@
         <v>744</v>
       </c>
       <c r="B745" s="5" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C745" s="5" t="s">
         <v>2047</v>
       </c>
-      <c r="C745" s="5" t="s">
+      <c r="D745" s="5" t="s">
         <v>2048</v>
-      </c>
-      <c r="D745" s="5" t="s">
-        <v>2049</v>
       </c>
       <c r="E745" s="3">
         <v>1</v>
@@ -23159,13 +23151,13 @@
         <v>745</v>
       </c>
       <c r="B746" s="5" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C746" s="5" t="s">
         <v>2050</v>
       </c>
-      <c r="C746" s="5" t="s">
+      <c r="D746" s="5" t="s">
         <v>2051</v>
-      </c>
-      <c r="D746" s="5" t="s">
-        <v>2052</v>
       </c>
       <c r="E746" s="3">
         <v>1</v>
@@ -23176,13 +23168,13 @@
         <v>746</v>
       </c>
       <c r="B747" s="5" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C747" s="5" t="s">
         <v>2053</v>
       </c>
-      <c r="C747" s="5" t="s">
+      <c r="D747" s="5" t="s">
         <v>2054</v>
-      </c>
-      <c r="D747" s="5" t="s">
-        <v>2055</v>
       </c>
       <c r="E747" s="3">
         <v>1</v>
@@ -23193,13 +23185,13 @@
         <v>747</v>
       </c>
       <c r="B748" s="5" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C748" s="5" t="s">
         <v>2056</v>
       </c>
-      <c r="C748" s="5" t="s">
+      <c r="D748" s="5" t="s">
         <v>2057</v>
-      </c>
-      <c r="D748" s="5" t="s">
-        <v>2058</v>
       </c>
       <c r="E748" s="3">
         <v>1</v>
@@ -23210,13 +23202,13 @@
         <v>748</v>
       </c>
       <c r="B749" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C749" s="5" t="s">
         <v>2059</v>
       </c>
-      <c r="C749" s="5" t="s">
+      <c r="D749" s="5" t="s">
         <v>2060</v>
-      </c>
-      <c r="D749" s="5" t="s">
-        <v>2061</v>
       </c>
       <c r="E749" s="3">
         <v>1</v>
@@ -23227,13 +23219,13 @@
         <v>749</v>
       </c>
       <c r="B750" s="5" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C750" s="5" t="s">
         <v>2062</v>
       </c>
-      <c r="C750" s="5" t="s">
+      <c r="D750" s="5" t="s">
         <v>2063</v>
-      </c>
-      <c r="D750" s="5" t="s">
-        <v>2064</v>
       </c>
       <c r="E750" s="3">
         <v>1</v>
@@ -23244,13 +23236,13 @@
         <v>750</v>
       </c>
       <c r="B751" s="5" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C751" s="5" t="s">
         <v>2065</v>
       </c>
-      <c r="C751" s="5" t="s">
+      <c r="D751" s="5" t="s">
         <v>2066</v>
-      </c>
-      <c r="D751" s="5" t="s">
-        <v>2067</v>
       </c>
       <c r="E751" s="3">
         <v>1</v>
@@ -23261,13 +23253,13 @@
         <v>751</v>
       </c>
       <c r="B752" s="5" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C752" s="5" t="s">
         <v>2068</v>
       </c>
-      <c r="C752" s="5" t="s">
+      <c r="D752" s="5" t="s">
         <v>2069</v>
-      </c>
-      <c r="D752" s="5" t="s">
-        <v>2070</v>
       </c>
       <c r="E752" s="3">
         <v>1</v>
@@ -23278,13 +23270,13 @@
         <v>752</v>
       </c>
       <c r="B753" s="5" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C753" s="5" t="s">
         <v>2071</v>
       </c>
-      <c r="C753" s="5" t="s">
+      <c r="D753" s="5" t="s">
         <v>2072</v>
-      </c>
-      <c r="D753" s="5" t="s">
-        <v>2073</v>
       </c>
       <c r="E753" s="3">
         <v>1</v>
@@ -23295,13 +23287,13 @@
         <v>753</v>
       </c>
       <c r="B754" s="5" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C754" s="5" t="s">
         <v>2074</v>
       </c>
-      <c r="C754" s="5" t="s">
+      <c r="D754" s="5" t="s">
         <v>2075</v>
-      </c>
-      <c r="D754" s="5" t="s">
-        <v>2076</v>
       </c>
       <c r="E754" s="3">
         <v>1</v>
@@ -23312,13 +23304,13 @@
         <v>754</v>
       </c>
       <c r="B755" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C755" s="5" t="s">
         <v>2077</v>
       </c>
-      <c r="C755" s="5" t="s">
+      <c r="D755" s="5" t="s">
         <v>2078</v>
-      </c>
-      <c r="D755" s="5" t="s">
-        <v>2079</v>
       </c>
       <c r="E755" s="3">
         <v>1</v>
@@ -23329,13 +23321,13 @@
         <v>755</v>
       </c>
       <c r="B756" s="5" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C756" s="5" t="s">
         <v>2080</v>
       </c>
-      <c r="C756" s="5" t="s">
+      <c r="D756" s="5" t="s">
         <v>2081</v>
-      </c>
-      <c r="D756" s="5" t="s">
-        <v>2082</v>
       </c>
       <c r="E756" s="3">
         <v>1</v>
@@ -23346,13 +23338,13 @@
         <v>756</v>
       </c>
       <c r="B757" s="5" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C757" s="5" t="s">
         <v>2083</v>
       </c>
-      <c r="C757" s="5" t="s">
+      <c r="D757" s="5" t="s">
         <v>2084</v>
-      </c>
-      <c r="D757" s="5" t="s">
-        <v>2085</v>
       </c>
       <c r="E757" s="3">
         <v>1</v>
@@ -23363,13 +23355,13 @@
         <v>757</v>
       </c>
       <c r="B758" s="5" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C758" s="5" t="s">
         <v>2086</v>
       </c>
-      <c r="C758" s="5" t="s">
+      <c r="D758" s="5" t="s">
         <v>2087</v>
-      </c>
-      <c r="D758" s="5" t="s">
-        <v>2088</v>
       </c>
       <c r="E758" s="3">
         <v>1</v>
@@ -23380,13 +23372,13 @@
         <v>758</v>
       </c>
       <c r="B759" s="5" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C759" s="5" t="s">
         <v>2089</v>
       </c>
-      <c r="C759" s="5" t="s">
+      <c r="D759" s="5" t="s">
         <v>2090</v>
-      </c>
-      <c r="D759" s="5" t="s">
-        <v>2091</v>
       </c>
       <c r="E759" s="3">
         <v>1</v>
@@ -23397,13 +23389,13 @@
         <v>759</v>
       </c>
       <c r="B760" s="5" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C760" s="5" t="s">
         <v>2092</v>
       </c>
-      <c r="C760" s="5" t="s">
+      <c r="D760" s="5" t="s">
         <v>2093</v>
-      </c>
-      <c r="D760" s="5" t="s">
-        <v>2094</v>
       </c>
       <c r="E760" s="3">
         <v>1</v>
@@ -23431,13 +23423,13 @@
         <v>761</v>
       </c>
       <c r="B762" s="5" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C762" s="5" t="s">
         <v>2095</v>
       </c>
-      <c r="C762" s="5" t="s">
+      <c r="D762" s="5" t="s">
         <v>2096</v>
-      </c>
-      <c r="D762" s="5" t="s">
-        <v>2097</v>
       </c>
       <c r="E762" s="3">
         <v>1</v>
@@ -23448,13 +23440,13 @@
         <v>762</v>
       </c>
       <c r="B763" s="5" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C763" s="5" t="s">
         <v>2098</v>
       </c>
-      <c r="C763" s="5" t="s">
+      <c r="D763" s="5" t="s">
         <v>2099</v>
-      </c>
-      <c r="D763" s="5" t="s">
-        <v>2100</v>
       </c>
       <c r="E763" s="3">
         <v>1</v>
@@ -23465,13 +23457,13 @@
         <v>763</v>
       </c>
       <c r="B764" s="5" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C764" s="5" t="s">
         <v>2101</v>
       </c>
-      <c r="C764" s="5" t="s">
+      <c r="D764" s="5" t="s">
         <v>2102</v>
-      </c>
-      <c r="D764" s="5" t="s">
-        <v>2103</v>
       </c>
       <c r="E764" s="3">
         <v>1</v>
@@ -23482,13 +23474,13 @@
         <v>764</v>
       </c>
       <c r="B765" s="5" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C765" s="5" t="s">
         <v>2104</v>
       </c>
-      <c r="C765" s="5" t="s">
+      <c r="D765" s="5" t="s">
         <v>2105</v>
-      </c>
-      <c r="D765" s="5" t="s">
-        <v>2106</v>
       </c>
       <c r="E765" s="3">
         <v>1</v>
@@ -23499,13 +23491,13 @@
         <v>765</v>
       </c>
       <c r="B766" s="5" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C766" s="5" t="s">
         <v>2107</v>
       </c>
-      <c r="C766" s="5" t="s">
+      <c r="D766" s="5" t="s">
         <v>2108</v>
-      </c>
-      <c r="D766" s="5" t="s">
-        <v>2109</v>
       </c>
       <c r="E766" s="3">
         <v>1</v>
@@ -23516,13 +23508,13 @@
         <v>766</v>
       </c>
       <c r="B767" s="5" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C767" s="5" t="s">
         <v>2110</v>
       </c>
-      <c r="C767" s="5" t="s">
+      <c r="D767" s="5" t="s">
         <v>2111</v>
-      </c>
-      <c r="D767" s="5" t="s">
-        <v>2112</v>
       </c>
       <c r="E767" s="3">
         <v>1</v>
@@ -23567,13 +23559,13 @@
         <v>769</v>
       </c>
       <c r="B770" s="5" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C770" s="5" t="s">
         <v>2113</v>
       </c>
-      <c r="C770" s="5" t="s">
+      <c r="D770" s="5" t="s">
         <v>2114</v>
-      </c>
-      <c r="D770" s="5" t="s">
-        <v>2115</v>
       </c>
       <c r="E770" s="3">
         <v>1</v>
@@ -23584,13 +23576,11 @@
         <v>770</v>
       </c>
       <c r="B771" s="5" t="s">
-        <v>2113</v>
-      </c>
-      <c r="C771" s="5" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C771" s="5"/>
+      <c r="D771" s="5" t="s">
         <v>2116</v>
-      </c>
-      <c r="D771" s="5" t="s">
-        <v>2117</v>
       </c>
       <c r="E771" s="3">
         <v>1</v>
@@ -23607,7 +23597,7 @@
         <v>1446</v>
       </c>
       <c r="D772" s="5" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="E772" s="3">
         <v>1</v>
@@ -23618,13 +23608,13 @@
         <v>772</v>
       </c>
       <c r="B773" s="5" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C773" s="5" t="s">
         <v>2119</v>
       </c>
-      <c r="C773" s="5" t="s">
+      <c r="D773" s="5" t="s">
         <v>2120</v>
-      </c>
-      <c r="D773" s="5" t="s">
-        <v>2121</v>
       </c>
       <c r="E773" s="3">
         <v>1</v>
@@ -23635,13 +23625,13 @@
         <v>773</v>
       </c>
       <c r="B774" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C774" s="5" t="s">
         <v>2122</v>
       </c>
-      <c r="C774" s="5" t="s">
+      <c r="D774" s="5" t="s">
         <v>2123</v>
-      </c>
-      <c r="D774" s="5" t="s">
-        <v>2124</v>
       </c>
       <c r="E774" s="3">
         <v>1</v>
@@ -23652,13 +23642,13 @@
         <v>774</v>
       </c>
       <c r="B775" s="5" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C775" s="5" t="s">
         <v>2125</v>
       </c>
-      <c r="C775" s="5" t="s">
+      <c r="D775" s="5" t="s">
         <v>2126</v>
-      </c>
-      <c r="D775" s="5" t="s">
-        <v>2127</v>
       </c>
       <c r="E775" s="3">
         <v>1</v>
@@ -23675,7 +23665,7 @@
         <v>1128</v>
       </c>
       <c r="D776" s="5" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="E776" s="3">
         <v>1</v>
@@ -23686,13 +23676,13 @@
         <v>776</v>
       </c>
       <c r="B777" s="5" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C777" s="5" t="s">
         <v>2129</v>
       </c>
-      <c r="C777" s="5" t="s">
+      <c r="D777" s="5" t="s">
         <v>2130</v>
-      </c>
-      <c r="D777" s="5" t="s">
-        <v>2131</v>
       </c>
       <c r="E777" s="3">
         <v>1</v>
@@ -23709,7 +23699,7 @@
         <v>225</v>
       </c>
       <c r="D778" s="5" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="E778" s="3">
         <v>1</v>
@@ -23720,13 +23710,13 @@
         <v>778</v>
       </c>
       <c r="B779" s="5" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C779" s="5" t="s">
         <v>2133</v>
       </c>
-      <c r="C779" s="5" t="s">
+      <c r="D779" s="5" t="s">
         <v>2134</v>
-      </c>
-      <c r="D779" s="5" t="s">
-        <v>2135</v>
       </c>
       <c r="E779" s="3">
         <v>1</v>
@@ -23737,13 +23727,13 @@
         <v>779</v>
       </c>
       <c r="B780" s="5" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C780" s="5" t="s">
         <v>2136</v>
       </c>
-      <c r="C780" s="5" t="s">
+      <c r="D780" s="5" t="s">
         <v>2137</v>
-      </c>
-      <c r="D780" s="5" t="s">
-        <v>2138</v>
       </c>
       <c r="E780" s="3">
         <v>1</v>
@@ -23771,13 +23761,13 @@
         <v>781</v>
       </c>
       <c r="B782" s="5" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C782" s="5" t="s">
         <v>2139</v>
       </c>
-      <c r="C782" s="5" t="s">
+      <c r="D782" s="5" t="s">
         <v>2140</v>
-      </c>
-      <c r="D782" s="5" t="s">
-        <v>2141</v>
       </c>
       <c r="E782" s="3">
         <v>1</v>
@@ -23794,7 +23784,7 @@
         <v>1226</v>
       </c>
       <c r="D783" s="5" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="E783" s="3">
         <v>1</v>
@@ -23805,13 +23795,13 @@
         <v>783</v>
       </c>
       <c r="B784" s="5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C784" s="5" t="s">
         <v>2143</v>
       </c>
-      <c r="C784" s="5" t="s">
+      <c r="D784" s="5" t="s">
         <v>2144</v>
-      </c>
-      <c r="D784" s="5" t="s">
-        <v>2145</v>
       </c>
       <c r="E784" s="3">
         <v>1</v>
@@ -23822,13 +23812,13 @@
         <v>784</v>
       </c>
       <c r="B785" s="5" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C785" s="5" t="s">
         <v>2146</v>
       </c>
-      <c r="C785" s="5" t="s">
+      <c r="D785" s="5" t="s">
         <v>2147</v>
-      </c>
-      <c r="D785" s="5" t="s">
-        <v>2148</v>
       </c>
       <c r="E785" s="3">
         <v>1</v>
@@ -23839,13 +23829,13 @@
         <v>785</v>
       </c>
       <c r="B786" s="5" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C786" s="5" t="s">
         <v>2149</v>
       </c>
-      <c r="C786" s="5" t="s">
+      <c r="D786" s="5" t="s">
         <v>2150</v>
-      </c>
-      <c r="D786" s="5" t="s">
-        <v>2151</v>
       </c>
       <c r="E786" s="3">
         <v>1</v>
@@ -23856,13 +23846,13 @@
         <v>786</v>
       </c>
       <c r="B787" s="5" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C787" s="5" t="s">
         <v>2152</v>
       </c>
-      <c r="C787" s="5" t="s">
+      <c r="D787" s="5" t="s">
         <v>2153</v>
-      </c>
-      <c r="D787" s="5" t="s">
-        <v>2154</v>
       </c>
       <c r="E787" s="3">
         <v>1</v>
@@ -23873,13 +23863,13 @@
         <v>787</v>
       </c>
       <c r="B788" s="5" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C788" s="5" t="s">
         <v>2155</v>
       </c>
-      <c r="C788" s="5" t="s">
+      <c r="D788" s="5" t="s">
         <v>2156</v>
-      </c>
-      <c r="D788" s="5" t="s">
-        <v>2157</v>
       </c>
       <c r="E788" s="3">
         <v>1</v>
@@ -23890,13 +23880,13 @@
         <v>788</v>
       </c>
       <c r="B789" s="5" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C789" s="5" t="s">
         <v>2158</v>
       </c>
-      <c r="C789" s="5" t="s">
+      <c r="D789" s="5" t="s">
         <v>2159</v>
-      </c>
-      <c r="D789" s="5" t="s">
-        <v>2160</v>
       </c>
       <c r="E789" s="3">
         <v>1</v>
@@ -23907,13 +23897,13 @@
         <v>789</v>
       </c>
       <c r="B790" s="5" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C790" s="5" t="s">
         <v>2161</v>
       </c>
-      <c r="C790" s="5" t="s">
+      <c r="D790" s="5" t="s">
         <v>2162</v>
-      </c>
-      <c r="D790" s="5" t="s">
-        <v>2163</v>
       </c>
       <c r="E790" s="3">
         <v>1</v>
@@ -23924,13 +23914,13 @@
         <v>790</v>
       </c>
       <c r="B791" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C791" s="5" t="s">
         <v>2164</v>
       </c>
-      <c r="C791" s="5" t="s">
+      <c r="D791" s="5" t="s">
         <v>2165</v>
-      </c>
-      <c r="D791" s="5" t="s">
-        <v>2166</v>
       </c>
       <c r="E791" s="3">
         <v>1</v>
@@ -23941,13 +23931,13 @@
         <v>791</v>
       </c>
       <c r="B792" s="5" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C792" s="5" t="s">
         <v>2167</v>
       </c>
-      <c r="C792" s="5" t="s">
+      <c r="D792" s="5" t="s">
         <v>2168</v>
-      </c>
-      <c r="D792" s="5" t="s">
-        <v>2169</v>
       </c>
       <c r="E792" s="3">
         <v>1</v>
@@ -23958,13 +23948,13 @@
         <v>792</v>
       </c>
       <c r="B793" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C793" s="5" t="s">
         <v>2164</v>
       </c>
-      <c r="C793" s="5" t="s">
-        <v>2165</v>
-      </c>
       <c r="D793" s="5" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="E793" s="3">
         <v>1</v>
@@ -23975,13 +23965,13 @@
         <v>793</v>
       </c>
       <c r="B794" s="5" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C794" s="5" t="s">
         <v>2171</v>
       </c>
-      <c r="C794" s="5" t="s">
+      <c r="D794" s="5" t="s">
         <v>2172</v>
-      </c>
-      <c r="D794" s="5" t="s">
-        <v>2173</v>
       </c>
       <c r="E794" s="3">
         <v>1</v>
@@ -23992,13 +23982,13 @@
         <v>794</v>
       </c>
       <c r="B795" s="5" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C795" s="5" t="s">
         <v>2174</v>
       </c>
-      <c r="C795" s="5" t="s">
+      <c r="D795" s="5" t="s">
         <v>2175</v>
-      </c>
-      <c r="D795" s="5" t="s">
-        <v>2176</v>
       </c>
       <c r="E795" s="3">
         <v>1</v>
@@ -24009,13 +23999,13 @@
         <v>795</v>
       </c>
       <c r="B796" s="5" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C796" s="5" t="s">
         <v>2177</v>
       </c>
-      <c r="C796" s="5" t="s">
+      <c r="D796" s="5" t="s">
         <v>2178</v>
-      </c>
-      <c r="D796" s="5" t="s">
-        <v>2179</v>
       </c>
       <c r="E796" s="3">
         <v>1</v>
@@ -24060,13 +24050,13 @@
         <v>798</v>
       </c>
       <c r="B799" s="5" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C799" s="5" t="s">
         <v>2180</v>
       </c>
-      <c r="C799" s="5" t="s">
+      <c r="D799" s="5" t="s">
         <v>2181</v>
-      </c>
-      <c r="D799" s="5" t="s">
-        <v>2182</v>
       </c>
       <c r="E799" s="3">
         <v>1</v>
@@ -24077,13 +24067,13 @@
         <v>799</v>
       </c>
       <c r="B800" s="5" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C800" s="5" t="s">
         <v>2183</v>
       </c>
-      <c r="C800" s="5" t="s">
+      <c r="D800" s="5" t="s">
         <v>2184</v>
-      </c>
-      <c r="D800" s="5" t="s">
-        <v>2185</v>
       </c>
       <c r="E800" s="3">
         <v>1</v>
@@ -24094,13 +24084,13 @@
         <v>800</v>
       </c>
       <c r="B801" s="5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C801" s="5" t="s">
         <v>2186</v>
       </c>
-      <c r="C801" s="5" t="s">
+      <c r="D801" s="5" t="s">
         <v>2187</v>
-      </c>
-      <c r="D801" s="5" t="s">
-        <v>2188</v>
       </c>
       <c r="E801" s="3">
         <v>1</v>
@@ -24111,13 +24101,13 @@
         <v>801</v>
       </c>
       <c r="B802" s="5" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C802" s="5" t="s">
         <v>2189</v>
       </c>
-      <c r="C802" s="5" t="s">
+      <c r="D802" s="5" t="s">
         <v>2190</v>
-      </c>
-      <c r="D802" s="5" t="s">
-        <v>2191</v>
       </c>
       <c r="E802" s="3">
         <v>1</v>
@@ -24145,13 +24135,13 @@
         <v>803</v>
       </c>
       <c r="B804" s="5" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C804" s="5" t="s">
         <v>2192</v>
       </c>
-      <c r="C804" s="5" t="s">
+      <c r="D804" s="5" t="s">
         <v>2193</v>
-      </c>
-      <c r="D804" s="5" t="s">
-        <v>2194</v>
       </c>
       <c r="E804" s="3">
         <v>1</v>
@@ -24162,13 +24152,13 @@
         <v>804</v>
       </c>
       <c r="B805" s="5" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C805" s="5" t="s">
         <v>2195</v>
       </c>
-      <c r="C805" s="5" t="s">
+      <c r="D805" s="5" t="s">
         <v>2196</v>
-      </c>
-      <c r="D805" s="5" t="s">
-        <v>2197</v>
       </c>
       <c r="E805" s="3">
         <v>1</v>
@@ -24179,13 +24169,13 @@
         <v>805</v>
       </c>
       <c r="B806" s="5" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C806" s="5" t="s">
         <v>2198</v>
       </c>
-      <c r="C806" s="5" t="s">
+      <c r="D806" s="5" t="s">
         <v>2199</v>
-      </c>
-      <c r="D806" s="5" t="s">
-        <v>2200</v>
       </c>
       <c r="E806" s="3">
         <v>1</v>
@@ -24196,13 +24186,13 @@
         <v>806</v>
       </c>
       <c r="B807" s="5" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C807" s="5" t="s">
         <v>2201</v>
       </c>
-      <c r="C807" s="5" t="s">
+      <c r="D807" s="5" t="s">
         <v>2202</v>
-      </c>
-      <c r="D807" s="5" t="s">
-        <v>2203</v>
       </c>
       <c r="E807" s="3">
         <v>1</v>
@@ -24213,13 +24203,13 @@
         <v>807</v>
       </c>
       <c r="B808" s="5" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C808" s="5" t="s">
         <v>2204</v>
       </c>
-      <c r="C808" s="5" t="s">
+      <c r="D808" s="5" t="s">
         <v>2205</v>
-      </c>
-      <c r="D808" s="5" t="s">
-        <v>2206</v>
       </c>
       <c r="E808" s="3">
         <v>1</v>
@@ -24230,13 +24220,13 @@
         <v>808</v>
       </c>
       <c r="B809" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C809" s="5" t="s">
         <v>2207</v>
       </c>
-      <c r="C809" s="5" t="s">
+      <c r="D809" s="5" t="s">
         <v>2208</v>
-      </c>
-      <c r="D809" s="5" t="s">
-        <v>2209</v>
       </c>
       <c r="E809" s="3">
         <v>1</v>
@@ -24247,13 +24237,13 @@
         <v>809</v>
       </c>
       <c r="B810" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C810" s="5" t="s">
         <v>2210</v>
       </c>
-      <c r="C810" s="5" t="s">
+      <c r="D810" s="5" t="s">
         <v>2211</v>
-      </c>
-      <c r="D810" s="5" t="s">
-        <v>2212</v>
       </c>
       <c r="E810" s="3">
         <v>1</v>
@@ -24264,13 +24254,13 @@
         <v>810</v>
       </c>
       <c r="B811" s="5" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C811" s="5" t="s">
         <v>2213</v>
       </c>
-      <c r="C811" s="5" t="s">
+      <c r="D811" s="5" t="s">
         <v>2214</v>
-      </c>
-      <c r="D811" s="5" t="s">
-        <v>2215</v>
       </c>
       <c r="E811" s="3">
         <v>1</v>
@@ -24281,13 +24271,13 @@
         <v>811</v>
       </c>
       <c r="B812" s="5" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C812" s="5" t="s">
         <v>2216</v>
       </c>
-      <c r="C812" s="5" t="s">
+      <c r="D812" s="5" t="s">
         <v>2217</v>
-      </c>
-      <c r="D812" s="5" t="s">
-        <v>2218</v>
       </c>
       <c r="E812" s="3">
         <v>1</v>
@@ -24298,13 +24288,13 @@
         <v>812</v>
       </c>
       <c r="B813" s="5" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C813" s="5" t="s">
         <v>2219</v>
       </c>
-      <c r="C813" s="5" t="s">
+      <c r="D813" s="5" t="s">
         <v>2220</v>
-      </c>
-      <c r="D813" s="5" t="s">
-        <v>2221</v>
       </c>
       <c r="E813" s="3">
         <v>1</v>
@@ -24315,13 +24305,13 @@
         <v>813</v>
       </c>
       <c r="B814" s="5" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C814" s="5" t="s">
         <v>2222</v>
       </c>
-      <c r="C814" s="5" t="s">
+      <c r="D814" s="5" t="s">
         <v>2223</v>
-      </c>
-      <c r="D814" s="5" t="s">
-        <v>2224</v>
       </c>
       <c r="E814" s="3">
         <v>1</v>
@@ -24332,13 +24322,13 @@
         <v>814</v>
       </c>
       <c r="B815" s="5" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C815" s="5" t="s">
         <v>2225</v>
       </c>
-      <c r="C815" s="5" t="s">
+      <c r="D815" s="5" t="s">
         <v>2226</v>
-      </c>
-      <c r="D815" s="5" t="s">
-        <v>2227</v>
       </c>
       <c r="E815" s="3">
         <v>1</v>
@@ -24349,13 +24339,13 @@
         <v>815</v>
       </c>
       <c r="B816" s="5" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C816" s="5" t="s">
         <v>2228</v>
       </c>
-      <c r="C816" s="5" t="s">
+      <c r="D816" s="5" t="s">
         <v>2229</v>
-      </c>
-      <c r="D816" s="5" t="s">
-        <v>2230</v>
       </c>
       <c r="E816" s="3">
         <v>1</v>
@@ -24366,13 +24356,13 @@
         <v>816</v>
       </c>
       <c r="B817" s="5" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C817" s="5" t="s">
         <v>2231</v>
       </c>
-      <c r="C817" s="5" t="s">
+      <c r="D817" s="5" t="s">
         <v>2232</v>
-      </c>
-      <c r="D817" s="5" t="s">
-        <v>2233</v>
       </c>
       <c r="E817" s="3">
         <v>1</v>
@@ -24383,13 +24373,13 @@
         <v>817</v>
       </c>
       <c r="B818" s="5" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C818" s="5" t="s">
         <v>2234</v>
       </c>
-      <c r="C818" s="5" t="s">
+      <c r="D818" s="5" t="s">
         <v>2235</v>
-      </c>
-      <c r="D818" s="5" t="s">
-        <v>2236</v>
       </c>
       <c r="E818" s="3">
         <v>1</v>
@@ -24400,13 +24390,13 @@
         <v>818</v>
       </c>
       <c r="B819" s="5" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C819" s="5" t="s">
         <v>2237</v>
       </c>
-      <c r="C819" s="5" t="s">
+      <c r="D819" s="5" t="s">
         <v>2238</v>
-      </c>
-      <c r="D819" s="5" t="s">
-        <v>2239</v>
       </c>
       <c r="E819" s="3">
         <v>1</v>
@@ -24417,13 +24407,13 @@
         <v>819</v>
       </c>
       <c r="B820" s="5" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C820" s="5" t="s">
         <v>2240</v>
       </c>
-      <c r="C820" s="5" t="s">
+      <c r="D820" s="5" t="s">
         <v>2241</v>
-      </c>
-      <c r="D820" s="5" t="s">
-        <v>2242</v>
       </c>
       <c r="E820" s="3">
         <v>1</v>
@@ -24434,13 +24424,13 @@
         <v>820</v>
       </c>
       <c r="B821" s="5" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C821" s="5" t="s">
         <v>2243</v>
       </c>
-      <c r="C821" s="5" t="s">
+      <c r="D821" s="5" t="s">
         <v>2244</v>
-      </c>
-      <c r="D821" s="5" t="s">
-        <v>2245</v>
       </c>
       <c r="E821" s="3">
         <v>1</v>
@@ -24451,13 +24441,13 @@
         <v>821</v>
       </c>
       <c r="B822" s="5" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C822" s="5" t="s">
         <v>2246</v>
       </c>
-      <c r="C822" s="5" t="s">
+      <c r="D822" s="5" t="s">
         <v>2247</v>
-      </c>
-      <c r="D822" s="5" t="s">
-        <v>2248</v>
       </c>
       <c r="E822" s="3">
         <v>1</v>
@@ -24468,13 +24458,13 @@
         <v>822</v>
       </c>
       <c r="B823" s="5" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C823" s="5" t="s">
         <v>2249</v>
       </c>
-      <c r="C823" s="5" t="s">
+      <c r="D823" s="5" t="s">
         <v>2250</v>
-      </c>
-      <c r="D823" s="5" t="s">
-        <v>2251</v>
       </c>
       <c r="E823" s="3">
         <v>1</v>
@@ -24485,13 +24475,13 @@
         <v>823</v>
       </c>
       <c r="B824" s="5" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C824" s="5" t="s">
         <v>2252</v>
       </c>
-      <c r="C824" s="5" t="s">
+      <c r="D824" s="5" t="s">
         <v>2253</v>
-      </c>
-      <c r="D824" s="5" t="s">
-        <v>2254</v>
       </c>
       <c r="E824" s="3">
         <v>1</v>
@@ -24502,13 +24492,13 @@
         <v>824</v>
       </c>
       <c r="B825" s="5" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C825" s="5" t="s">
         <v>2255</v>
       </c>
-      <c r="C825" s="5" t="s">
+      <c r="D825" s="5" t="s">
         <v>2256</v>
-      </c>
-      <c r="D825" s="5" t="s">
-        <v>2257</v>
       </c>
       <c r="E825" s="3">
         <v>1</v>
@@ -24519,13 +24509,13 @@
         <v>825</v>
       </c>
       <c r="B826" s="5" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C826" s="5" t="s">
         <v>2258</v>
       </c>
-      <c r="C826" s="5" t="s">
+      <c r="D826" s="5" t="s">
         <v>2259</v>
-      </c>
-      <c r="D826" s="5" t="s">
-        <v>2260</v>
       </c>
       <c r="E826" s="3">
         <v>1</v>
@@ -24553,13 +24543,13 @@
         <v>827</v>
       </c>
       <c r="B828" s="5" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C828" s="5" t="s">
         <v>2261</v>
       </c>
-      <c r="C828" s="5" t="s">
+      <c r="D828" s="5" t="s">
         <v>2262</v>
-      </c>
-      <c r="D828" s="5" t="s">
-        <v>2263</v>
       </c>
       <c r="E828" s="3">
         <v>1</v>
@@ -24570,13 +24560,13 @@
         <v>828</v>
       </c>
       <c r="B829" s="5" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C829" s="5" t="s">
         <v>2264</v>
       </c>
-      <c r="C829" s="5" t="s">
+      <c r="D829" s="5" t="s">
         <v>2265</v>
-      </c>
-      <c r="D829" s="5" t="s">
-        <v>2266</v>
       </c>
       <c r="E829" s="3">
         <v>1</v>
@@ -24587,13 +24577,13 @@
         <v>829</v>
       </c>
       <c r="B830" s="5" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C830" s="5" t="s">
         <v>2267</v>
       </c>
-      <c r="C830" s="5" t="s">
+      <c r="D830" s="5" t="s">
         <v>2268</v>
-      </c>
-      <c r="D830" s="5" t="s">
-        <v>2269</v>
       </c>
       <c r="E830" s="3">
         <v>1</v>
@@ -24604,13 +24594,13 @@
         <v>830</v>
       </c>
       <c r="B831" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C831" s="5" t="s">
         <v>2270</v>
       </c>
-      <c r="C831" s="5" t="s">
+      <c r="D831" s="5" t="s">
         <v>2271</v>
-      </c>
-      <c r="D831" s="5" t="s">
-        <v>2272</v>
       </c>
       <c r="E831" s="3">
         <v>1</v>
@@ -24621,13 +24611,13 @@
         <v>831</v>
       </c>
       <c r="B832" s="5" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C832" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C832" s="5" t="s">
+      <c r="D832" s="5" t="s">
         <v>2274</v>
-      </c>
-      <c r="D832" s="5" t="s">
-        <v>2275</v>
       </c>
       <c r="E832" s="3">
         <v>1</v>
@@ -24638,13 +24628,13 @@
         <v>832</v>
       </c>
       <c r="B833" s="5" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C833" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C833" s="5" t="s">
+      <c r="D833" s="5" t="s">
         <v>2277</v>
-      </c>
-      <c r="D833" s="5" t="s">
-        <v>2278</v>
       </c>
       <c r="E833" s="3">
         <v>1</v>
@@ -24655,13 +24645,13 @@
         <v>833</v>
       </c>
       <c r="B834" s="5" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C834" s="5" t="s">
         <v>2279</v>
       </c>
-      <c r="C834" s="5" t="s">
+      <c r="D834" s="5" t="s">
         <v>2280</v>
-      </c>
-      <c r="D834" s="5" t="s">
-        <v>2281</v>
       </c>
       <c r="E834" s="3">
         <v>1</v>
@@ -24672,13 +24662,13 @@
         <v>834</v>
       </c>
       <c r="B835" s="5" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C835" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C835" s="5" t="s">
+      <c r="D835" s="5" t="s">
         <v>2283</v>
-      </c>
-      <c r="D835" s="5" t="s">
-        <v>2284</v>
       </c>
       <c r="E835" s="3">
         <v>1</v>
@@ -24689,13 +24679,13 @@
         <v>835</v>
       </c>
       <c r="B836" s="5" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C836" s="5" t="s">
         <v>1725</v>
       </c>
-      <c r="C836" s="5" t="s">
+      <c r="D836" s="5" t="s">
         <v>1726</v>
-      </c>
-      <c r="D836" s="5" t="s">
-        <v>1727</v>
       </c>
       <c r="E836" s="3">
         <v>1</v>
@@ -24706,13 +24696,13 @@
         <v>836</v>
       </c>
       <c r="B837" s="5" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C837" s="5" t="s">
         <v>2285</v>
       </c>
-      <c r="C837" s="5" t="s">
+      <c r="D837" s="5" t="s">
         <v>2286</v>
-      </c>
-      <c r="D837" s="5" t="s">
-        <v>2287</v>
       </c>
       <c r="E837" s="3">
         <v>1</v>
@@ -24723,13 +24713,13 @@
         <v>837</v>
       </c>
       <c r="B838" s="5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C838" s="5" t="s">
         <v>2288</v>
       </c>
-      <c r="C838" s="5" t="s">
+      <c r="D838" s="5" t="s">
         <v>2289</v>
-      </c>
-      <c r="D838" s="5" t="s">
-        <v>2290</v>
       </c>
       <c r="E838" s="3">
         <v>1</v>
@@ -24740,13 +24730,13 @@
         <v>838</v>
       </c>
       <c r="B839" s="5" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C839" s="5" t="s">
         <v>2291</v>
       </c>
-      <c r="C839" s="5" t="s">
+      <c r="D839" s="5" t="s">
         <v>2292</v>
-      </c>
-      <c r="D839" s="5" t="s">
-        <v>2293</v>
       </c>
       <c r="E839" s="3">
         <v>1</v>
@@ -24757,13 +24747,13 @@
         <v>839</v>
       </c>
       <c r="B840" s="5" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C840" s="5" t="s">
         <v>2294</v>
       </c>
-      <c r="C840" s="5" t="s">
+      <c r="D840" s="5" t="s">
         <v>2295</v>
-      </c>
-      <c r="D840" s="5" t="s">
-        <v>2296</v>
       </c>
       <c r="E840" s="3">
         <v>1</v>
@@ -24774,13 +24764,13 @@
         <v>840</v>
       </c>
       <c r="B841" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C841" s="5" t="s">
         <v>2297</v>
       </c>
-      <c r="C841" s="5" t="s">
+      <c r="D841" s="5" t="s">
         <v>2298</v>
-      </c>
-      <c r="D841" s="5" t="s">
-        <v>2299</v>
       </c>
       <c r="E841" s="3">
         <v>1</v>
@@ -24791,13 +24781,13 @@
         <v>841</v>
       </c>
       <c r="B842" s="5" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C842" s="5" t="s">
         <v>2300</v>
       </c>
-      <c r="C842" s="5" t="s">
+      <c r="D842" s="5" t="s">
         <v>2301</v>
-      </c>
-      <c r="D842" s="5" t="s">
-        <v>2302</v>
       </c>
       <c r="E842" s="3">
         <v>1</v>
@@ -24808,13 +24798,13 @@
         <v>842</v>
       </c>
       <c r="B843" s="5" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C843" s="5" t="s">
         <v>2303</v>
       </c>
-      <c r="C843" s="5" t="s">
+      <c r="D843" s="5" t="s">
         <v>2304</v>
-      </c>
-      <c r="D843" s="5" t="s">
-        <v>2305</v>
       </c>
       <c r="E843" s="3">
         <v>1</v>
@@ -24825,13 +24815,13 @@
         <v>843</v>
       </c>
       <c r="B844" s="5" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C844" s="5" t="s">
         <v>2306</v>
       </c>
-      <c r="C844" s="5" t="s">
+      <c r="D844" s="5" t="s">
         <v>2307</v>
-      </c>
-      <c r="D844" s="5" t="s">
-        <v>2308</v>
       </c>
       <c r="E844" s="3">
         <v>1</v>
@@ -24848,7 +24838,7 @@
         <v>243</v>
       </c>
       <c r="D845" s="5" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="E845" s="3">
         <v>1</v>
@@ -24859,13 +24849,13 @@
         <v>845</v>
       </c>
       <c r="B846" s="5" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C846" s="5" t="s">
         <v>2310</v>
       </c>
-      <c r="C846" s="5" t="s">
+      <c r="D846" s="5" t="s">
         <v>2311</v>
-      </c>
-      <c r="D846" s="5" t="s">
-        <v>2312</v>
       </c>
       <c r="E846" s="3">
         <v>1</v>
@@ -24876,13 +24866,13 @@
         <v>846</v>
       </c>
       <c r="B847" s="5" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C847" s="5" t="s">
         <v>2313</v>
       </c>
-      <c r="C847" s="5" t="s">
+      <c r="D847" s="5" t="s">
         <v>2314</v>
-      </c>
-      <c r="D847" s="5" t="s">
-        <v>2315</v>
       </c>
       <c r="E847" s="3">
         <v>1</v>
@@ -24893,13 +24883,13 @@
         <v>847</v>
       </c>
       <c r="B848" s="5" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C848" s="5" t="s">
         <v>2316</v>
       </c>
-      <c r="C848" s="5" t="s">
+      <c r="D848" s="5" t="s">
         <v>2317</v>
-      </c>
-      <c r="D848" s="5" t="s">
-        <v>2318</v>
       </c>
       <c r="E848" s="3">
         <v>1</v>
@@ -24910,13 +24900,13 @@
         <v>848</v>
       </c>
       <c r="B849" s="5" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C849" s="5" t="s">
         <v>2319</v>
       </c>
-      <c r="C849" s="5" t="s">
+      <c r="D849" s="5" t="s">
         <v>2320</v>
-      </c>
-      <c r="D849" s="5" t="s">
-        <v>2321</v>
       </c>
       <c r="E849" s="3">
         <v>1</v>
@@ -24927,13 +24917,13 @@
         <v>849</v>
       </c>
       <c r="B850" s="5" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C850" s="5" t="s">
         <v>2322</v>
       </c>
-      <c r="C850" s="5" t="s">
+      <c r="D850" s="5" t="s">
         <v>2323</v>
-      </c>
-      <c r="D850" s="5" t="s">
-        <v>2324</v>
       </c>
       <c r="E850" s="3">
         <v>1</v>
@@ -24950,7 +24940,7 @@
         <v>620</v>
       </c>
       <c r="D851" s="5" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="E851" s="3">
         <v>1</v>
@@ -24961,13 +24951,13 @@
         <v>851</v>
       </c>
       <c r="B852" s="5" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C852" s="5" t="s">
         <v>2326</v>
       </c>
-      <c r="C852" s="5" t="s">
+      <c r="D852" s="5" t="s">
         <v>2327</v>
-      </c>
-      <c r="D852" s="5" t="s">
-        <v>2328</v>
       </c>
       <c r="E852" s="3">
         <v>1</v>
@@ -24978,13 +24968,13 @@
         <v>852</v>
       </c>
       <c r="B853" s="5" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C853" s="5" t="s">
         <v>2329</v>
       </c>
-      <c r="C853" s="5" t="s">
+      <c r="D853" s="5" t="s">
         <v>2330</v>
-      </c>
-      <c r="D853" s="5" t="s">
-        <v>2331</v>
       </c>
       <c r="E853" s="3">
         <v>1</v>
@@ -24995,13 +24985,13 @@
         <v>853</v>
       </c>
       <c r="B854" s="5" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C854" s="5" t="s">
         <v>2332</v>
       </c>
-      <c r="C854" s="5" t="s">
+      <c r="D854" s="5" t="s">
         <v>2333</v>
-      </c>
-      <c r="D854" s="5" t="s">
-        <v>2334</v>
       </c>
       <c r="E854" s="3">
         <v>1</v>
@@ -25012,13 +25002,13 @@
         <v>854</v>
       </c>
       <c r="B855" s="5" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C855" s="5" t="s">
         <v>2335</v>
       </c>
-      <c r="C855" s="5" t="s">
+      <c r="D855" s="5" t="s">
         <v>2336</v>
-      </c>
-      <c r="D855" s="5" t="s">
-        <v>2337</v>
       </c>
       <c r="E855" s="3">
         <v>1</v>
@@ -25029,13 +25019,13 @@
         <v>855</v>
       </c>
       <c r="B856" s="5" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C856" s="5" t="s">
         <v>2338</v>
       </c>
-      <c r="C856" s="5" t="s">
+      <c r="D856" s="5" t="s">
         <v>2339</v>
-      </c>
-      <c r="D856" s="5" t="s">
-        <v>2340</v>
       </c>
       <c r="E856" s="3">
         <v>1</v>
@@ -25046,13 +25036,13 @@
         <v>856</v>
       </c>
       <c r="B857" s="5" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C857" s="5" t="s">
         <v>2341</v>
       </c>
-      <c r="C857" s="5" t="s">
+      <c r="D857" s="5" t="s">
         <v>2342</v>
-      </c>
-      <c r="D857" s="5" t="s">
-        <v>2343</v>
       </c>
       <c r="E857" s="3">
         <v>1</v>
@@ -25063,13 +25053,13 @@
         <v>857</v>
       </c>
       <c r="B858" s="5" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C858" s="5" t="s">
         <v>2344</v>
       </c>
-      <c r="C858" s="5" t="s">
+      <c r="D858" s="5" t="s">
         <v>2345</v>
-      </c>
-      <c r="D858" s="5" t="s">
-        <v>2346</v>
       </c>
       <c r="E858" s="3">
         <v>1</v>
@@ -25080,13 +25070,13 @@
         <v>858</v>
       </c>
       <c r="B859" s="5" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C859" s="5" t="s">
         <v>2347</v>
       </c>
-      <c r="C859" s="5" t="s">
+      <c r="D859" s="5" t="s">
         <v>2348</v>
-      </c>
-      <c r="D859" s="5" t="s">
-        <v>2349</v>
       </c>
       <c r="E859" s="3">
         <v>1</v>
@@ -25097,13 +25087,13 @@
         <v>859</v>
       </c>
       <c r="B860" s="5" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C860" s="5" t="s">
         <v>2350</v>
       </c>
-      <c r="C860" s="5" t="s">
+      <c r="D860" s="5" t="s">
         <v>2351</v>
-      </c>
-      <c r="D860" s="5" t="s">
-        <v>2352</v>
       </c>
       <c r="E860" s="3">
         <v>1</v>
@@ -25131,13 +25121,13 @@
         <v>861</v>
       </c>
       <c r="B862" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C862" s="5" t="s">
         <v>2353</v>
       </c>
-      <c r="C862" s="5" t="s">
+      <c r="D862" s="5" t="s">
         <v>2354</v>
-      </c>
-      <c r="D862" s="5" t="s">
-        <v>2355</v>
       </c>
       <c r="E862" s="3">
         <v>1</v>
@@ -25148,13 +25138,13 @@
         <v>862</v>
       </c>
       <c r="B863" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C863" s="5" t="s">
         <v>2356</v>
       </c>
-      <c r="C863" s="5" t="s">
+      <c r="D863" s="5" t="s">
         <v>2357</v>
-      </c>
-      <c r="D863" s="5" t="s">
-        <v>2358</v>
       </c>
       <c r="E863" s="3">
         <v>1</v>
@@ -25165,13 +25155,13 @@
         <v>863</v>
       </c>
       <c r="B864" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C864" s="5" t="s">
         <v>2359</v>
       </c>
-      <c r="C864" s="5" t="s">
+      <c r="D864" s="5" t="s">
         <v>2360</v>
-      </c>
-      <c r="D864" s="5" t="s">
-        <v>2361</v>
       </c>
       <c r="E864" s="3">
         <v>1</v>
@@ -25182,13 +25172,13 @@
         <v>864</v>
       </c>
       <c r="B865" s="5" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C865" s="5" t="s">
         <v>2362</v>
       </c>
-      <c r="C865" s="5" t="s">
+      <c r="D865" s="5" t="s">
         <v>2363</v>
-      </c>
-      <c r="D865" s="5" t="s">
-        <v>2364</v>
       </c>
       <c r="E865" s="3">
         <v>1</v>
@@ -25199,13 +25189,11 @@
         <v>865</v>
       </c>
       <c r="B866" s="5" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C866" s="5"/>
+      <c r="D866" s="5" t="s">
         <v>2365</v>
-      </c>
-      <c r="C866" s="5" t="s">
-        <v>2366</v>
-      </c>
-      <c r="D866" s="5" t="s">
-        <v>2367</v>
       </c>
       <c r="E866" s="3">
         <v>1</v>
@@ -25216,13 +25204,13 @@
         <v>866</v>
       </c>
       <c r="B867" s="5" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C867" s="5" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D867" s="5" t="s">
         <v>2368</v>
-      </c>
-      <c r="C867" s="5" t="s">
-        <v>2369</v>
-      </c>
-      <c r="D867" s="5" t="s">
-        <v>2370</v>
       </c>
       <c r="E867" s="3">
         <v>1</v>
@@ -25233,13 +25221,13 @@
         <v>867</v>
       </c>
       <c r="B868" s="5" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C868" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D868" s="5" t="s">
         <v>2371</v>
-      </c>
-      <c r="C868" s="5" t="s">
-        <v>2372</v>
-      </c>
-      <c r="D868" s="5" t="s">
-        <v>2373</v>
       </c>
       <c r="E868" s="3">
         <v>1</v>
@@ -25250,13 +25238,13 @@
         <v>868</v>
       </c>
       <c r="B869" s="5" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C869" s="5" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D869" s="5" t="s">
         <v>2374</v>
-      </c>
-      <c r="C869" s="5" t="s">
-        <v>2375</v>
-      </c>
-      <c r="D869" s="5" t="s">
-        <v>2376</v>
       </c>
       <c r="E869" s="3">
         <v>1</v>
@@ -25267,13 +25255,13 @@
         <v>869</v>
       </c>
       <c r="B870" s="5" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C870" s="5" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D870" s="5" t="s">
         <v>2377</v>
-      </c>
-      <c r="C870" s="5" t="s">
-        <v>2378</v>
-      </c>
-      <c r="D870" s="5" t="s">
-        <v>2379</v>
       </c>
       <c r="E870" s="3">
         <v>1</v>
@@ -25284,13 +25272,13 @@
         <v>870</v>
       </c>
       <c r="B871" s="5" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C871" s="5" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D871" s="5" t="s">
         <v>2380</v>
-      </c>
-      <c r="C871" s="5" t="s">
-        <v>2381</v>
-      </c>
-      <c r="D871" s="5" t="s">
-        <v>2382</v>
       </c>
       <c r="E871" s="3">
         <v>1</v>
@@ -25301,13 +25289,13 @@
         <v>871</v>
       </c>
       <c r="B872" s="5" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C872" s="5" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D872" s="5" t="s">
         <v>2383</v>
-      </c>
-      <c r="C872" s="5" t="s">
-        <v>2384</v>
-      </c>
-      <c r="D872" s="5" t="s">
-        <v>2385</v>
       </c>
       <c r="E872" s="3">
         <v>1</v>
@@ -25318,13 +25306,13 @@
         <v>872</v>
       </c>
       <c r="B873" s="5" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C873" s="5" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D873" s="5" t="s">
         <v>2386</v>
-      </c>
-      <c r="C873" s="5" t="s">
-        <v>2387</v>
-      </c>
-      <c r="D873" s="5" t="s">
-        <v>2388</v>
       </c>
       <c r="E873" s="3">
         <v>1</v>
@@ -25352,13 +25340,13 @@
         <v>874</v>
       </c>
       <c r="B875" s="5" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C875" s="5" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D875" s="5" t="s">
         <v>2389</v>
-      </c>
-      <c r="C875" s="5" t="s">
-        <v>2390</v>
-      </c>
-      <c r="D875" s="5" t="s">
-        <v>2391</v>
       </c>
       <c r="E875" s="3">
         <v>1</v>
@@ -25369,13 +25357,13 @@
         <v>875</v>
       </c>
       <c r="B876" s="5" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C876" s="5" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D876" s="5" t="s">
         <v>2392</v>
-      </c>
-      <c r="C876" s="5" t="s">
-        <v>2393</v>
-      </c>
-      <c r="D876" s="5" t="s">
-        <v>2394</v>
       </c>
       <c r="E876" s="3">
         <v>1</v>
@@ -25386,13 +25374,13 @@
         <v>876</v>
       </c>
       <c r="B877" s="5" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C877" s="5" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D877" s="5" t="s">
         <v>2395</v>
-      </c>
-      <c r="C877" s="5" t="s">
-        <v>2396</v>
-      </c>
-      <c r="D877" s="5" t="s">
-        <v>2397</v>
       </c>
       <c r="E877" s="3">
         <v>1</v>
@@ -25403,13 +25391,13 @@
         <v>877</v>
       </c>
       <c r="B878" s="5" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C878" s="5" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D878" s="5" t="s">
         <v>2398</v>
-      </c>
-      <c r="C878" s="5" t="s">
-        <v>2399</v>
-      </c>
-      <c r="D878" s="5" t="s">
-        <v>2400</v>
       </c>
       <c r="E878" s="3">
         <v>1</v>
@@ -25420,13 +25408,13 @@
         <v>878</v>
       </c>
       <c r="B879" s="5" t="s">
+        <v>2399</v>
+      </c>
+      <c r="C879" s="5" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D879" s="5" t="s">
         <v>2401</v>
-      </c>
-      <c r="C879" s="5" t="s">
-        <v>2402</v>
-      </c>
-      <c r="D879" s="5" t="s">
-        <v>2403</v>
       </c>
       <c r="E879" s="3">
         <v>1</v>
@@ -25437,13 +25425,13 @@
         <v>879</v>
       </c>
       <c r="B880" s="5" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C880" s="5" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D880" s="5" t="s">
         <v>2404</v>
-      </c>
-      <c r="C880" s="5" t="s">
-        <v>2405</v>
-      </c>
-      <c r="D880" s="5" t="s">
-        <v>2406</v>
       </c>
       <c r="E880" s="3">
         <v>1</v>
@@ -25454,13 +25442,13 @@
         <v>880</v>
       </c>
       <c r="B881" s="5" t="s">
+        <v>2405</v>
+      </c>
+      <c r="C881" s="5" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D881" s="5" t="s">
         <v>2407</v>
-      </c>
-      <c r="C881" s="5" t="s">
-        <v>2408</v>
-      </c>
-      <c r="D881" s="5" t="s">
-        <v>2409</v>
       </c>
       <c r="E881" s="3">
         <v>1</v>
@@ -25471,13 +25459,13 @@
         <v>881</v>
       </c>
       <c r="B882" s="5" t="s">
+        <v>2408</v>
+      </c>
+      <c r="C882" s="5" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D882" s="5" t="s">
         <v>2410</v>
-      </c>
-      <c r="C882" s="5" t="s">
-        <v>2411</v>
-      </c>
-      <c r="D882" s="5" t="s">
-        <v>2412</v>
       </c>
       <c r="E882" s="3">
         <v>1</v>
@@ -25488,13 +25476,13 @@
         <v>882</v>
       </c>
       <c r="B883" s="5" t="s">
+        <v>2411</v>
+      </c>
+      <c r="C883" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D883" s="5" t="s">
         <v>2413</v>
-      </c>
-      <c r="C883" s="5" t="s">
-        <v>2414</v>
-      </c>
-      <c r="D883" s="5" t="s">
-        <v>2415</v>
       </c>
       <c r="E883" s="3">
         <v>1</v>
@@ -25505,13 +25493,13 @@
         <v>883</v>
       </c>
       <c r="B884" s="5" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C884" s="5" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D884" s="5" t="s">
         <v>2416</v>
-      </c>
-      <c r="C884" s="5" t="s">
-        <v>2417</v>
-      </c>
-      <c r="D884" s="5" t="s">
-        <v>2418</v>
       </c>
       <c r="E884" s="3">
         <v>1</v>
@@ -25522,13 +25510,13 @@
         <v>884</v>
       </c>
       <c r="B885" s="5" t="s">
+        <v>2417</v>
+      </c>
+      <c r="C885" s="5" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D885" s="5" t="s">
         <v>2419</v>
-      </c>
-      <c r="C885" s="5" t="s">
-        <v>2420</v>
-      </c>
-      <c r="D885" s="5" t="s">
-        <v>2421</v>
       </c>
       <c r="E885" s="3">
         <v>1</v>
@@ -25539,13 +25527,13 @@
         <v>885</v>
       </c>
       <c r="B886" s="5" t="s">
+        <v>2420</v>
+      </c>
+      <c r="C886" s="5" t="s">
+        <v>2421</v>
+      </c>
+      <c r="D886" s="5" t="s">
         <v>2422</v>
-      </c>
-      <c r="C886" s="5" t="s">
-        <v>2423</v>
-      </c>
-      <c r="D886" s="5" t="s">
-        <v>2424</v>
       </c>
       <c r="E886" s="3">
         <v>1</v>
@@ -25556,13 +25544,13 @@
         <v>886</v>
       </c>
       <c r="B887" s="5" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C887" s="5" t="s">
+        <v>2424</v>
+      </c>
+      <c r="D887" s="5" t="s">
         <v>2425</v>
-      </c>
-      <c r="C887" s="5" t="s">
-        <v>2426</v>
-      </c>
-      <c r="D887" s="5" t="s">
-        <v>2427</v>
       </c>
       <c r="E887" s="3">
         <v>1</v>
@@ -25573,13 +25561,13 @@
         <v>887</v>
       </c>
       <c r="B888" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C888" s="5" t="s">
         <v>1900</v>
       </c>
-      <c r="C888" s="5" t="s">
-        <v>1901</v>
-      </c>
       <c r="D888" s="5" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="E888" s="3">
         <v>1</v>
@@ -25590,13 +25578,13 @@
         <v>888</v>
       </c>
       <c r="B889" s="5" t="s">
+        <v>2427</v>
+      </c>
+      <c r="C889" s="5" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D889" s="5" t="s">
         <v>2429</v>
-      </c>
-      <c r="C889" s="5" t="s">
-        <v>2430</v>
-      </c>
-      <c r="D889" s="5" t="s">
-        <v>2431</v>
       </c>
       <c r="E889" s="3">
         <v>1</v>
@@ -25607,11 +25595,11 @@
         <v>889</v>
       </c>
       <c r="B890" s="5" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="C890" s="5"/>
       <c r="D890" s="5" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="E890" s="3">
         <v>1</v>
@@ -25622,13 +25610,13 @@
         <v>890</v>
       </c>
       <c r="B891" s="5" t="s">
+        <v>2432</v>
+      </c>
+      <c r="C891" s="5" t="s">
+        <v>2433</v>
+      </c>
+      <c r="D891" s="5" t="s">
         <v>2434</v>
-      </c>
-      <c r="C891" s="5" t="s">
-        <v>2435</v>
-      </c>
-      <c r="D891" s="5" t="s">
-        <v>2436</v>
       </c>
       <c r="E891" s="3">
         <v>1</v>
@@ -25656,13 +25644,13 @@
         <v>892</v>
       </c>
       <c r="B893" s="5" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C893" s="5" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D893" s="5" t="s">
         <v>2437</v>
-      </c>
-      <c r="C893" s="5" t="s">
-        <v>2438</v>
-      </c>
-      <c r="D893" s="5" t="s">
-        <v>2439</v>
       </c>
       <c r="E893" s="3">
         <v>1</v>
@@ -25673,13 +25661,13 @@
         <v>893</v>
       </c>
       <c r="B894" s="5" t="s">
+        <v>2438</v>
+      </c>
+      <c r="C894" s="5" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D894" s="5" t="s">
         <v>2440</v>
-      </c>
-      <c r="C894" s="5" t="s">
-        <v>2441</v>
-      </c>
-      <c r="D894" s="5" t="s">
-        <v>2442</v>
       </c>
       <c r="E894" s="3">
         <v>1</v>
@@ -25690,13 +25678,13 @@
         <v>894</v>
       </c>
       <c r="B895" s="5" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C895" s="5" t="s">
+        <v>2442</v>
+      </c>
+      <c r="D895" s="5" t="s">
         <v>2443</v>
-      </c>
-      <c r="C895" s="5" t="s">
-        <v>2444</v>
-      </c>
-      <c r="D895" s="5" t="s">
-        <v>2445</v>
       </c>
       <c r="E895" s="3">
         <v>1</v>
@@ -25707,13 +25695,13 @@
         <v>895</v>
       </c>
       <c r="B896" s="5" t="s">
+        <v>2444</v>
+      </c>
+      <c r="C896" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="D896" s="5" t="s">
         <v>2446</v>
-      </c>
-      <c r="C896" s="5" t="s">
-        <v>2447</v>
-      </c>
-      <c r="D896" s="5" t="s">
-        <v>2448</v>
       </c>
       <c r="E896" s="3">
         <v>1</v>
@@ -25724,13 +25712,13 @@
         <v>896</v>
       </c>
       <c r="B897" s="5" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C897" s="5" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D897" s="5" t="s">
         <v>2449</v>
-      </c>
-      <c r="C897" s="5" t="s">
-        <v>2450</v>
-      </c>
-      <c r="D897" s="5" t="s">
-        <v>2451</v>
       </c>
       <c r="E897" s="3">
         <v>1</v>
@@ -25741,13 +25729,13 @@
         <v>897</v>
       </c>
       <c r="B898" s="5" t="s">
+        <v>2450</v>
+      </c>
+      <c r="C898" s="5" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D898" s="5" t="s">
         <v>2452</v>
-      </c>
-      <c r="C898" s="5" t="s">
-        <v>2453</v>
-      </c>
-      <c r="D898" s="5" t="s">
-        <v>2454</v>
       </c>
       <c r="E898" s="3">
         <v>1</v>
@@ -25758,13 +25746,13 @@
         <v>898</v>
       </c>
       <c r="B899" s="5" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C899" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D899" s="5" t="s">
         <v>2455</v>
-      </c>
-      <c r="C899" s="5" t="s">
-        <v>2456</v>
-      </c>
-      <c r="D899" s="5" t="s">
-        <v>2457</v>
       </c>
       <c r="E899" s="3">
         <v>1</v>
@@ -25792,13 +25780,13 @@
         <v>900</v>
       </c>
       <c r="B901" s="5" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C901" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="D901" s="5" t="s">
         <v>2458</v>
-      </c>
-      <c r="C901" s="5" t="s">
-        <v>2459</v>
-      </c>
-      <c r="D901" s="5" t="s">
-        <v>2460</v>
       </c>
       <c r="E901" s="3">
         <v>1</v>
@@ -25809,13 +25797,13 @@
         <v>901</v>
       </c>
       <c r="B902" s="5" t="s">
+        <v>2459</v>
+      </c>
+      <c r="C902" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D902" s="5" t="s">
         <v>2461</v>
-      </c>
-      <c r="C902" s="5" t="s">
-        <v>2462</v>
-      </c>
-      <c r="D902" s="5" t="s">
-        <v>2463</v>
       </c>
       <c r="E902" s="3">
         <v>1</v>
@@ -25826,13 +25814,13 @@
         <v>902</v>
       </c>
       <c r="B903" s="5" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C903" s="5" t="s">
         <v>1677</v>
       </c>
-      <c r="C903" s="5" t="s">
+      <c r="D903" s="5" t="s">
         <v>1678</v>
-      </c>
-      <c r="D903" s="5" t="s">
-        <v>1679</v>
       </c>
       <c r="E903" s="3">
         <v>1</v>
@@ -25843,13 +25831,13 @@
         <v>903</v>
       </c>
       <c r="B904" s="5" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C904" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="D904" s="5" t="s">
         <v>2464</v>
-      </c>
-      <c r="C904" s="5" t="s">
-        <v>2465</v>
-      </c>
-      <c r="D904" s="5" t="s">
-        <v>2466</v>
       </c>
       <c r="E904" s="3">
         <v>1</v>
@@ -25860,13 +25848,13 @@
         <v>904</v>
       </c>
       <c r="B905" s="5" t="s">
+        <v>2465</v>
+      </c>
+      <c r="C905" s="5" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D905" s="5" t="s">
         <v>2467</v>
-      </c>
-      <c r="C905" s="5" t="s">
-        <v>2468</v>
-      </c>
-      <c r="D905" s="5" t="s">
-        <v>2469</v>
       </c>
       <c r="E905" s="3">
         <v>1</v>
@@ -25877,13 +25865,13 @@
         <v>905</v>
       </c>
       <c r="B906" s="5" t="s">
+        <v>2468</v>
+      </c>
+      <c r="C906" s="5" t="s">
+        <v>2469</v>
+      </c>
+      <c r="D906" s="5" t="s">
         <v>2470</v>
-      </c>
-      <c r="C906" s="5" t="s">
-        <v>2471</v>
-      </c>
-      <c r="D906" s="5" t="s">
-        <v>2472</v>
       </c>
       <c r="E906" s="3">
         <v>1</v>
@@ -25894,13 +25882,13 @@
         <v>906</v>
       </c>
       <c r="B907" s="5" t="s">
+        <v>2471</v>
+      </c>
+      <c r="C907" s="5" t="s">
+        <v>2472</v>
+      </c>
+      <c r="D907" s="5" t="s">
         <v>2473</v>
-      </c>
-      <c r="C907" s="5" t="s">
-        <v>2474</v>
-      </c>
-      <c r="D907" s="5" t="s">
-        <v>2475</v>
       </c>
       <c r="E907" s="3">
         <v>1</v>
@@ -25911,13 +25899,13 @@
         <v>907</v>
       </c>
       <c r="B908" s="5" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C908" s="5" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D908" s="5" t="s">
         <v>2476</v>
-      </c>
-      <c r="C908" s="5" t="s">
-        <v>2477</v>
-      </c>
-      <c r="D908" s="5" t="s">
-        <v>2478</v>
       </c>
       <c r="E908" s="3">
         <v>1</v>
@@ -25928,13 +25916,13 @@
         <v>908</v>
       </c>
       <c r="B909" s="5" t="s">
+        <v>2477</v>
+      </c>
+      <c r="C909" s="5" t="s">
+        <v>2478</v>
+      </c>
+      <c r="D909" s="5" t="s">
         <v>2479</v>
-      </c>
-      <c r="C909" s="5" t="s">
-        <v>2480</v>
-      </c>
-      <c r="D909" s="5" t="s">
-        <v>2481</v>
       </c>
       <c r="E909" s="3">
         <v>1</v>
@@ -25945,13 +25933,13 @@
         <v>909</v>
       </c>
       <c r="B910" s="5" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C910" s="5" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D910" s="5" t="s">
         <v>2482</v>
-      </c>
-      <c r="C910" s="5" t="s">
-        <v>2483</v>
-      </c>
-      <c r="D910" s="5" t="s">
-        <v>2484</v>
       </c>
       <c r="E910" s="3">
         <v>1</v>
@@ -25962,13 +25950,13 @@
         <v>910</v>
       </c>
       <c r="B911" s="5" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C911" s="5" t="s">
+        <v>2484</v>
+      </c>
+      <c r="D911" s="5" t="s">
         <v>2485</v>
-      </c>
-      <c r="C911" s="5" t="s">
-        <v>2486</v>
-      </c>
-      <c r="D911" s="5" t="s">
-        <v>2487</v>
       </c>
       <c r="E911" s="3">
         <v>1</v>
@@ -25979,13 +25967,13 @@
         <v>911</v>
       </c>
       <c r="B912" s="5" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C912" s="5" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D912" s="5" t="s">
         <v>2488</v>
-      </c>
-      <c r="C912" s="5" t="s">
-        <v>2489</v>
-      </c>
-      <c r="D912" s="5" t="s">
-        <v>2490</v>
       </c>
       <c r="E912" s="3">
         <v>1</v>
@@ -25996,13 +25984,13 @@
         <v>912</v>
       </c>
       <c r="B913" s="5" t="s">
+        <v>2489</v>
+      </c>
+      <c r="C913" s="5" t="s">
+        <v>2490</v>
+      </c>
+      <c r="D913" s="5" t="s">
         <v>2491</v>
-      </c>
-      <c r="C913" s="5" t="s">
-        <v>2492</v>
-      </c>
-      <c r="D913" s="5" t="s">
-        <v>2493</v>
       </c>
       <c r="E913" s="3">
         <v>1</v>
@@ -26030,13 +26018,13 @@
         <v>914</v>
       </c>
       <c r="B915" s="5" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C915" s="5" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D915" s="5" t="s">
         <v>2494</v>
-      </c>
-      <c r="C915" s="5" t="s">
-        <v>2495</v>
-      </c>
-      <c r="D915" s="5" t="s">
-        <v>2496</v>
       </c>
       <c r="E915" s="3">
         <v>1</v>
@@ -26047,13 +26035,13 @@
         <v>915</v>
       </c>
       <c r="B916" s="5" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C916" s="5" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D916" s="5" t="s">
         <v>2497</v>
-      </c>
-      <c r="C916" s="5" t="s">
-        <v>2498</v>
-      </c>
-      <c r="D916" s="5" t="s">
-        <v>2499</v>
       </c>
       <c r="E916" s="3">
         <v>1</v>
@@ -26064,13 +26052,13 @@
         <v>916</v>
       </c>
       <c r="B917" s="5" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C917" s="5" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D917" s="5" t="s">
         <v>2500</v>
-      </c>
-      <c r="C917" s="5" t="s">
-        <v>2501</v>
-      </c>
-      <c r="D917" s="5" t="s">
-        <v>2502</v>
       </c>
       <c r="E917" s="3">
         <v>1</v>
@@ -26081,13 +26069,13 @@
         <v>917</v>
       </c>
       <c r="B918" s="5" t="s">
+        <v>2501</v>
+      </c>
+      <c r="C918" s="5" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D918" s="5" t="s">
         <v>2503</v>
-      </c>
-      <c r="C918" s="5" t="s">
-        <v>2504</v>
-      </c>
-      <c r="D918" s="5" t="s">
-        <v>2505</v>
       </c>
       <c r="E918" s="3">
         <v>1</v>
@@ -26098,13 +26086,13 @@
         <v>918</v>
       </c>
       <c r="B919" s="5" t="s">
+        <v>2504</v>
+      </c>
+      <c r="C919" s="5" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D919" s="5" t="s">
         <v>2506</v>
-      </c>
-      <c r="C919" s="5" t="s">
-        <v>2507</v>
-      </c>
-      <c r="D919" s="5" t="s">
-        <v>2508</v>
       </c>
       <c r="E919" s="3">
         <v>1</v>
@@ -26121,7 +26109,7 @@
         <v>1428</v>
       </c>
       <c r="D920" s="5" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="E920" s="3">
         <v>1</v>
@@ -26135,10 +26123,10 @@
         <v>1427</v>
       </c>
       <c r="C921" s="5" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="D921" s="5" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="E921" s="3">
         <v>1</v>
@@ -26166,13 +26154,13 @@
         <v>922</v>
       </c>
       <c r="B923" s="5" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C923" s="5" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D923" s="5" t="s">
         <v>2512</v>
-      </c>
-      <c r="C923" s="5" t="s">
-        <v>2513</v>
-      </c>
-      <c r="D923" s="5" t="s">
-        <v>2514</v>
       </c>
       <c r="E923" s="3">
         <v>1</v>
@@ -26183,13 +26171,13 @@
         <v>923</v>
       </c>
       <c r="B924" s="5" t="s">
+        <v>2513</v>
+      </c>
+      <c r="C924" s="5" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D924" s="5" t="s">
         <v>2515</v>
-      </c>
-      <c r="C924" s="5" t="s">
-        <v>2516</v>
-      </c>
-      <c r="D924" s="5" t="s">
-        <v>2517</v>
       </c>
       <c r="E924" s="3">
         <v>1</v>
@@ -26200,13 +26188,13 @@
         <v>924</v>
       </c>
       <c r="B925" s="5" t="s">
+        <v>2516</v>
+      </c>
+      <c r="C925" s="5" t="s">
+        <v>2517</v>
+      </c>
+      <c r="D925" s="5" t="s">
         <v>2518</v>
-      </c>
-      <c r="C925" s="5" t="s">
-        <v>2519</v>
-      </c>
-      <c r="D925" s="5" t="s">
-        <v>2520</v>
       </c>
       <c r="E925" s="3">
         <v>1</v>
@@ -26217,13 +26205,13 @@
         <v>925</v>
       </c>
       <c r="B926" s="5" t="s">
+        <v>2519</v>
+      </c>
+      <c r="C926" s="5" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D926" s="5" t="s">
         <v>2521</v>
-      </c>
-      <c r="C926" s="5" t="s">
-        <v>2522</v>
-      </c>
-      <c r="D926" s="5" t="s">
-        <v>2523</v>
       </c>
       <c r="E926" s="3">
         <v>1</v>
@@ -26234,13 +26222,13 @@
         <v>926</v>
       </c>
       <c r="B927" s="5" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C927" s="5" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D927" s="5" t="s">
         <v>2524</v>
-      </c>
-      <c r="C927" s="5" t="s">
-        <v>2525</v>
-      </c>
-      <c r="D927" s="5" t="s">
-        <v>2526</v>
       </c>
       <c r="E927" s="3">
         <v>1</v>
@@ -26251,13 +26239,13 @@
         <v>927</v>
       </c>
       <c r="B928" s="5" t="s">
+        <v>2525</v>
+      </c>
+      <c r="C928" s="5" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D928" s="5" t="s">
         <v>2527</v>
-      </c>
-      <c r="C928" s="5" t="s">
-        <v>2528</v>
-      </c>
-      <c r="D928" s="5" t="s">
-        <v>2529</v>
       </c>
       <c r="E928" s="3">
         <v>1</v>
@@ -26268,13 +26256,13 @@
         <v>928</v>
       </c>
       <c r="B929" s="5" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C929" s="5" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D929" s="5" t="s">
         <v>2530</v>
-      </c>
-      <c r="C929" s="5" t="s">
-        <v>2531</v>
-      </c>
-      <c r="D929" s="5" t="s">
-        <v>2532</v>
       </c>
       <c r="E929" s="3">
         <v>1</v>
@@ -26285,13 +26273,13 @@
         <v>929</v>
       </c>
       <c r="B930" s="5" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C930" s="5" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D930" s="5" t="s">
         <v>2533</v>
-      </c>
-      <c r="C930" s="5" t="s">
-        <v>2534</v>
-      </c>
-      <c r="D930" s="5" t="s">
-        <v>2535</v>
       </c>
       <c r="E930" s="3">
         <v>1</v>
@@ -26319,13 +26307,13 @@
         <v>931</v>
       </c>
       <c r="B932" s="5" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C932" s="5" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D932" s="5" t="s">
         <v>2536</v>
-      </c>
-      <c r="C932" s="5" t="s">
-        <v>2537</v>
-      </c>
-      <c r="D932" s="5" t="s">
-        <v>2538</v>
       </c>
       <c r="E932" s="3">
         <v>1</v>
@@ -26336,13 +26324,13 @@
         <v>932</v>
       </c>
       <c r="B933" s="5" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C933" s="5" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D933" s="5" t="s">
         <v>2539</v>
-      </c>
-      <c r="C933" s="5" t="s">
-        <v>2540</v>
-      </c>
-      <c r="D933" s="5" t="s">
-        <v>2541</v>
       </c>
       <c r="E933" s="3">
         <v>1</v>
@@ -26353,13 +26341,13 @@
         <v>933</v>
       </c>
       <c r="B934" s="5" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C934" s="5" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D934" s="5" t="s">
         <v>2542</v>
-      </c>
-      <c r="C934" s="5" t="s">
-        <v>2543</v>
-      </c>
-      <c r="D934" s="5" t="s">
-        <v>2544</v>
       </c>
       <c r="E934" s="3">
         <v>1</v>
@@ -26370,13 +26358,13 @@
         <v>934</v>
       </c>
       <c r="B935" s="5" t="s">
+        <v>2543</v>
+      </c>
+      <c r="C935" s="5" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D935" s="5" t="s">
         <v>2545</v>
-      </c>
-      <c r="C935" s="5" t="s">
-        <v>2546</v>
-      </c>
-      <c r="D935" s="5" t="s">
-        <v>2547</v>
       </c>
       <c r="E935" s="3">
         <v>1</v>
@@ -26387,13 +26375,13 @@
         <v>935</v>
       </c>
       <c r="B936" s="5" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C936" s="5" t="s">
+        <v>2547</v>
+      </c>
+      <c r="D936" s="5" t="s">
         <v>2548</v>
-      </c>
-      <c r="C936" s="5" t="s">
-        <v>2549</v>
-      </c>
-      <c r="D936" s="5" t="s">
-        <v>2550</v>
       </c>
       <c r="E936" s="3">
         <v>1</v>
@@ -26404,13 +26392,13 @@
         <v>936</v>
       </c>
       <c r="B937" s="5" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C937" s="5" t="s">
+        <v>2550</v>
+      </c>
+      <c r="D937" s="5" t="s">
         <v>2551</v>
-      </c>
-      <c r="C937" s="5" t="s">
-        <v>2552</v>
-      </c>
-      <c r="D937" s="5" t="s">
-        <v>2553</v>
       </c>
       <c r="E937" s="3">
         <v>1</v>
@@ -26438,13 +26426,13 @@
         <v>938</v>
       </c>
       <c r="B939" s="5" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C939" s="5" t="s">
+        <v>2553</v>
+      </c>
+      <c r="D939" s="5" t="s">
         <v>2554</v>
-      </c>
-      <c r="C939" s="5" t="s">
-        <v>2555</v>
-      </c>
-      <c r="D939" s="5" t="s">
-        <v>2556</v>
       </c>
       <c r="E939" s="3">
         <v>1</v>
@@ -26455,13 +26443,13 @@
         <v>939</v>
       </c>
       <c r="B940" s="5" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C940" s="5" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D940" s="5" t="s">
         <v>2557</v>
-      </c>
-      <c r="C940" s="5" t="s">
-        <v>2558</v>
-      </c>
-      <c r="D940" s="5" t="s">
-        <v>2559</v>
       </c>
       <c r="E940" s="3">
         <v>1</v>
@@ -26472,13 +26460,13 @@
         <v>940</v>
       </c>
       <c r="B941" s="5" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C941" s="5" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D941" s="5" t="s">
         <v>2560</v>
-      </c>
-      <c r="C941" s="5" t="s">
-        <v>2561</v>
-      </c>
-      <c r="D941" s="5" t="s">
-        <v>2562</v>
       </c>
       <c r="E941" s="3">
         <v>1</v>
@@ -26489,13 +26477,13 @@
         <v>941</v>
       </c>
       <c r="B942" s="5" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C942" s="5" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D942" s="5" t="s">
         <v>2563</v>
-      </c>
-      <c r="C942" s="5" t="s">
-        <v>2564</v>
-      </c>
-      <c r="D942" s="5" t="s">
-        <v>2565</v>
       </c>
       <c r="E942" s="3">
         <v>1</v>
@@ -26506,13 +26494,13 @@
         <v>942</v>
       </c>
       <c r="B943" s="5" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C943" s="5" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D943" s="5" t="s">
         <v>2566</v>
-      </c>
-      <c r="C943" s="5" t="s">
-        <v>2567</v>
-      </c>
-      <c r="D943" s="5" t="s">
-        <v>2568</v>
       </c>
       <c r="E943" s="3">
         <v>1</v>
@@ -26523,13 +26511,13 @@
         <v>943</v>
       </c>
       <c r="B944" s="5" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="C944" s="5" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="D944" s="5" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="E944" s="3">
         <v>1</v>
@@ -26540,13 +26528,13 @@
         <v>944</v>
       </c>
       <c r="B945" s="5" t="s">
+        <v>2569</v>
+      </c>
+      <c r="C945" s="5" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D945" s="5" t="s">
         <v>2571</v>
-      </c>
-      <c r="C945" s="5" t="s">
-        <v>2572</v>
-      </c>
-      <c r="D945" s="5" t="s">
-        <v>2573</v>
       </c>
       <c r="E945" s="3">
         <v>1</v>
@@ -26557,13 +26545,13 @@
         <v>945</v>
       </c>
       <c r="B946" s="5" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C946" s="5" t="s">
+        <v>2573</v>
+      </c>
+      <c r="D946" s="5" t="s">
         <v>2574</v>
-      </c>
-      <c r="C946" s="5" t="s">
-        <v>2575</v>
-      </c>
-      <c r="D946" s="5" t="s">
-        <v>2576</v>
       </c>
       <c r="E946" s="3">
         <v>1</v>
@@ -26574,13 +26562,13 @@
         <v>946</v>
       </c>
       <c r="B947" s="5" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C947" s="5" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D947" s="5" t="s">
         <v>2577</v>
-      </c>
-      <c r="C947" s="5" t="s">
-        <v>2578</v>
-      </c>
-      <c r="D947" s="5" t="s">
-        <v>2579</v>
       </c>
       <c r="E947" s="3">
         <v>1</v>
@@ -26591,13 +26579,13 @@
         <v>947</v>
       </c>
       <c r="B948" s="5" t="s">
+        <v>2578</v>
+      </c>
+      <c r="C948" s="5" t="s">
+        <v>2579</v>
+      </c>
+      <c r="D948" s="5" t="s">
         <v>2580</v>
-      </c>
-      <c r="C948" s="5" t="s">
-        <v>2581</v>
-      </c>
-      <c r="D948" s="5" t="s">
-        <v>2582</v>
       </c>
       <c r="E948" s="3">
         <v>1</v>
@@ -26608,13 +26596,13 @@
         <v>948</v>
       </c>
       <c r="B949" s="5" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C949" s="5" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D949" s="5" t="s">
         <v>2583</v>
-      </c>
-      <c r="C949" s="5" t="s">
-        <v>2584</v>
-      </c>
-      <c r="D949" s="5" t="s">
-        <v>2585</v>
       </c>
       <c r="E949" s="3">
         <v>1</v>
@@ -26625,13 +26613,13 @@
         <v>949</v>
       </c>
       <c r="B950" s="5" t="s">
+        <v>2584</v>
+      </c>
+      <c r="C950" s="5" t="s">
+        <v>2585</v>
+      </c>
+      <c r="D950" s="5" t="s">
         <v>2586</v>
-      </c>
-      <c r="C950" s="5" t="s">
-        <v>2587</v>
-      </c>
-      <c r="D950" s="5" t="s">
-        <v>2588</v>
       </c>
       <c r="E950" s="3">
         <v>1</v>
@@ -26642,13 +26630,13 @@
         <v>950</v>
       </c>
       <c r="B951" s="5" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C951" s="5" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D951" s="5" t="s">
         <v>2589</v>
-      </c>
-      <c r="C951" s="5" t="s">
-        <v>2590</v>
-      </c>
-      <c r="D951" s="5" t="s">
-        <v>2591</v>
       </c>
       <c r="E951" s="3">
         <v>1</v>
@@ -26659,13 +26647,13 @@
         <v>951</v>
       </c>
       <c r="B952" s="5" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C952" s="5" t="s">
+        <v>2591</v>
+      </c>
+      <c r="D952" s="5" t="s">
         <v>2592</v>
-      </c>
-      <c r="C952" s="5" t="s">
-        <v>2593</v>
-      </c>
-      <c r="D952" s="5" t="s">
-        <v>2594</v>
       </c>
       <c r="E952" s="3">
         <v>1</v>
@@ -26676,13 +26664,13 @@
         <v>952</v>
       </c>
       <c r="B953" s="5" t="s">
+        <v>2593</v>
+      </c>
+      <c r="C953" s="5" t="s">
+        <v>2594</v>
+      </c>
+      <c r="D953" s="5" t="s">
         <v>2595</v>
-      </c>
-      <c r="C953" s="5" t="s">
-        <v>2596</v>
-      </c>
-      <c r="D953" s="5" t="s">
-        <v>2597</v>
       </c>
       <c r="E953" s="3">
         <v>1</v>
@@ -26693,13 +26681,13 @@
         <v>953</v>
       </c>
       <c r="B954" s="5" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C954" s="5" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D954" s="5" t="s">
         <v>2598</v>
-      </c>
-      <c r="C954" s="5" t="s">
-        <v>2599</v>
-      </c>
-      <c r="D954" s="5" t="s">
-        <v>2600</v>
       </c>
       <c r="E954" s="3">
         <v>1</v>
@@ -26710,13 +26698,13 @@
         <v>954</v>
       </c>
       <c r="B955" s="5" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C955" s="5" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D955" s="5" t="s">
         <v>2601</v>
-      </c>
-      <c r="C955" s="5" t="s">
-        <v>2602</v>
-      </c>
-      <c r="D955" s="5" t="s">
-        <v>2603</v>
       </c>
       <c r="E955" s="3">
         <v>1</v>
@@ -26778,13 +26766,13 @@
         <v>958</v>
       </c>
       <c r="B959" s="5" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C959" s="5" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D959" s="5" t="s">
         <v>2604</v>
-      </c>
-      <c r="C959" s="5" t="s">
-        <v>2605</v>
-      </c>
-      <c r="D959" s="5" t="s">
-        <v>2606</v>
       </c>
       <c r="E959" s="3">
         <v>1</v>
@@ -26812,13 +26800,13 @@
         <v>960</v>
       </c>
       <c r="B961" s="5" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C961" s="5" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D961" s="5" t="s">
         <v>2607</v>
-      </c>
-      <c r="C961" s="5" t="s">
-        <v>2608</v>
-      </c>
-      <c r="D961" s="5" t="s">
-        <v>2609</v>
       </c>
       <c r="E961" s="3">
         <v>1</v>
@@ -26829,13 +26817,13 @@
         <v>961</v>
       </c>
       <c r="B962" s="5" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C962" s="5" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D962" s="5" t="s">
         <v>2610</v>
-      </c>
-      <c r="C962" s="5" t="s">
-        <v>2611</v>
-      </c>
-      <c r="D962" s="5" t="s">
-        <v>2612</v>
       </c>
       <c r="E962" s="3">
         <v>1</v>
@@ -26863,13 +26851,13 @@
         <v>963</v>
       </c>
       <c r="B964" s="5" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C964" s="5" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D964" s="5" t="s">
         <v>2613</v>
-      </c>
-      <c r="C964" s="5" t="s">
-        <v>2614</v>
-      </c>
-      <c r="D964" s="5" t="s">
-        <v>2615</v>
       </c>
       <c r="E964" s="3">
         <v>1</v>
@@ -26880,13 +26868,13 @@
         <v>964</v>
       </c>
       <c r="B965" s="5" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C965" s="5" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D965" s="5" t="s">
         <v>2616</v>
-      </c>
-      <c r="C965" s="5" t="s">
-        <v>2617</v>
-      </c>
-      <c r="D965" s="5" t="s">
-        <v>2618</v>
       </c>
       <c r="E965" s="3">
         <v>1</v>
@@ -26897,13 +26885,13 @@
         <v>965</v>
       </c>
       <c r="B966" s="5" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C966" s="5" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D966" s="5" t="s">
         <v>2619</v>
-      </c>
-      <c r="C966" s="5" t="s">
-        <v>2620</v>
-      </c>
-      <c r="D966" s="5" t="s">
-        <v>2621</v>
       </c>
       <c r="E966" s="3">
         <v>1</v>
@@ -26914,13 +26902,13 @@
         <v>966</v>
       </c>
       <c r="B967" s="5" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C967" s="5" t="s">
+        <v>2621</v>
+      </c>
+      <c r="D967" s="5" t="s">
         <v>2622</v>
-      </c>
-      <c r="C967" s="5" t="s">
-        <v>2623</v>
-      </c>
-      <c r="D967" s="5" t="s">
-        <v>2624</v>
       </c>
       <c r="E967" s="3">
         <v>1</v>
@@ -26931,13 +26919,13 @@
         <v>967</v>
       </c>
       <c r="B968" s="5" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C968" s="5" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D968" s="5" t="s">
         <v>2625</v>
-      </c>
-      <c r="C968" s="5" t="s">
-        <v>2626</v>
-      </c>
-      <c r="D968" s="5" t="s">
-        <v>2627</v>
       </c>
       <c r="E968" s="3">
         <v>1</v>
@@ -26948,13 +26936,13 @@
         <v>968</v>
       </c>
       <c r="B969" s="5" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C969" s="5" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D969" s="5" t="s">
         <v>2628</v>
-      </c>
-      <c r="C969" s="5" t="s">
-        <v>2629</v>
-      </c>
-      <c r="D969" s="5" t="s">
-        <v>2630</v>
       </c>
       <c r="E969" s="3">
         <v>1</v>
@@ -26965,11 +26953,11 @@
         <v>969</v>
       </c>
       <c r="B970" s="5" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="C970" s="5"/>
       <c r="D970" s="5" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="E970" s="3">
         <v>1</v>
@@ -26980,13 +26968,13 @@
         <v>970</v>
       </c>
       <c r="B971" s="5" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C971" s="5" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D971" s="5" t="s">
         <v>2633</v>
-      </c>
-      <c r="C971" s="5" t="s">
-        <v>2634</v>
-      </c>
-      <c r="D971" s="5" t="s">
-        <v>2635</v>
       </c>
       <c r="E971" s="3">
         <v>1</v>
@@ -26997,13 +26985,13 @@
         <v>971</v>
       </c>
       <c r="B972" s="5" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="C972" s="5" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="D972" s="5" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="E972" s="3">
         <v>1</v>
@@ -27014,13 +27002,13 @@
         <v>972</v>
       </c>
       <c r="B973" s="5" t="s">
+        <v>2635</v>
+      </c>
+      <c r="C973" s="5" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D973" s="5" t="s">
         <v>2637</v>
-      </c>
-      <c r="C973" s="5" t="s">
-        <v>2638</v>
-      </c>
-      <c r="D973" s="5" t="s">
-        <v>2639</v>
       </c>
       <c r="E973" s="3">
         <v>1</v>
@@ -27031,13 +27019,13 @@
         <v>973</v>
       </c>
       <c r="B974" s="5" t="s">
+        <v>2638</v>
+      </c>
+      <c r="C974" s="5" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D974" s="5" t="s">
         <v>2640</v>
-      </c>
-      <c r="C974" s="5" t="s">
-        <v>2641</v>
-      </c>
-      <c r="D974" s="5" t="s">
-        <v>2642</v>
       </c>
       <c r="E974" s="3">
         <v>1</v>
@@ -27048,13 +27036,13 @@
         <v>974</v>
       </c>
       <c r="B975" s="5" t="s">
+        <v>2641</v>
+      </c>
+      <c r="C975" s="5" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D975" s="5" t="s">
         <v>2643</v>
-      </c>
-      <c r="C975" s="5" t="s">
-        <v>2644</v>
-      </c>
-      <c r="D975" s="5" t="s">
-        <v>2645</v>
       </c>
       <c r="E975" s="3">
         <v>1</v>
@@ -27065,13 +27053,13 @@
         <v>975</v>
       </c>
       <c r="B976" s="5" t="s">
+        <v>2644</v>
+      </c>
+      <c r="C976" s="5" t="s">
+        <v>2645</v>
+      </c>
+      <c r="D976" s="5" t="s">
         <v>2646</v>
-      </c>
-      <c r="C976" s="5" t="s">
-        <v>2647</v>
-      </c>
-      <c r="D976" s="5" t="s">
-        <v>2648</v>
       </c>
       <c r="E976" s="3">
         <v>1</v>
@@ -27082,13 +27070,13 @@
         <v>976</v>
       </c>
       <c r="B977" s="5" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C977" s="5" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D977" s="5" t="s">
         <v>2649</v>
-      </c>
-      <c r="C977" s="5" t="s">
-        <v>2650</v>
-      </c>
-      <c r="D977" s="5" t="s">
-        <v>2651</v>
       </c>
       <c r="E977" s="3">
         <v>1</v>
@@ -27099,13 +27087,13 @@
         <v>977</v>
       </c>
       <c r="B978" s="5" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C978" s="5" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D978" s="5" t="s">
         <v>2652</v>
-      </c>
-      <c r="C978" s="5" t="s">
-        <v>2653</v>
-      </c>
-      <c r="D978" s="5" t="s">
-        <v>2654</v>
       </c>
       <c r="E978" s="3">
         <v>1</v>
@@ -27116,13 +27104,13 @@
         <v>978</v>
       </c>
       <c r="B979" s="5" t="s">
+        <v>2653</v>
+      </c>
+      <c r="C979" s="5" t="s">
+        <v>2654</v>
+      </c>
+      <c r="D979" s="5" t="s">
         <v>2655</v>
-      </c>
-      <c r="C979" s="5" t="s">
-        <v>2656</v>
-      </c>
-      <c r="D979" s="5" t="s">
-        <v>2657</v>
       </c>
       <c r="E979" s="3">
         <v>1</v>
@@ -27133,13 +27121,13 @@
         <v>979</v>
       </c>
       <c r="B980" s="5" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C980" s="5" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D980" s="5" t="s">
         <v>2658</v>
-      </c>
-      <c r="C980" s="5" t="s">
-        <v>2659</v>
-      </c>
-      <c r="D980" s="5" t="s">
-        <v>2660</v>
       </c>
       <c r="E980" s="3">
         <v>1</v>
@@ -27167,13 +27155,13 @@
         <v>981</v>
       </c>
       <c r="B982" s="5" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C982" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D982" s="5" t="s">
         <v>2661</v>
-      </c>
-      <c r="C982" s="5" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D982" s="5" t="s">
-        <v>2663</v>
       </c>
       <c r="E982" s="3">
         <v>1</v>
@@ -27184,13 +27172,13 @@
         <v>982</v>
       </c>
       <c r="B983" s="5" t="s">
+        <v>2662</v>
+      </c>
+      <c r="C983" s="5" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D983" s="5" t="s">
         <v>2664</v>
-      </c>
-      <c r="C983" s="5" t="s">
-        <v>2665</v>
-      </c>
-      <c r="D983" s="5" t="s">
-        <v>2666</v>
       </c>
       <c r="E983" s="3">
         <v>1</v>
@@ -27201,13 +27189,13 @@
         <v>983</v>
       </c>
       <c r="B984" s="5" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C984" s="5" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D984" s="5" t="s">
         <v>2667</v>
-      </c>
-      <c r="C984" s="5" t="s">
-        <v>2668</v>
-      </c>
-      <c r="D984" s="5" t="s">
-        <v>2669</v>
       </c>
       <c r="E984" s="3">
         <v>1</v>
@@ -27218,13 +27206,13 @@
         <v>984</v>
       </c>
       <c r="B985" s="5" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C985" s="5" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D985" s="5" t="s">
         <v>2670</v>
-      </c>
-      <c r="C985" s="5" t="s">
-        <v>2671</v>
-      </c>
-      <c r="D985" s="5" t="s">
-        <v>2672</v>
       </c>
       <c r="E985" s="3">
         <v>1</v>
@@ -27235,13 +27223,13 @@
         <v>985</v>
       </c>
       <c r="B986" s="5" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C986" s="5" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D986" s="5" t="s">
         <v>2673</v>
-      </c>
-      <c r="C986" s="5" t="s">
-        <v>2674</v>
-      </c>
-      <c r="D986" s="5" t="s">
-        <v>2675</v>
       </c>
       <c r="E986" s="3">
         <v>1</v>
@@ -27269,13 +27257,13 @@
         <v>987</v>
       </c>
       <c r="B988" s="5" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C988" s="5" t="s">
+        <v>2675</v>
+      </c>
+      <c r="D988" s="5" t="s">
         <v>2676</v>
-      </c>
-      <c r="C988" s="5" t="s">
-        <v>2677</v>
-      </c>
-      <c r="D988" s="5" t="s">
-        <v>2678</v>
       </c>
       <c r="E988" s="3">
         <v>1</v>
@@ -27286,13 +27274,13 @@
         <v>988</v>
       </c>
       <c r="B989" s="5" t="s">
+        <v>2677</v>
+      </c>
+      <c r="C989" s="5" t="s">
+        <v>2678</v>
+      </c>
+      <c r="D989" s="5" t="s">
         <v>2679</v>
-      </c>
-      <c r="C989" s="5" t="s">
-        <v>2680</v>
-      </c>
-      <c r="D989" s="5" t="s">
-        <v>2681</v>
       </c>
       <c r="E989" s="3">
         <v>1</v>
@@ -27303,13 +27291,13 @@
         <v>989</v>
       </c>
       <c r="B990" s="5" t="s">
+        <v>2680</v>
+      </c>
+      <c r="C990" s="5" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D990" s="5" t="s">
         <v>2682</v>
-      </c>
-      <c r="C990" s="5" t="s">
-        <v>2683</v>
-      </c>
-      <c r="D990" s="5" t="s">
-        <v>2684</v>
       </c>
       <c r="E990" s="3">
         <v>1</v>
@@ -27337,13 +27325,13 @@
         <v>991</v>
       </c>
       <c r="B992" s="5" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C992" s="5" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D992" s="5" t="s">
         <v>2685</v>
-      </c>
-      <c r="C992" s="5" t="s">
-        <v>2686</v>
-      </c>
-      <c r="D992" s="5" t="s">
-        <v>2687</v>
       </c>
       <c r="E992" s="3">
         <v>1</v>
@@ -27354,13 +27342,13 @@
         <v>992</v>
       </c>
       <c r="B993" s="5" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C993" s="5" t="s">
+        <v>2687</v>
+      </c>
+      <c r="D993" s="5" t="s">
         <v>2688</v>
-      </c>
-      <c r="C993" s="5" t="s">
-        <v>2689</v>
-      </c>
-      <c r="D993" s="5" t="s">
-        <v>2690</v>
       </c>
       <c r="E993" s="3">
         <v>1</v>
@@ -27371,13 +27359,13 @@
         <v>993</v>
       </c>
       <c r="B994" s="5" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C994" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D994" s="5" t="s">
         <v>2691</v>
-      </c>
-      <c r="C994" s="5" t="s">
-        <v>2692</v>
-      </c>
-      <c r="D994" s="5" t="s">
-        <v>2693</v>
       </c>
       <c r="E994" s="3">
         <v>1</v>
@@ -27388,13 +27376,13 @@
         <v>994</v>
       </c>
       <c r="B995" s="5" t="s">
+        <v>2692</v>
+      </c>
+      <c r="C995" s="5" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D995" s="5" t="s">
         <v>2694</v>
-      </c>
-      <c r="C995" s="5" t="s">
-        <v>2695</v>
-      </c>
-      <c r="D995" s="5" t="s">
-        <v>2696</v>
       </c>
       <c r="E995" s="3">
         <v>1</v>
@@ -27405,13 +27393,13 @@
         <v>995</v>
       </c>
       <c r="B996" s="5" t="s">
+        <v>2695</v>
+      </c>
+      <c r="C996" s="5" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D996" s="5" t="s">
         <v>2697</v>
-      </c>
-      <c r="C996" s="5" t="s">
-        <v>2698</v>
-      </c>
-      <c r="D996" s="5" t="s">
-        <v>2699</v>
       </c>
       <c r="E996" s="3">
         <v>1</v>
@@ -27422,13 +27410,13 @@
         <v>996</v>
       </c>
       <c r="B997" s="5" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C997" s="5" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D997" s="5" t="s">
         <v>2700</v>
-      </c>
-      <c r="C997" s="5" t="s">
-        <v>2701</v>
-      </c>
-      <c r="D997" s="5" t="s">
-        <v>2702</v>
       </c>
       <c r="E997" s="3">
         <v>1</v>
@@ -27439,13 +27427,13 @@
         <v>997</v>
       </c>
       <c r="B998" s="5" t="s">
+        <v>2701</v>
+      </c>
+      <c r="C998" s="5" t="s">
+        <v>2702</v>
+      </c>
+      <c r="D998" s="5" t="s">
         <v>2703</v>
-      </c>
-      <c r="C998" s="5" t="s">
-        <v>2704</v>
-      </c>
-      <c r="D998" s="5" t="s">
-        <v>2705</v>
       </c>
       <c r="E998" s="3">
         <v>1</v>
@@ -27456,13 +27444,13 @@
         <v>998</v>
       </c>
       <c r="B999" s="5" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C999" s="5" t="s">
+        <v>2705</v>
+      </c>
+      <c r="D999" s="5" t="s">
         <v>2706</v>
-      </c>
-      <c r="C999" s="5" t="s">
-        <v>2707</v>
-      </c>
-      <c r="D999" s="5" t="s">
-        <v>2708</v>
       </c>
       <c r="E999" s="3">
         <v>1</v>
@@ -27473,13 +27461,13 @@
         <v>999</v>
       </c>
       <c r="B1000" s="5" t="s">
+        <v>2707</v>
+      </c>
+      <c r="C1000" s="5" t="s">
+        <v>2708</v>
+      </c>
+      <c r="D1000" s="5" t="s">
         <v>2709</v>
-      </c>
-      <c r="C1000" s="5" t="s">
-        <v>2710</v>
-      </c>
-      <c r="D1000" s="5" t="s">
-        <v>2711</v>
       </c>
       <c r="E1000" s="3">
         <v>1</v>
@@ -27490,13 +27478,13 @@
         <v>1000</v>
       </c>
       <c r="B1001" s="5" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C1001" s="5" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D1001" s="5" t="s">
         <v>2712</v>
-      </c>
-      <c r="C1001" s="5" t="s">
-        <v>2713</v>
-      </c>
-      <c r="D1001" s="5" t="s">
-        <v>2714</v>
       </c>
       <c r="E1001" s="3">
         <v>1</v>
@@ -27513,7 +27501,7 @@
         <v>1601</v>
       </c>
       <c r="D1002" s="5" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="E1002" s="3">
         <v>1</v>
@@ -27541,13 +27529,13 @@
         <v>1003</v>
       </c>
       <c r="B1004" s="5" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C1004" s="5" t="s">
+        <v>2715</v>
+      </c>
+      <c r="D1004" s="5" t="s">
         <v>2716</v>
-      </c>
-      <c r="C1004" s="5" t="s">
-        <v>2717</v>
-      </c>
-      <c r="D1004" s="5" t="s">
-        <v>2718</v>
       </c>
       <c r="E1004" s="3">
         <v>1</v>
@@ -27558,11 +27546,11 @@
         <v>1004</v>
       </c>
       <c r="B1005" s="5" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="C1005" s="5"/>
       <c r="D1005" s="5" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="E1005" s="3">
         <v>1</v>
@@ -27573,13 +27561,13 @@
         <v>1005</v>
       </c>
       <c r="B1006" s="5" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1006" s="5" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D1006" s="5" t="s">
         <v>2721</v>
-      </c>
-      <c r="C1006" s="5" t="s">
-        <v>2722</v>
-      </c>
-      <c r="D1006" s="5" t="s">
-        <v>2723</v>
       </c>
       <c r="E1006" s="3">
         <v>1</v>
@@ -27590,13 +27578,13 @@
         <v>1006</v>
       </c>
       <c r="B1007" s="5" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C1007" s="5" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D1007" s="5" t="s">
         <v>2724</v>
-      </c>
-      <c r="C1007" s="5" t="s">
-        <v>2725</v>
-      </c>
-      <c r="D1007" s="5" t="s">
-        <v>2726</v>
       </c>
       <c r="E1007" s="3">
         <v>1</v>
@@ -27607,13 +27595,13 @@
         <v>1007</v>
       </c>
       <c r="B1008" s="5" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C1008" s="5" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D1008" s="5" t="s">
         <v>2727</v>
-      </c>
-      <c r="C1008" s="5" t="s">
-        <v>2728</v>
-      </c>
-      <c r="D1008" s="5" t="s">
-        <v>2729</v>
       </c>
       <c r="E1008" s="3">
         <v>1</v>
@@ -27624,13 +27612,13 @@
         <v>1008</v>
       </c>
       <c r="B1009" s="5" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C1009" s="5" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D1009" s="5" t="s">
         <v>2730</v>
-      </c>
-      <c r="C1009" s="5" t="s">
-        <v>2731</v>
-      </c>
-      <c r="D1009" s="5" t="s">
-        <v>2732</v>
       </c>
       <c r="E1009" s="3">
         <v>1</v>
@@ -27641,13 +27629,13 @@
         <v>1009</v>
       </c>
       <c r="B1010" s="5" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C1010" s="5" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D1010" s="5" t="s">
         <v>2733</v>
-      </c>
-      <c r="C1010" s="5" t="s">
-        <v>2734</v>
-      </c>
-      <c r="D1010" s="5" t="s">
-        <v>2735</v>
       </c>
       <c r="E1010" s="3">
         <v>1</v>
@@ -27658,13 +27646,13 @@
         <v>1010</v>
       </c>
       <c r="B1011" s="5" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C1011" s="5" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D1011" s="5" t="s">
         <v>2736</v>
-      </c>
-      <c r="C1011" s="5" t="s">
-        <v>2737</v>
-      </c>
-      <c r="D1011" s="5" t="s">
-        <v>2738</v>
       </c>
       <c r="E1011" s="3">
         <v>1</v>
@@ -27675,13 +27663,13 @@
         <v>1011</v>
       </c>
       <c r="B1012" s="5" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C1012" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="D1012" s="5" t="s">
         <v>2739</v>
-      </c>
-      <c r="C1012" s="5" t="s">
-        <v>2740</v>
-      </c>
-      <c r="D1012" s="5" t="s">
-        <v>2741</v>
       </c>
       <c r="E1012" s="3">
         <v>1</v>
@@ -27692,13 +27680,13 @@
         <v>1012</v>
       </c>
       <c r="B1013" s="5" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C1013" s="5" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D1013" s="5" t="s">
         <v>2742</v>
-      </c>
-      <c r="C1013" s="5" t="s">
-        <v>2743</v>
-      </c>
-      <c r="D1013" s="5" t="s">
-        <v>2744</v>
       </c>
       <c r="E1013" s="3">
         <v>1</v>
@@ -27709,13 +27697,13 @@
         <v>1013</v>
       </c>
       <c r="B1014" s="5" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="C1014" s="5" t="s">
         <v>641</v>
       </c>
       <c r="D1014" s="5" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="E1014" s="3">
         <v>1</v>
@@ -27732,7 +27720,7 @@
         <v>1589</v>
       </c>
       <c r="D1015" s="5" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
       <c r="E1015" s="3">
         <v>1</v>
@@ -27743,13 +27731,13 @@
         <v>1015</v>
       </c>
       <c r="B1016" s="5" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C1016" s="5" t="s">
+        <v>2747</v>
+      </c>
+      <c r="D1016" s="5" t="s">
         <v>2748</v>
-      </c>
-      <c r="C1016" s="5" t="s">
-        <v>2749</v>
-      </c>
-      <c r="D1016" s="5" t="s">
-        <v>2750</v>
       </c>
       <c r="E1016" s="3">
         <v>1</v>
@@ -27760,13 +27748,13 @@
         <v>1016</v>
       </c>
       <c r="B1017" s="5" t="s">
+        <v>2749</v>
+      </c>
+      <c r="C1017" s="5" t="s">
+        <v>2750</v>
+      </c>
+      <c r="D1017" s="5" t="s">
         <v>2751</v>
-      </c>
-      <c r="C1017" s="5" t="s">
-        <v>2752</v>
-      </c>
-      <c r="D1017" s="5" t="s">
-        <v>2753</v>
       </c>
       <c r="E1017" s="3">
         <v>1</v>
@@ -27777,13 +27765,13 @@
         <v>1017</v>
       </c>
       <c r="B1018" s="5" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C1018" s="5" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D1018" s="5" t="s">
         <v>2754</v>
-      </c>
-      <c r="C1018" s="5" t="s">
-        <v>2755</v>
-      </c>
-      <c r="D1018" s="5" t="s">
-        <v>2756</v>
       </c>
       <c r="E1018" s="3">
         <v>1</v>
@@ -27794,13 +27782,13 @@
         <v>1018</v>
       </c>
       <c r="B1019" s="5" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C1019" s="5" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D1019" s="5" t="s">
         <v>2757</v>
-      </c>
-      <c r="C1019" s="5" t="s">
-        <v>2758</v>
-      </c>
-      <c r="D1019" s="5" t="s">
-        <v>2759</v>
       </c>
       <c r="E1019" s="3">
         <v>1</v>
@@ -27811,13 +27799,13 @@
         <v>1019</v>
       </c>
       <c r="B1020" s="5" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C1020" s="5" t="s">
+        <v>2759</v>
+      </c>
+      <c r="D1020" s="5" t="s">
         <v>2760</v>
-      </c>
-      <c r="C1020" s="5" t="s">
-        <v>2761</v>
-      </c>
-      <c r="D1020" s="5" t="s">
-        <v>2762</v>
       </c>
       <c r="E1020" s="3">
         <v>1</v>
@@ -27828,13 +27816,13 @@
         <v>1020</v>
       </c>
       <c r="B1021" s="5" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C1021" s="5" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D1021" s="5" t="s">
         <v>2763</v>
-      </c>
-      <c r="C1021" s="5" t="s">
-        <v>2764</v>
-      </c>
-      <c r="D1021" s="5" t="s">
-        <v>2765</v>
       </c>
       <c r="E1021" s="3">
         <v>1</v>
@@ -27845,13 +27833,13 @@
         <v>1021</v>
       </c>
       <c r="B1022" s="5" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C1022" s="5" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D1022" s="5" t="s">
         <v>2766</v>
-      </c>
-      <c r="C1022" s="5" t="s">
-        <v>2767</v>
-      </c>
-      <c r="D1022" s="5" t="s">
-        <v>2768</v>
       </c>
       <c r="E1022" s="3">
         <v>1</v>
@@ -27862,13 +27850,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" s="5" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C1023" s="5" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D1023" s="5" t="s">
         <v>2769</v>
-      </c>
-      <c r="C1023" s="5" t="s">
-        <v>2770</v>
-      </c>
-      <c r="D1023" s="5" t="s">
-        <v>2771</v>
       </c>
       <c r="E1023" s="3">
         <v>1</v>
@@ -27879,13 +27867,13 @@
         <v>1023</v>
       </c>
       <c r="B1024" s="5" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C1024" s="5" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D1024" s="5" t="s">
         <v>2772</v>
-      </c>
-      <c r="C1024" s="5" t="s">
-        <v>2773</v>
-      </c>
-      <c r="D1024" s="5" t="s">
-        <v>2774</v>
       </c>
       <c r="E1024" s="3">
         <v>1</v>
@@ -27896,13 +27884,13 @@
         <v>1024</v>
       </c>
       <c r="B1025" s="5" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C1025" s="5" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D1025" s="5" t="s">
         <v>2775</v>
-      </c>
-      <c r="C1025" s="5" t="s">
-        <v>2776</v>
-      </c>
-      <c r="D1025" s="5" t="s">
-        <v>2777</v>
       </c>
       <c r="E1025" s="3">
         <v>1</v>
@@ -27913,13 +27901,13 @@
         <v>1025</v>
       </c>
       <c r="B1026" s="5" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C1026" s="5" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D1026" s="5" t="s">
         <v>2778</v>
-      </c>
-      <c r="C1026" s="5" t="s">
-        <v>2779</v>
-      </c>
-      <c r="D1026" s="5" t="s">
-        <v>2780</v>
       </c>
       <c r="E1026" s="3">
         <v>1</v>
@@ -27930,13 +27918,13 @@
         <v>1026</v>
       </c>
       <c r="B1027" s="5" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C1027" s="5" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D1027" s="5" t="s">
         <v>2781</v>
-      </c>
-      <c r="C1027" s="5" t="s">
-        <v>2782</v>
-      </c>
-      <c r="D1027" s="5" t="s">
-        <v>2783</v>
       </c>
       <c r="E1027" s="3">
         <v>1</v>
@@ -27947,13 +27935,13 @@
         <v>1027</v>
       </c>
       <c r="B1028" s="5" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C1028" s="5" t="s">
+        <v>2783</v>
+      </c>
+      <c r="D1028" s="5" t="s">
         <v>2784</v>
-      </c>
-      <c r="C1028" s="5" t="s">
-        <v>2785</v>
-      </c>
-      <c r="D1028" s="5" t="s">
-        <v>2786</v>
       </c>
       <c r="E1028" s="3">
         <v>1</v>
@@ -27970,7 +27958,7 @@
         <v>605</v>
       </c>
       <c r="D1029" s="5" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="E1029" s="3">
         <v>1</v>
@@ -27981,13 +27969,13 @@
         <v>1029</v>
       </c>
       <c r="B1030" s="5" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C1030" s="5" t="s">
+        <v>2787</v>
+      </c>
+      <c r="D1030" s="5" t="s">
         <v>2788</v>
-      </c>
-      <c r="C1030" s="5" t="s">
-        <v>2789</v>
-      </c>
-      <c r="D1030" s="5" t="s">
-        <v>2790</v>
       </c>
       <c r="E1030" s="3">
         <v>1</v>
@@ -27998,13 +27986,13 @@
         <v>1030</v>
       </c>
       <c r="B1031" s="5" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C1031" s="5" t="s">
+        <v>2790</v>
+      </c>
+      <c r="D1031" s="5" t="s">
         <v>2791</v>
-      </c>
-      <c r="C1031" s="5" t="s">
-        <v>2792</v>
-      </c>
-      <c r="D1031" s="5" t="s">
-        <v>2793</v>
       </c>
       <c r="E1031" s="3">
         <v>1</v>
@@ -28021,7 +28009,7 @@
         <v>32</v>
       </c>
       <c r="D1032" s="5" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="E1032" s="3">
         <v>1</v>
@@ -28049,13 +28037,13 @@
         <v>1033</v>
       </c>
       <c r="B1034" s="5" t="s">
+        <v>2793</v>
+      </c>
+      <c r="C1034" s="5" t="s">
+        <v>2794</v>
+      </c>
+      <c r="D1034" s="5" t="s">
         <v>2795</v>
-      </c>
-      <c r="C1034" s="5" t="s">
-        <v>2796</v>
-      </c>
-      <c r="D1034" s="5" t="s">
-        <v>2797</v>
       </c>
       <c r="E1034" s="3">
         <v>1</v>
@@ -28066,13 +28054,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" s="5" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C1035" s="5" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D1035" s="5" t="s">
         <v>2798</v>
-      </c>
-      <c r="C1035" s="5" t="s">
-        <v>2799</v>
-      </c>
-      <c r="D1035" s="5" t="s">
-        <v>2800</v>
       </c>
       <c r="E1035" s="3">
         <v>1</v>
@@ -28083,13 +28071,13 @@
         <v>1035</v>
       </c>
       <c r="B1036" s="5" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C1036" s="5" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D1036" s="5" t="s">
         <v>2801</v>
-      </c>
-      <c r="C1036" s="5" t="s">
-        <v>2802</v>
-      </c>
-      <c r="D1036" s="5" t="s">
-        <v>2803</v>
       </c>
       <c r="E1036" s="3">
         <v>1</v>
@@ -28100,13 +28088,13 @@
         <v>1036</v>
       </c>
       <c r="B1037" s="5" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C1037" s="5" t="s">
+        <v>2803</v>
+      </c>
+      <c r="D1037" s="5" t="s">
         <v>2804</v>
-      </c>
-      <c r="C1037" s="5" t="s">
-        <v>2805</v>
-      </c>
-      <c r="D1037" s="5" t="s">
-        <v>2806</v>
       </c>
       <c r="E1037" s="3">
         <v>1</v>
@@ -28117,13 +28105,13 @@
         <v>1037</v>
       </c>
       <c r="B1038" s="5" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C1038" s="5" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D1038" s="5" t="s">
         <v>2807</v>
-      </c>
-      <c r="C1038" s="5" t="s">
-        <v>2808</v>
-      </c>
-      <c r="D1038" s="5" t="s">
-        <v>2809</v>
       </c>
       <c r="E1038" s="3">
         <v>1</v>
@@ -28134,13 +28122,13 @@
         <v>1038</v>
       </c>
       <c r="B1039" s="5" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C1039" s="5" t="s">
+        <v>2809</v>
+      </c>
+      <c r="D1039" s="5" t="s">
         <v>2810</v>
-      </c>
-      <c r="C1039" s="5" t="s">
-        <v>2811</v>
-      </c>
-      <c r="D1039" s="5" t="s">
-        <v>2812</v>
       </c>
       <c r="E1039" s="3">
         <v>1</v>
@@ -28151,13 +28139,13 @@
         <v>1039</v>
       </c>
       <c r="B1040" s="5" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C1040" s="5" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1040" s="5" t="s">
         <v>2813</v>
-      </c>
-      <c r="C1040" s="5" t="s">
-        <v>2814</v>
-      </c>
-      <c r="D1040" s="5" t="s">
-        <v>2815</v>
       </c>
       <c r="E1040" s="3">
         <v>1</v>
@@ -28168,13 +28156,13 @@
         <v>1040</v>
       </c>
       <c r="B1041" s="5" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C1041" s="5" t="s">
+        <v>2815</v>
+      </c>
+      <c r="D1041" s="5" t="s">
         <v>2816</v>
-      </c>
-      <c r="C1041" s="5" t="s">
-        <v>2817</v>
-      </c>
-      <c r="D1041" s="5" t="s">
-        <v>2818</v>
       </c>
       <c r="E1041" s="3">
         <v>1</v>
@@ -28185,13 +28173,13 @@
         <v>1041</v>
       </c>
       <c r="B1042" s="5" t="s">
+        <v>2817</v>
+      </c>
+      <c r="C1042" s="5" t="s">
+        <v>2818</v>
+      </c>
+      <c r="D1042" s="5" t="s">
         <v>2819</v>
-      </c>
-      <c r="C1042" s="5" t="s">
-        <v>2820</v>
-      </c>
-      <c r="D1042" s="5" t="s">
-        <v>2821</v>
       </c>
       <c r="E1042" s="3">
         <v>1</v>
@@ -28202,13 +28190,13 @@
         <v>1042</v>
       </c>
       <c r="B1043" s="5" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C1043" s="5" t="s">
+        <v>2821</v>
+      </c>
+      <c r="D1043" s="5" t="s">
         <v>2822</v>
-      </c>
-      <c r="C1043" s="5" t="s">
-        <v>2823</v>
-      </c>
-      <c r="D1043" s="5" t="s">
-        <v>2824</v>
       </c>
       <c r="E1043" s="3">
         <v>1</v>
@@ -28219,13 +28207,13 @@
         <v>1043</v>
       </c>
       <c r="B1044" s="5" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C1044" s="5" t="s">
+        <v>2824</v>
+      </c>
+      <c r="D1044" s="5" t="s">
         <v>2825</v>
-      </c>
-      <c r="C1044" s="5" t="s">
-        <v>2826</v>
-      </c>
-      <c r="D1044" s="5" t="s">
-        <v>2827</v>
       </c>
       <c r="E1044" s="3">
         <v>1</v>
@@ -28236,13 +28224,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" s="5" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C1045" s="5" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D1045" s="5" t="s">
         <v>2828</v>
-      </c>
-      <c r="C1045" s="5" t="s">
-        <v>2829</v>
-      </c>
-      <c r="D1045" s="5" t="s">
-        <v>2830</v>
       </c>
       <c r="E1045" s="3">
         <v>1</v>
@@ -28270,13 +28258,13 @@
         <v>1046</v>
       </c>
       <c r="B1047" s="5" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C1047" s="5" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1047" s="5" t="s">
         <v>2831</v>
-      </c>
-      <c r="C1047" s="5" t="s">
-        <v>2832</v>
-      </c>
-      <c r="D1047" s="5" t="s">
-        <v>2833</v>
       </c>
       <c r="E1047" s="3">
         <v>1</v>
@@ -28287,13 +28275,13 @@
         <v>1047</v>
       </c>
       <c r="B1048" s="5" t="s">
+        <v>2832</v>
+      </c>
+      <c r="C1048" s="5" t="s">
+        <v>2833</v>
+      </c>
+      <c r="D1048" s="5" t="s">
         <v>2834</v>
-      </c>
-      <c r="C1048" s="5" t="s">
-        <v>2835</v>
-      </c>
-      <c r="D1048" s="5" t="s">
-        <v>2836</v>
       </c>
       <c r="E1048" s="3">
         <v>1</v>
@@ -28304,13 +28292,13 @@
         <v>1048</v>
       </c>
       <c r="B1049" s="5" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C1049" s="5" t="s">
+        <v>2836</v>
+      </c>
+      <c r="D1049" s="5" t="s">
         <v>2837</v>
-      </c>
-      <c r="C1049" s="5" t="s">
-        <v>2838</v>
-      </c>
-      <c r="D1049" s="5" t="s">
-        <v>2839</v>
       </c>
       <c r="E1049" s="3">
         <v>1</v>
@@ -28338,13 +28326,13 @@
         <v>1050</v>
       </c>
       <c r="B1051" s="5" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C1051" s="5" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D1051" s="5" t="s">
         <v>2840</v>
-      </c>
-      <c r="C1051" s="5" t="s">
-        <v>2841</v>
-      </c>
-      <c r="D1051" s="5" t="s">
-        <v>2842</v>
       </c>
       <c r="E1051" s="3">
         <v>1</v>
@@ -28355,13 +28343,13 @@
         <v>1051</v>
       </c>
       <c r="B1052" s="5" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C1052" s="5" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D1052" s="5" t="s">
         <v>2843</v>
-      </c>
-      <c r="C1052" s="5" t="s">
-        <v>2844</v>
-      </c>
-      <c r="D1052" s="5" t="s">
-        <v>2845</v>
       </c>
       <c r="E1052" s="3">
         <v>1</v>
@@ -28372,13 +28360,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" s="5" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C1053" s="5" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D1053" s="5" t="s">
         <v>2846</v>
-      </c>
-      <c r="C1053" s="5" t="s">
-        <v>2847</v>
-      </c>
-      <c r="D1053" s="5" t="s">
-        <v>2848</v>
       </c>
       <c r="E1053" s="3">
         <v>1</v>
@@ -28389,13 +28377,13 @@
         <v>1053</v>
       </c>
       <c r="B1054" s="5" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C1054" s="5" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D1054" s="5" t="s">
         <v>2849</v>
-      </c>
-      <c r="C1054" s="5" t="s">
-        <v>2850</v>
-      </c>
-      <c r="D1054" s="5" t="s">
-        <v>2851</v>
       </c>
       <c r="E1054" s="3">
         <v>1</v>
@@ -28406,13 +28394,13 @@
         <v>1054</v>
       </c>
       <c r="B1055" s="5" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C1055" s="5" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D1055" s="5" t="s">
         <v>2852</v>
-      </c>
-      <c r="C1055" s="5" t="s">
-        <v>2853</v>
-      </c>
-      <c r="D1055" s="5" t="s">
-        <v>2854</v>
       </c>
       <c r="E1055" s="3">
         <v>1</v>
@@ -28457,13 +28445,13 @@
         <v>1057</v>
       </c>
       <c r="B1058" s="5" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C1058" s="5" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D1058" s="5" t="s">
         <v>2855</v>
-      </c>
-      <c r="C1058" s="5" t="s">
-        <v>2856</v>
-      </c>
-      <c r="D1058" s="5" t="s">
-        <v>2857</v>
       </c>
       <c r="E1058" s="3">
         <v>1</v>
@@ -28491,13 +28479,13 @@
         <v>1059</v>
       </c>
       <c r="B1060" s="5" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C1060" s="5" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D1060" s="5" t="s">
         <v>2858</v>
-      </c>
-      <c r="C1060" s="5" t="s">
-        <v>2859</v>
-      </c>
-      <c r="D1060" s="5" t="s">
-        <v>2860</v>
       </c>
       <c r="E1060" s="3">
         <v>1</v>
@@ -28508,13 +28496,13 @@
         <v>1060</v>
       </c>
       <c r="B1061" s="5" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C1061" s="5" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D1061" s="5" t="s">
         <v>2861</v>
-      </c>
-      <c r="C1061" s="5" t="s">
-        <v>2862</v>
-      </c>
-      <c r="D1061" s="5" t="s">
-        <v>2863</v>
       </c>
       <c r="E1061" s="3">
         <v>1</v>
@@ -28542,13 +28530,13 @@
         <v>1062</v>
       </c>
       <c r="B1063" s="5" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C1063" s="5" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D1063" s="5" t="s">
         <v>2864</v>
-      </c>
-      <c r="C1063" s="5" t="s">
-        <v>2865</v>
-      </c>
-      <c r="D1063" s="5" t="s">
-        <v>2866</v>
       </c>
       <c r="E1063" s="3">
         <v>1</v>
@@ -28559,13 +28547,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" s="5" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C1064" s="5" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D1064" s="5" t="s">
         <v>2867</v>
-      </c>
-      <c r="C1064" s="5" t="s">
-        <v>2868</v>
-      </c>
-      <c r="D1064" s="5" t="s">
-        <v>2869</v>
       </c>
       <c r="E1064" s="3">
         <v>1</v>
@@ -28576,13 +28564,13 @@
         <v>1064</v>
       </c>
       <c r="B1065" s="5" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C1065" s="5" t="s">
+        <v>2869</v>
+      </c>
+      <c r="D1065" s="5" t="s">
         <v>2870</v>
-      </c>
-      <c r="C1065" s="5" t="s">
-        <v>2871</v>
-      </c>
-      <c r="D1065" s="5" t="s">
-        <v>2872</v>
       </c>
       <c r="E1065" s="3">
         <v>1</v>
@@ -28593,13 +28581,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" s="5" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C1066" s="5" t="s">
+        <v>2872</v>
+      </c>
+      <c r="D1066" s="5" t="s">
         <v>2873</v>
-      </c>
-      <c r="C1066" s="5" t="s">
-        <v>2874</v>
-      </c>
-      <c r="D1066" s="5" t="s">
-        <v>2875</v>
       </c>
       <c r="E1066" s="3">
         <v>1</v>
@@ -28610,13 +28598,13 @@
         <v>1066</v>
       </c>
       <c r="B1067" s="5" t="s">
+        <v>2874</v>
+      </c>
+      <c r="C1067" s="5" t="s">
+        <v>2875</v>
+      </c>
+      <c r="D1067" s="5" t="s">
         <v>2876</v>
-      </c>
-      <c r="C1067" s="5" t="s">
-        <v>2877</v>
-      </c>
-      <c r="D1067" s="5" t="s">
-        <v>2878</v>
       </c>
       <c r="E1067" s="3">
         <v>1</v>
@@ -28627,13 +28615,13 @@
         <v>1067</v>
       </c>
       <c r="B1068" s="5" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C1068" s="5" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D1068" s="5" t="s">
         <v>2879</v>
-      </c>
-      <c r="C1068" s="5" t="s">
-        <v>2880</v>
-      </c>
-      <c r="D1068" s="5" t="s">
-        <v>2881</v>
       </c>
       <c r="E1068" s="3">
         <v>1</v>
@@ -28644,13 +28632,13 @@
         <v>1068</v>
       </c>
       <c r="B1069" s="5" t="s">
+        <v>2880</v>
+      </c>
+      <c r="C1069" s="5" t="s">
+        <v>2881</v>
+      </c>
+      <c r="D1069" s="5" t="s">
         <v>2882</v>
-      </c>
-      <c r="C1069" s="5" t="s">
-        <v>2883</v>
-      </c>
-      <c r="D1069" s="5" t="s">
-        <v>2884</v>
       </c>
       <c r="E1069" s="3">
         <v>1</v>
@@ -28661,13 +28649,13 @@
         <v>1069</v>
       </c>
       <c r="B1070" s="5" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C1070" s="5" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D1070" s="5" t="s">
         <v>2885</v>
-      </c>
-      <c r="C1070" s="5" t="s">
-        <v>2886</v>
-      </c>
-      <c r="D1070" s="5" t="s">
-        <v>2887</v>
       </c>
       <c r="E1070" s="3">
         <v>1</v>
@@ -28678,13 +28666,13 @@
         <v>1070</v>
       </c>
       <c r="B1071" s="5" t="s">
+        <v>2886</v>
+      </c>
+      <c r="C1071" s="5" t="s">
+        <v>2887</v>
+      </c>
+      <c r="D1071" s="5" t="s">
         <v>2888</v>
-      </c>
-      <c r="C1071" s="5" t="s">
-        <v>2889</v>
-      </c>
-      <c r="D1071" s="5" t="s">
-        <v>2890</v>
       </c>
       <c r="E1071" s="3">
         <v>1</v>
@@ -28695,13 +28683,13 @@
         <v>1071</v>
       </c>
       <c r="B1072" s="5" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C1072" s="5" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D1072" s="5" t="s">
         <v>2891</v>
-      </c>
-      <c r="C1072" s="5" t="s">
-        <v>2892</v>
-      </c>
-      <c r="D1072" s="5" t="s">
-        <v>2893</v>
       </c>
       <c r="E1072" s="3">
         <v>1</v>
@@ -28712,13 +28700,13 @@
         <v>1072</v>
       </c>
       <c r="B1073" s="5" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C1073" s="5" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D1073" s="5" t="s">
         <v>2894</v>
-      </c>
-      <c r="C1073" s="5" t="s">
-        <v>2895</v>
-      </c>
-      <c r="D1073" s="5" t="s">
-        <v>2896</v>
       </c>
       <c r="E1073" s="3">
         <v>1</v>
@@ -28729,13 +28717,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" s="5" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C1074" s="5" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D1074" s="5" t="s">
         <v>2897</v>
-      </c>
-      <c r="C1074" s="5" t="s">
-        <v>2898</v>
-      </c>
-      <c r="D1074" s="5" t="s">
-        <v>2899</v>
       </c>
       <c r="E1074" s="3">
         <v>1</v>
@@ -28746,13 +28734,13 @@
         <v>1074</v>
       </c>
       <c r="B1075" s="5" t="s">
+        <v>2898</v>
+      </c>
+      <c r="C1075" s="5" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D1075" s="5" t="s">
         <v>2900</v>
-      </c>
-      <c r="C1075" s="5" t="s">
-        <v>2901</v>
-      </c>
-      <c r="D1075" s="5" t="s">
-        <v>2902</v>
       </c>
       <c r="E1075" s="3">
         <v>1</v>
@@ -28763,13 +28751,13 @@
         <v>1075</v>
       </c>
       <c r="B1076" s="5" t="s">
+        <v>2901</v>
+      </c>
+      <c r="C1076" s="5" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D1076" s="5" t="s">
         <v>2903</v>
-      </c>
-      <c r="C1076" s="5" t="s">
-        <v>2904</v>
-      </c>
-      <c r="D1076" s="5" t="s">
-        <v>2905</v>
       </c>
       <c r="E1076" s="3">
         <v>1</v>
@@ -28797,13 +28785,13 @@
         <v>1077</v>
       </c>
       <c r="B1078" s="5" t="s">
+        <v>2904</v>
+      </c>
+      <c r="C1078" s="5" t="s">
+        <v>2905</v>
+      </c>
+      <c r="D1078" s="5" t="s">
         <v>2906</v>
-      </c>
-      <c r="C1078" s="5" t="s">
-        <v>2907</v>
-      </c>
-      <c r="D1078" s="5" t="s">
-        <v>2908</v>
       </c>
       <c r="E1078" s="3">
         <v>1</v>
@@ -28814,13 +28802,13 @@
         <v>1078</v>
       </c>
       <c r="B1079" s="5" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C1079" s="5" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D1079" s="5" t="s">
         <v>2909</v>
-      </c>
-      <c r="C1079" s="5" t="s">
-        <v>2910</v>
-      </c>
-      <c r="D1079" s="5" t="s">
-        <v>2911</v>
       </c>
       <c r="E1079" s="3">
         <v>1</v>
@@ -28831,13 +28819,13 @@
         <v>1079</v>
       </c>
       <c r="B1080" s="5" t="s">
+        <v>2910</v>
+      </c>
+      <c r="C1080" s="5" t="s">
+        <v>2911</v>
+      </c>
+      <c r="D1080" s="5" t="s">
         <v>2912</v>
-      </c>
-      <c r="C1080" s="5" t="s">
-        <v>2913</v>
-      </c>
-      <c r="D1080" s="5" t="s">
-        <v>2914</v>
       </c>
       <c r="E1080" s="3">
         <v>1</v>
@@ -28848,13 +28836,13 @@
         <v>1080</v>
       </c>
       <c r="B1081" s="5" t="s">
+        <v>2913</v>
+      </c>
+      <c r="C1081" s="5" t="s">
+        <v>2914</v>
+      </c>
+      <c r="D1081" s="5" t="s">
         <v>2915</v>
-      </c>
-      <c r="C1081" s="5" t="s">
-        <v>2916</v>
-      </c>
-      <c r="D1081" s="5" t="s">
-        <v>2917</v>
       </c>
       <c r="E1081" s="3">
         <v>1</v>
@@ -28865,13 +28853,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" s="5" t="s">
+        <v>2916</v>
+      </c>
+      <c r="C1082" s="5" t="s">
+        <v>2917</v>
+      </c>
+      <c r="D1082" s="5" t="s">
         <v>2918</v>
-      </c>
-      <c r="C1082" s="5" t="s">
-        <v>2919</v>
-      </c>
-      <c r="D1082" s="5" t="s">
-        <v>2920</v>
       </c>
       <c r="E1082" s="3">
         <v>1</v>
@@ -28882,13 +28870,13 @@
         <v>1082</v>
       </c>
       <c r="B1083" s="5" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C1083" s="5" t="s">
+        <v>2920</v>
+      </c>
+      <c r="D1083" s="5" t="s">
         <v>2921</v>
-      </c>
-      <c r="C1083" s="5" t="s">
-        <v>2922</v>
-      </c>
-      <c r="D1083" s="5" t="s">
-        <v>2923</v>
       </c>
       <c r="E1083" s="3">
         <v>1</v>
@@ -28899,13 +28887,13 @@
         <v>1083</v>
       </c>
       <c r="B1084" s="5" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C1084" s="5" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D1084" s="5" t="s">
         <v>2398</v>
-      </c>
-      <c r="C1084" s="5" t="s">
-        <v>2399</v>
-      </c>
-      <c r="D1084" s="5" t="s">
-        <v>2400</v>
       </c>
       <c r="E1084" s="3">
         <v>1</v>
@@ -28916,13 +28904,13 @@
         <v>1084</v>
       </c>
       <c r="B1085" s="5" t="s">
+        <v>2922</v>
+      </c>
+      <c r="C1085" s="5" t="s">
+        <v>2923</v>
+      </c>
+      <c r="D1085" s="5" t="s">
         <v>2924</v>
-      </c>
-      <c r="C1085" s="5" t="s">
-        <v>2925</v>
-      </c>
-      <c r="D1085" s="5" t="s">
-        <v>2926</v>
       </c>
       <c r="E1085" s="3">
         <v>1</v>
@@ -28933,13 +28921,13 @@
         <v>1085</v>
       </c>
       <c r="B1086" s="5" t="s">
+        <v>2925</v>
+      </c>
+      <c r="C1086" s="5" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D1086" s="5" t="s">
         <v>2927</v>
-      </c>
-      <c r="C1086" s="5" t="s">
-        <v>2928</v>
-      </c>
-      <c r="D1086" s="5" t="s">
-        <v>2929</v>
       </c>
       <c r="E1086" s="3">
         <v>1</v>
@@ -28950,13 +28938,13 @@
         <v>1086</v>
       </c>
       <c r="B1087" s="5" t="s">
+        <v>2928</v>
+      </c>
+      <c r="C1087" s="5" t="s">
+        <v>2929</v>
+      </c>
+      <c r="D1087" s="5" t="s">
         <v>2930</v>
-      </c>
-      <c r="C1087" s="5" t="s">
-        <v>2931</v>
-      </c>
-      <c r="D1087" s="5" t="s">
-        <v>2932</v>
       </c>
       <c r="E1087" s="3">
         <v>1</v>
@@ -28967,13 +28955,13 @@
         <v>1087</v>
       </c>
       <c r="B1088" s="5" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C1088" s="5" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D1088" s="5" t="s">
         <v>2933</v>
-      </c>
-      <c r="C1088" s="5" t="s">
-        <v>2934</v>
-      </c>
-      <c r="D1088" s="5" t="s">
-        <v>2935</v>
       </c>
       <c r="E1088" s="3">
         <v>1</v>
@@ -29001,13 +28989,13 @@
         <v>1089</v>
       </c>
       <c r="B1090" s="5" t="s">
+        <v>2934</v>
+      </c>
+      <c r="C1090" s="5" t="s">
+        <v>2935</v>
+      </c>
+      <c r="D1090" s="5" t="s">
         <v>2936</v>
-      </c>
-      <c r="C1090" s="5" t="s">
-        <v>2937</v>
-      </c>
-      <c r="D1090" s="5" t="s">
-        <v>2938</v>
       </c>
       <c r="E1090" s="3">
         <v>1</v>
@@ -29018,13 +29006,13 @@
         <v>1090</v>
       </c>
       <c r="B1091" s="5" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C1091" s="5" t="s">
+        <v>2938</v>
+      </c>
+      <c r="D1091" s="5" t="s">
         <v>2939</v>
-      </c>
-      <c r="C1091" s="5" t="s">
-        <v>2940</v>
-      </c>
-      <c r="D1091" s="5" t="s">
-        <v>2941</v>
       </c>
       <c r="E1091" s="3">
         <v>1</v>
@@ -29035,13 +29023,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="C1092" s="5" t="s">
+        <v>2941</v>
+      </c>
+      <c r="D1092" s="5" t="s">
         <v>2942</v>
-      </c>
-      <c r="C1092" s="5" t="s">
-        <v>2943</v>
-      </c>
-      <c r="D1092" s="5" t="s">
-        <v>2944</v>
       </c>
       <c r="E1092" s="3">
         <v>1</v>
@@ -29052,13 +29040,13 @@
         <v>1092</v>
       </c>
       <c r="B1093" s="5" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C1093" s="5" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D1093" s="5" t="s">
         <v>2945</v>
-      </c>
-      <c r="C1093" s="5" t="s">
-        <v>2946</v>
-      </c>
-      <c r="D1093" s="5" t="s">
-        <v>2947</v>
       </c>
       <c r="E1093" s="3">
         <v>1</v>
@@ -29069,13 +29057,13 @@
         <v>1093</v>
       </c>
       <c r="B1094" s="5" t="s">
+        <v>2946</v>
+      </c>
+      <c r="C1094" s="5" t="s">
+        <v>2947</v>
+      </c>
+      <c r="D1094" s="5" t="s">
         <v>2948</v>
-      </c>
-      <c r="C1094" s="5" t="s">
-        <v>2949</v>
-      </c>
-      <c r="D1094" s="5" t="s">
-        <v>2950</v>
       </c>
       <c r="E1094" s="3">
         <v>1</v>
@@ -29086,13 +29074,13 @@
         <v>1094</v>
       </c>
       <c r="B1095" s="5" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C1095" s="5" t="s">
+        <v>2950</v>
+      </c>
+      <c r="D1095" s="5" t="s">
         <v>2951</v>
-      </c>
-      <c r="C1095" s="5" t="s">
-        <v>2952</v>
-      </c>
-      <c r="D1095" s="5" t="s">
-        <v>2953</v>
       </c>
       <c r="E1095" s="3">
         <v>1</v>
@@ -29103,13 +29091,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="C1096" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="D1096" s="5" t="s">
         <v>2954</v>
-      </c>
-      <c r="C1096" s="5" t="s">
-        <v>2955</v>
-      </c>
-      <c r="D1096" s="5" t="s">
-        <v>2956</v>
       </c>
       <c r="E1096" s="3">
         <v>1</v>
@@ -29120,13 +29108,13 @@
         <v>1096</v>
       </c>
       <c r="B1097" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="C1097" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D1097" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="C1097" s="5" t="s">
-        <v>2958</v>
-      </c>
-      <c r="D1097" s="5" t="s">
-        <v>2959</v>
       </c>
       <c r="E1097" s="3">
         <v>1</v>
@@ -29137,13 +29125,13 @@
         <v>1097</v>
       </c>
       <c r="B1098" s="5" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C1098" s="5" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D1098" s="5" t="s">
         <v>2960</v>
-      </c>
-      <c r="C1098" s="5" t="s">
-        <v>2961</v>
-      </c>
-      <c r="D1098" s="5" t="s">
-        <v>2962</v>
       </c>
       <c r="E1098" s="3">
         <v>1</v>
@@ -29154,13 +29142,13 @@
         <v>1098</v>
       </c>
       <c r="B1099" s="5" t="s">
+        <v>2961</v>
+      </c>
+      <c r="C1099" s="5" t="s">
+        <v>2962</v>
+      </c>
+      <c r="D1099" s="5" t="s">
         <v>2963</v>
-      </c>
-      <c r="C1099" s="5" t="s">
-        <v>2964</v>
-      </c>
-      <c r="D1099" s="5" t="s">
-        <v>2965</v>
       </c>
       <c r="E1099" s="3">
         <v>1</v>
@@ -29171,13 +29159,13 @@
         <v>1099</v>
       </c>
       <c r="B1100" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="C1100" s="5" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D1100" s="5" t="s">
         <v>2966</v>
-      </c>
-      <c r="C1100" s="5" t="s">
-        <v>2967</v>
-      </c>
-      <c r="D1100" s="5" t="s">
-        <v>2968</v>
       </c>
       <c r="E1100" s="3">
         <v>1</v>
@@ -29188,13 +29176,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" s="5" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C1101" s="5" t="s">
+        <v>2968</v>
+      </c>
+      <c r="D1101" s="5" t="s">
         <v>2969</v>
-      </c>
-      <c r="C1101" s="5" t="s">
-        <v>2970</v>
-      </c>
-      <c r="D1101" s="5" t="s">
-        <v>2971</v>
       </c>
       <c r="E1101" s="3">
         <v>1</v>
@@ -29205,13 +29193,13 @@
         <v>1101</v>
       </c>
       <c r="B1102" s="5" t="s">
+        <v>2970</v>
+      </c>
+      <c r="C1102" s="5" t="s">
+        <v>2971</v>
+      </c>
+      <c r="D1102" s="5" t="s">
         <v>2972</v>
-      </c>
-      <c r="C1102" s="5" t="s">
-        <v>2973</v>
-      </c>
-      <c r="D1102" s="5" t="s">
-        <v>2974</v>
       </c>
       <c r="E1102" s="3">
         <v>1</v>
@@ -29222,13 +29210,13 @@
         <v>1102</v>
       </c>
       <c r="B1103" s="5" t="s">
+        <v>2973</v>
+      </c>
+      <c r="C1103" s="5" t="s">
+        <v>2974</v>
+      </c>
+      <c r="D1103" s="5" t="s">
         <v>2975</v>
-      </c>
-      <c r="C1103" s="5" t="s">
-        <v>2976</v>
-      </c>
-      <c r="D1103" s="5" t="s">
-        <v>2977</v>
       </c>
       <c r="E1103" s="3">
         <v>1</v>
@@ -29239,13 +29227,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" s="5" t="s">
+        <v>2976</v>
+      </c>
+      <c r="C1104" s="5" t="s">
+        <v>2977</v>
+      </c>
+      <c r="D1104" s="5" t="s">
         <v>2978</v>
-      </c>
-      <c r="C1104" s="5" t="s">
-        <v>2979</v>
-      </c>
-      <c r="D1104" s="5" t="s">
-        <v>2980</v>
       </c>
       <c r="E1104" s="3">
         <v>1</v>
@@ -29256,13 +29244,13 @@
         <v>1104</v>
       </c>
       <c r="B1105" s="5" t="s">
+        <v>2979</v>
+      </c>
+      <c r="C1105" s="5" t="s">
+        <v>2980</v>
+      </c>
+      <c r="D1105" s="5" t="s">
         <v>2981</v>
-      </c>
-      <c r="C1105" s="5" t="s">
-        <v>2982</v>
-      </c>
-      <c r="D1105" s="5" t="s">
-        <v>2983</v>
       </c>
       <c r="E1105" s="3">
         <v>1</v>
@@ -29273,13 +29261,13 @@
         <v>1105</v>
       </c>
       <c r="B1106" s="5" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C1106" s="5" t="s">
+        <v>2983</v>
+      </c>
+      <c r="D1106" s="5" t="s">
         <v>2984</v>
-      </c>
-      <c r="C1106" s="5" t="s">
-        <v>2985</v>
-      </c>
-      <c r="D1106" s="5" t="s">
-        <v>2986</v>
       </c>
       <c r="E1106" s="3">
         <v>1</v>
@@ -29290,13 +29278,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" s="5" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C1107" s="5" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D1107" s="5" t="s">
         <v>2987</v>
-      </c>
-      <c r="C1107" s="5" t="s">
-        <v>2988</v>
-      </c>
-      <c r="D1107" s="5" t="s">
-        <v>2989</v>
       </c>
       <c r="E1107" s="3">
         <v>1</v>
@@ -29307,13 +29295,13 @@
         <v>1107</v>
       </c>
       <c r="B1108" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C1108" s="5" t="s">
+        <v>2989</v>
+      </c>
+      <c r="D1108" s="5" t="s">
         <v>2990</v>
-      </c>
-      <c r="C1108" s="5" t="s">
-        <v>2991</v>
-      </c>
-      <c r="D1108" s="5" t="s">
-        <v>2992</v>
       </c>
       <c r="E1108" s="3">
         <v>1</v>
@@ -29324,13 +29312,13 @@
         <v>1108</v>
       </c>
       <c r="B1109" s="5" t="s">
+        <v>2991</v>
+      </c>
+      <c r="C1109" s="5" t="s">
+        <v>2992</v>
+      </c>
+      <c r="D1109" s="5" t="s">
         <v>2993</v>
-      </c>
-      <c r="C1109" s="5" t="s">
-        <v>2994</v>
-      </c>
-      <c r="D1109" s="5" t="s">
-        <v>2995</v>
       </c>
       <c r="E1109" s="3">
         <v>1</v>
@@ -29341,13 +29329,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" s="5" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C1110" s="5" t="s">
+        <v>2995</v>
+      </c>
+      <c r="D1110" s="5" t="s">
         <v>2996</v>
-      </c>
-      <c r="C1110" s="5" t="s">
-        <v>2997</v>
-      </c>
-      <c r="D1110" s="5" t="s">
-        <v>2998</v>
       </c>
       <c r="E1110" s="3">
         <v>1</v>
@@ -29358,13 +29346,13 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="5" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="C1111" s="5" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="D1111" s="5" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="E1111" s="3">
         <v>1</v>
@@ -29375,13 +29363,13 @@
         <v>1111</v>
       </c>
       <c r="B1112" s="5" t="s">
+        <v>2998</v>
+      </c>
+      <c r="C1112" s="5" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D1112" s="5" t="s">
         <v>3000</v>
-      </c>
-      <c r="C1112" s="5" t="s">
-        <v>3001</v>
-      </c>
-      <c r="D1112" s="5" t="s">
-        <v>3002</v>
       </c>
       <c r="E1112" s="3">
         <v>1</v>
@@ -29392,13 +29380,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" s="5" t="s">
+        <v>3001</v>
+      </c>
+      <c r="C1113" s="5" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D1113" s="5" t="s">
         <v>3003</v>
-      </c>
-      <c r="C1113" s="5" t="s">
-        <v>3004</v>
-      </c>
-      <c r="D1113" s="5" t="s">
-        <v>3005</v>
       </c>
       <c r="E1113" s="3">
         <v>1</v>
@@ -29409,13 +29397,13 @@
         <v>1113</v>
       </c>
       <c r="B1114" s="5" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C1114" s="5" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D1114" s="5" t="s">
         <v>3006</v>
-      </c>
-      <c r="C1114" s="5" t="s">
-        <v>3007</v>
-      </c>
-      <c r="D1114" s="5" t="s">
-        <v>3008</v>
       </c>
       <c r="E1114" s="3">
         <v>1</v>
@@ -29426,13 +29414,13 @@
         <v>1114</v>
       </c>
       <c r="B1115" s="5" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C1115" s="5" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D1115" s="5" t="s">
         <v>3009</v>
-      </c>
-      <c r="C1115" s="5" t="s">
-        <v>3010</v>
-      </c>
-      <c r="D1115" s="5" t="s">
-        <v>3011</v>
       </c>
       <c r="E1115" s="3">
         <v>1</v>
@@ -29443,13 +29431,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" s="5" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C1116" s="5" t="s">
+        <v>3011</v>
+      </c>
+      <c r="D1116" s="5" t="s">
         <v>3012</v>
-      </c>
-      <c r="C1116" s="5" t="s">
-        <v>3013</v>
-      </c>
-      <c r="D1116" s="5" t="s">
-        <v>3014</v>
       </c>
       <c r="E1116" s="3">
         <v>1</v>
@@ -29460,13 +29448,13 @@
         <v>1116</v>
       </c>
       <c r="B1117" s="5" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1117" s="5" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D1117" s="5" t="s">
         <v>3015</v>
-      </c>
-      <c r="C1117" s="5" t="s">
-        <v>3016</v>
-      </c>
-      <c r="D1117" s="5" t="s">
-        <v>3017</v>
       </c>
       <c r="E1117" s="3">
         <v>1</v>
@@ -29477,13 +29465,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" s="5" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C1118" s="5" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D1118" s="5" t="s">
         <v>3018</v>
-      </c>
-      <c r="C1118" s="5" t="s">
-        <v>3019</v>
-      </c>
-      <c r="D1118" s="5" t="s">
-        <v>3020</v>
       </c>
       <c r="E1118" s="3">
         <v>1</v>
@@ -29494,13 +29482,13 @@
         <v>1118</v>
       </c>
       <c r="B1119" s="5" t="s">
+        <v>3019</v>
+      </c>
+      <c r="C1119" s="5" t="s">
+        <v>3020</v>
+      </c>
+      <c r="D1119" s="5" t="s">
         <v>3021</v>
-      </c>
-      <c r="C1119" s="5" t="s">
-        <v>3022</v>
-      </c>
-      <c r="D1119" s="5" t="s">
-        <v>3023</v>
       </c>
       <c r="E1119" s="3">
         <v>1</v>
@@ -29511,13 +29499,13 @@
         <v>1119</v>
       </c>
       <c r="B1120" s="5" t="s">
+        <v>3022</v>
+      </c>
+      <c r="C1120" s="5" t="s">
+        <v>3023</v>
+      </c>
+      <c r="D1120" s="5" t="s">
         <v>3024</v>
-      </c>
-      <c r="C1120" s="5" t="s">
-        <v>3025</v>
-      </c>
-      <c r="D1120" s="5" t="s">
-        <v>3026</v>
       </c>
       <c r="E1120" s="3">
         <v>1</v>
@@ -29528,13 +29516,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" s="5" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C1121" s="5" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D1121" s="5" t="s">
         <v>3027</v>
-      </c>
-      <c r="C1121" s="5" t="s">
-        <v>3028</v>
-      </c>
-      <c r="D1121" s="5" t="s">
-        <v>3029</v>
       </c>
       <c r="E1121" s="3">
         <v>1</v>
@@ -29545,13 +29533,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" s="5" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C1122" s="5" t="s">
         <v>2017</v>
       </c>
-      <c r="C1122" s="5" t="s">
+      <c r="D1122" s="5" t="s">
         <v>2018</v>
-      </c>
-      <c r="D1122" s="5" t="s">
-        <v>2019</v>
       </c>
       <c r="E1122" s="3">
         <v>1</v>
@@ -29562,13 +29550,13 @@
         <v>1122</v>
       </c>
       <c r="B1123" s="5" t="s">
+        <v>3028</v>
+      </c>
+      <c r="C1123" s="5" t="s">
+        <v>3029</v>
+      </c>
+      <c r="D1123" s="5" t="s">
         <v>3030</v>
-      </c>
-      <c r="C1123" s="5" t="s">
-        <v>3031</v>
-      </c>
-      <c r="D1123" s="5" t="s">
-        <v>3032</v>
       </c>
       <c r="E1123" s="3">
         <v>1</v>
@@ -29579,13 +29567,13 @@
         <v>1123</v>
       </c>
       <c r="B1124" s="5" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C1124" s="5" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D1124" s="5" t="s">
         <v>3033</v>
-      </c>
-      <c r="C1124" s="5" t="s">
-        <v>3034</v>
-      </c>
-      <c r="D1124" s="5" t="s">
-        <v>3035</v>
       </c>
       <c r="E1124" s="3">
         <v>1</v>
@@ -29596,13 +29584,13 @@
         <v>1124</v>
       </c>
       <c r="B1125" s="5" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="C1125" s="5" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="D1125" s="5" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="E1125" s="3">
         <v>1</v>
@@ -29613,13 +29601,13 @@
         <v>1125</v>
       </c>
       <c r="B1126" s="5" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C1126" s="5" t="s">
+        <v>3036</v>
+      </c>
+      <c r="D1126" s="5" t="s">
         <v>3037</v>
-      </c>
-      <c r="C1126" s="5" t="s">
-        <v>3038</v>
-      </c>
-      <c r="D1126" s="5" t="s">
-        <v>3039</v>
       </c>
       <c r="E1126" s="3">
         <v>1</v>
@@ -29630,13 +29618,13 @@
         <v>1126</v>
       </c>
       <c r="B1127" s="5" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C1127" s="5" t="s">
+        <v>3039</v>
+      </c>
+      <c r="D1127" s="5" t="s">
         <v>3040</v>
-      </c>
-      <c r="C1127" s="5" t="s">
-        <v>3041</v>
-      </c>
-      <c r="D1127" s="5" t="s">
-        <v>3042</v>
       </c>
       <c r="E1127" s="3">
         <v>1</v>
@@ -29647,13 +29635,13 @@
         <v>1127</v>
       </c>
       <c r="B1128" s="5" t="s">
+        <v>3041</v>
+      </c>
+      <c r="C1128" s="5" t="s">
+        <v>3042</v>
+      </c>
+      <c r="D1128" s="5" t="s">
         <v>3043</v>
-      </c>
-      <c r="C1128" s="5" t="s">
-        <v>3044</v>
-      </c>
-      <c r="D1128" s="5" t="s">
-        <v>3045</v>
       </c>
       <c r="E1128" s="3">
         <v>1</v>
@@ -29664,11 +29652,11 @@
         <v>1128</v>
       </c>
       <c r="B1129" s="5" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="C1129" s="5"/>
       <c r="D1129" s="5" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="E1129" s="3">
         <v>1</v>
@@ -29679,13 +29667,13 @@
         <v>1129</v>
       </c>
       <c r="B1130" s="5" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C1130" s="5" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D1130" s="5" t="s">
         <v>3048</v>
-      </c>
-      <c r="C1130" s="5" t="s">
-        <v>3049</v>
-      </c>
-      <c r="D1130" s="5" t="s">
-        <v>3050</v>
       </c>
       <c r="E1130" s="3">
         <v>1</v>
@@ -29696,13 +29684,13 @@
         <v>1130</v>
       </c>
       <c r="B1131" s="5" t="s">
+        <v>3049</v>
+      </c>
+      <c r="C1131" s="5" t="s">
+        <v>3050</v>
+      </c>
+      <c r="D1131" s="5" t="s">
         <v>3051</v>
-      </c>
-      <c r="C1131" s="5" t="s">
-        <v>3052</v>
-      </c>
-      <c r="D1131" s="5" t="s">
-        <v>3053</v>
       </c>
       <c r="E1131" s="3">
         <v>1</v>
@@ -29713,13 +29701,13 @@
         <v>1131</v>
       </c>
       <c r="B1132" s="5" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C1132" s="5" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1132" s="5" t="s">
         <v>3054</v>
-      </c>
-      <c r="C1132" s="5" t="s">
-        <v>3055</v>
-      </c>
-      <c r="D1132" s="5" t="s">
-        <v>3056</v>
       </c>
       <c r="E1132" s="3">
         <v>1</v>
@@ -29730,13 +29718,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" s="5" t="s">
+        <v>3055</v>
+      </c>
+      <c r="C1133" s="5" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D1133" s="5" t="s">
         <v>3057</v>
-      </c>
-      <c r="C1133" s="5" t="s">
-        <v>3058</v>
-      </c>
-      <c r="D1133" s="5" t="s">
-        <v>3059</v>
       </c>
       <c r="E1133" s="3">
         <v>1</v>
@@ -29747,13 +29735,13 @@
         <v>1133</v>
       </c>
       <c r="B1134" s="5" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C1134" s="5" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D1134" s="5" t="s">
         <v>3060</v>
-      </c>
-      <c r="C1134" s="5" t="s">
-        <v>3061</v>
-      </c>
-      <c r="D1134" s="5" t="s">
-        <v>3062</v>
       </c>
       <c r="E1134" s="3">
         <v>1</v>
@@ -29764,13 +29752,13 @@
         <v>1134</v>
       </c>
       <c r="B1135" s="5" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C1135" s="5" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D1135" s="5" t="s">
         <v>3063</v>
-      </c>
-      <c r="C1135" s="5" t="s">
-        <v>3064</v>
-      </c>
-      <c r="D1135" s="5" t="s">
-        <v>3065</v>
       </c>
       <c r="E1135" s="3">
         <v>1</v>
@@ -29781,13 +29769,13 @@
         <v>1135</v>
       </c>
       <c r="B1136" s="5" t="s">
+        <v>3064</v>
+      </c>
+      <c r="C1136" s="5" t="s">
+        <v>3065</v>
+      </c>
+      <c r="D1136" s="5" t="s">
         <v>3066</v>
-      </c>
-      <c r="C1136" s="5" t="s">
-        <v>3067</v>
-      </c>
-      <c r="D1136" s="5" t="s">
-        <v>3068</v>
       </c>
       <c r="E1136" s="3">
         <v>1</v>
@@ -29798,13 +29786,13 @@
         <v>1136</v>
       </c>
       <c r="B1137" s="5" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="C1137" s="5" t="s">
         <v>1187</v>
       </c>
       <c r="D1137" s="5" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
       <c r="E1137" s="3">
         <v>1</v>
@@ -29815,13 +29803,13 @@
         <v>1137</v>
       </c>
       <c r="B1138" s="5" t="s">
+        <v>3069</v>
+      </c>
+      <c r="C1138" s="5" t="s">
+        <v>3070</v>
+      </c>
+      <c r="D1138" s="5" t="s">
         <v>3071</v>
-      </c>
-      <c r="C1138" s="5" t="s">
-        <v>3072</v>
-      </c>
-      <c r="D1138" s="5" t="s">
-        <v>3073</v>
       </c>
       <c r="E1138" s="3">
         <v>1</v>
@@ -29832,13 +29820,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" s="5" t="s">
+        <v>3072</v>
+      </c>
+      <c r="C1139" s="5" t="s">
+        <v>3073</v>
+      </c>
+      <c r="D1139" s="5" t="s">
         <v>3074</v>
-      </c>
-      <c r="C1139" s="5" t="s">
-        <v>3075</v>
-      </c>
-      <c r="D1139" s="5" t="s">
-        <v>3076</v>
       </c>
       <c r="E1139" s="3">
         <v>1</v>
@@ -29849,13 +29837,13 @@
         <v>1139</v>
       </c>
       <c r="B1140" s="5" t="s">
+        <v>3075</v>
+      </c>
+      <c r="C1140" s="5" t="s">
+        <v>3076</v>
+      </c>
+      <c r="D1140" s="5" t="s">
         <v>3077</v>
-      </c>
-      <c r="C1140" s="5" t="s">
-        <v>3078</v>
-      </c>
-      <c r="D1140" s="5" t="s">
-        <v>3079</v>
       </c>
       <c r="E1140" s="3">
         <v>1</v>
@@ -29866,13 +29854,13 @@
         <v>1140</v>
       </c>
       <c r="B1141" s="5" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C1141" s="5" t="s">
+        <v>3079</v>
+      </c>
+      <c r="D1141" s="5" t="s">
         <v>3080</v>
-      </c>
-      <c r="C1141" s="5" t="s">
-        <v>3081</v>
-      </c>
-      <c r="D1141" s="5" t="s">
-        <v>3082</v>
       </c>
       <c r="E1141" s="3">
         <v>1</v>
@@ -29883,13 +29871,13 @@
         <v>1141</v>
       </c>
       <c r="B1142" s="5" t="s">
+        <v>3081</v>
+      </c>
+      <c r="C1142" s="5" t="s">
+        <v>3082</v>
+      </c>
+      <c r="D1142" s="5" t="s">
         <v>3083</v>
-      </c>
-      <c r="C1142" s="5" t="s">
-        <v>3084</v>
-      </c>
-      <c r="D1142" s="5" t="s">
-        <v>3085</v>
       </c>
       <c r="E1142" s="3">
         <v>1</v>
@@ -29900,13 +29888,13 @@
         <v>1142</v>
       </c>
       <c r="B1143" s="5" t="s">
+        <v>3084</v>
+      </c>
+      <c r="C1143" s="5" t="s">
+        <v>3085</v>
+      </c>
+      <c r="D1143" s="5" t="s">
         <v>3086</v>
-      </c>
-      <c r="C1143" s="5" t="s">
-        <v>3087</v>
-      </c>
-      <c r="D1143" s="5" t="s">
-        <v>3088</v>
       </c>
       <c r="E1143" s="3">
         <v>1</v>
@@ -29917,13 +29905,13 @@
         <v>1143</v>
       </c>
       <c r="B1144" s="5" t="s">
+        <v>3087</v>
+      </c>
+      <c r="C1144" s="5" t="s">
+        <v>3088</v>
+      </c>
+      <c r="D1144" s="5" t="s">
         <v>3089</v>
-      </c>
-      <c r="C1144" s="5" t="s">
-        <v>3090</v>
-      </c>
-      <c r="D1144" s="5" t="s">
-        <v>3091</v>
       </c>
       <c r="E1144" s="3">
         <v>1</v>
@@ -29934,13 +29922,13 @@
         <v>1144</v>
       </c>
       <c r="B1145" s="5" t="s">
+        <v>3090</v>
+      </c>
+      <c r="C1145" s="5" t="s">
+        <v>3091</v>
+      </c>
+      <c r="D1145" s="5" t="s">
         <v>3092</v>
-      </c>
-      <c r="C1145" s="5" t="s">
-        <v>3093</v>
-      </c>
-      <c r="D1145" s="5" t="s">
-        <v>3094</v>
       </c>
       <c r="E1145" s="3">
         <v>1</v>
@@ -29951,13 +29939,13 @@
         <v>1145</v>
       </c>
       <c r="B1146" s="5" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C1146" s="5" t="s">
+        <v>3094</v>
+      </c>
+      <c r="D1146" s="5" t="s">
         <v>3095</v>
-      </c>
-      <c r="C1146" s="5" t="s">
-        <v>3096</v>
-      </c>
-      <c r="D1146" s="5" t="s">
-        <v>3097</v>
       </c>
       <c r="E1146" s="3">
         <v>1</v>
@@ -29968,13 +29956,13 @@
         <v>1146</v>
       </c>
       <c r="B1147" s="5" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C1147" s="5" t="s">
+        <v>3097</v>
+      </c>
+      <c r="D1147" s="5" t="s">
         <v>3098</v>
-      </c>
-      <c r="C1147" s="5" t="s">
-        <v>3099</v>
-      </c>
-      <c r="D1147" s="5" t="s">
-        <v>3100</v>
       </c>
       <c r="E1147" s="3">
         <v>1</v>
@@ -29985,13 +29973,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" s="5" t="s">
+        <v>3099</v>
+      </c>
+      <c r="C1148" s="5" t="s">
+        <v>3100</v>
+      </c>
+      <c r="D1148" s="5" t="s">
         <v>3101</v>
-      </c>
-      <c r="C1148" s="5" t="s">
-        <v>3102</v>
-      </c>
-      <c r="D1148" s="5" t="s">
-        <v>3103</v>
       </c>
       <c r="E1148" s="3">
         <v>1</v>
@@ -30002,13 +29990,13 @@
         <v>1148</v>
       </c>
       <c r="B1149" s="5" t="s">
+        <v>3102</v>
+      </c>
+      <c r="C1149" s="5" t="s">
+        <v>3103</v>
+      </c>
+      <c r="D1149" s="5" t="s">
         <v>3104</v>
-      </c>
-      <c r="C1149" s="5" t="s">
-        <v>3105</v>
-      </c>
-      <c r="D1149" s="5" t="s">
-        <v>3106</v>
       </c>
       <c r="E1149" s="3">
         <v>1</v>
@@ -30019,13 +30007,13 @@
         <v>1149</v>
       </c>
       <c r="B1150" s="5" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1150" s="5" t="s">
+        <v>3106</v>
+      </c>
+      <c r="D1150" s="5" t="s">
         <v>3107</v>
-      </c>
-      <c r="C1150" s="5" t="s">
-        <v>3108</v>
-      </c>
-      <c r="D1150" s="5" t="s">
-        <v>3109</v>
       </c>
       <c r="E1150" s="3">
         <v>1</v>
@@ -30036,13 +30024,13 @@
         <v>1150</v>
       </c>
       <c r="B1151" s="5" t="s">
+        <v>3108</v>
+      </c>
+      <c r="C1151" s="5" t="s">
+        <v>3109</v>
+      </c>
+      <c r="D1151" s="5" t="s">
         <v>3110</v>
-      </c>
-      <c r="C1151" s="5" t="s">
-        <v>3111</v>
-      </c>
-      <c r="D1151" s="5" t="s">
-        <v>3112</v>
       </c>
       <c r="E1151" s="3">
         <v>1</v>
@@ -30053,13 +30041,13 @@
         <v>1151</v>
       </c>
       <c r="B1152" s="5" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C1152" s="5" t="s">
+        <v>3112</v>
+      </c>
+      <c r="D1152" s="5" t="s">
         <v>3113</v>
-      </c>
-      <c r="C1152" s="5" t="s">
-        <v>3114</v>
-      </c>
-      <c r="D1152" s="5" t="s">
-        <v>3115</v>
       </c>
       <c r="E1152" s="3">
         <v>1</v>
@@ -30070,13 +30058,13 @@
         <v>1152</v>
       </c>
       <c r="B1153" s="5" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C1153" s="5" t="s">
+        <v>3115</v>
+      </c>
+      <c r="D1153" s="5" t="s">
         <v>3116</v>
-      </c>
-      <c r="C1153" s="5" t="s">
-        <v>3117</v>
-      </c>
-      <c r="D1153" s="5" t="s">
-        <v>3118</v>
       </c>
       <c r="E1153" s="3">
         <v>1</v>
@@ -30087,13 +30075,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" s="5" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="C1154" s="5" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="D1154" s="5" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="E1154" s="3">
         <v>1</v>
@@ -30104,13 +30092,13 @@
         <v>1154</v>
       </c>
       <c r="B1155" s="5" t="s">
+        <v>3118</v>
+      </c>
+      <c r="C1155" s="5" t="s">
+        <v>3119</v>
+      </c>
+      <c r="D1155" s="5" t="s">
         <v>3120</v>
-      </c>
-      <c r="C1155" s="5" t="s">
-        <v>3121</v>
-      </c>
-      <c r="D1155" s="5" t="s">
-        <v>3122</v>
       </c>
       <c r="E1155" s="3">
         <v>1</v>
@@ -30121,13 +30109,13 @@
         <v>1155</v>
       </c>
       <c r="B1156" s="5" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C1156" s="5" t="s">
+        <v>3122</v>
+      </c>
+      <c r="D1156" s="5" t="s">
         <v>3123</v>
-      </c>
-      <c r="C1156" s="5" t="s">
-        <v>3124</v>
-      </c>
-      <c r="D1156" s="5" t="s">
-        <v>3125</v>
       </c>
       <c r="E1156" s="3">
         <v>1</v>
@@ -30138,13 +30126,13 @@
         <v>1156</v>
       </c>
       <c r="B1157" s="5" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="C1157" s="5" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="D1157" s="5" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="E1157" s="3">
         <v>1</v>
@@ -30155,13 +30143,13 @@
         <v>1157</v>
       </c>
       <c r="B1158" s="5" t="s">
+        <v>3126</v>
+      </c>
+      <c r="C1158" s="5" t="s">
+        <v>3127</v>
+      </c>
+      <c r="D1158" s="5" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1158" s="5" t="s">
-        <v>3129</v>
-      </c>
-      <c r="D1158" s="5" t="s">
-        <v>3130</v>
       </c>
       <c r="E1158" s="3">
         <v>1</v>
@@ -30172,13 +30160,13 @@
         <v>1158</v>
       </c>
       <c r="B1159" s="5" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1159" s="5" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D1159" s="5" t="s">
         <v>3131</v>
-      </c>
-      <c r="C1159" s="5" t="s">
-        <v>3132</v>
-      </c>
-      <c r="D1159" s="5" t="s">
-        <v>3133</v>
       </c>
       <c r="E1159" s="3">
         <v>1</v>
@@ -30189,13 +30177,13 @@
         <v>1159</v>
       </c>
       <c r="B1160" s="5" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1160" s="5" t="s">
+        <v>3133</v>
+      </c>
+      <c r="D1160" s="5" t="s">
         <v>3134</v>
-      </c>
-      <c r="C1160" s="5" t="s">
-        <v>3135</v>
-      </c>
-      <c r="D1160" s="5" t="s">
-        <v>3136</v>
       </c>
       <c r="E1160" s="3">
         <v>1</v>
@@ -30206,13 +30194,13 @@
         <v>1160</v>
       </c>
       <c r="B1161" s="5" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1161" s="5" t="s">
+        <v>3136</v>
+      </c>
+      <c r="D1161" s="5" t="s">
         <v>3137</v>
-      </c>
-      <c r="C1161" s="5" t="s">
-        <v>3138</v>
-      </c>
-      <c r="D1161" s="5" t="s">
-        <v>3139</v>
       </c>
       <c r="E1161" s="3">
         <v>1</v>
@@ -30223,13 +30211,13 @@
         <v>1161</v>
       </c>
       <c r="B1162" s="5" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C1162" s="5" t="s">
+        <v>3139</v>
+      </c>
+      <c r="D1162" s="5" t="s">
         <v>3140</v>
-      </c>
-      <c r="C1162" s="5" t="s">
-        <v>3141</v>
-      </c>
-      <c r="D1162" s="5" t="s">
-        <v>3142</v>
       </c>
       <c r="E1162" s="3">
         <v>1</v>
@@ -30240,13 +30228,13 @@
         <v>1162</v>
       </c>
       <c r="B1163" s="5" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1163" s="5" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D1163" s="5" t="s">
         <v>3143</v>
-      </c>
-      <c r="C1163" s="5" t="s">
-        <v>3144</v>
-      </c>
-      <c r="D1163" s="5" t="s">
-        <v>3145</v>
       </c>
       <c r="E1163" s="3">
         <v>1</v>
@@ -30257,13 +30245,13 @@
         <v>1163</v>
       </c>
       <c r="B1164" s="5" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1164" s="5" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D1164" s="5" t="s">
         <v>3146</v>
-      </c>
-      <c r="C1164" s="5" t="s">
-        <v>3147</v>
-      </c>
-      <c r="D1164" s="5" t="s">
-        <v>3148</v>
       </c>
       <c r="E1164" s="3">
         <v>1</v>
@@ -30274,13 +30262,13 @@
         <v>1164</v>
       </c>
       <c r="B1165" s="5" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1165" s="5" t="s">
+        <v>3148</v>
+      </c>
+      <c r="D1165" s="5" t="s">
         <v>3149</v>
-      </c>
-      <c r="C1165" s="5" t="s">
-        <v>3150</v>
-      </c>
-      <c r="D1165" s="5" t="s">
-        <v>3151</v>
       </c>
       <c r="E1165" s="3">
         <v>1</v>
@@ -30291,13 +30279,13 @@
         <v>1165</v>
       </c>
       <c r="B1166" s="5" t="s">
+        <v>3150</v>
+      </c>
+      <c r="C1166" s="5" t="s">
+        <v>3151</v>
+      </c>
+      <c r="D1166" s="5" t="s">
         <v>3152</v>
-      </c>
-      <c r="C1166" s="5" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D1166" s="5" t="s">
-        <v>3154</v>
       </c>
       <c r="E1166" s="3">
         <v>1</v>
@@ -30308,13 +30296,13 @@
         <v>1166</v>
       </c>
       <c r="B1167" s="5" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1167" s="5" t="s">
+        <v>3154</v>
+      </c>
+      <c r="D1167" s="5" t="s">
         <v>3155</v>
-      </c>
-      <c r="C1167" s="5" t="s">
-        <v>3156</v>
-      </c>
-      <c r="D1167" s="5" t="s">
-        <v>3157</v>
       </c>
       <c r="E1167" s="3">
         <v>1</v>
